--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -1007,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1015,11 +1015,12 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1050,25 +1051,30 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>roll_before</t>
+          <t>base_roll</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>base_roll_is</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>names_left_off_or_fall</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>per_100</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>state_per_100</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1103,13 +1109,18 @@
       <c r="F2" t="n">
         <v>10388363</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>4688703</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>45.13</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>19.48</v>
       </c>
     </row>
@@ -1142,13 +1153,18 @@
       <c r="F3" t="n">
         <v>1851499</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>227324</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>12.28</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>19.48</v>
       </c>
     </row>
@@ -1181,13 +1197,18 @@
       <c r="F4" t="n">
         <v>43192452</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>5880312</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>13.61</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>19.48</v>
       </c>
     </row>
@@ -1220,16 +1241,21 @@
       <c r="F5" t="n">
         <v>4736669</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>1941444</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>40.99</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>21.7</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>figures as reported in the press</t>
         </is>
@@ -1264,16 +1290,21 @@
       <c r="F6" t="n">
         <v>8136309</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>2656935</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>32.66</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>21.7</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>figures as reported in the press</t>
         </is>
@@ -1308,16 +1339,21 @@
       <c r="F7" t="n">
         <v>20953470</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>2740856</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>13.08</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>21.7</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>figures as reported in the press</t>
         </is>
@@ -1352,13 +1388,18 @@
       <c r="F8" t="n">
         <v>4004694</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>1425018</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>35.58</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>15.19</v>
       </c>
     </row>
@@ -1391,13 +1432,18 @@
       <c r="F9" t="n">
         <v>7770786</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>1595922</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>20.54</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>15.19</v>
       </c>
     </row>
@@ -1430,13 +1476,18 @@
       <c r="F10" t="n">
         <v>52339107</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>6716891</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>12.83</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>15.19</v>
       </c>
     </row>
@@ -1469,13 +1520,18 @@
       <c r="F11" t="n">
         <v>10385510</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>3608922</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>34.75</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>21.14</v>
       </c>
     </row>
@@ -1508,13 +1564,18 @@
       <c r="F12" t="n">
         <v>9826568</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>3528086</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>35.9</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>21.14</v>
       </c>
     </row>
@@ -1547,13 +1608,18 @@
       <c r="F13" t="n">
         <v>77641971</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>13551479</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>17.45</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>21.14</v>
       </c>
     </row>
@@ -1586,13 +1652,18 @@
       <c r="F14" t="n">
         <v>9080173</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>2866481</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>31.57</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>21.14</v>
       </c>
     </row>
@@ -1625,13 +1696,18 @@
       <c r="F15" t="n">
         <v>88773876</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>17822006</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>20.08</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>21.14</v>
       </c>
     </row>
@@ -1664,15 +1740,20 @@
       <c r="F16" t="n">
         <v>14510299</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>4756722</v>
-      </c>
-      <c r="H16" t="n">
-        <v>32.78</v>
       </c>
       <c r="I16" t="n">
         <v>32.78</v>
       </c>
+      <c r="J16" t="n">
+        <v>32.78</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1703,13 +1784,18 @@
       <c r="F17" t="n">
         <v>4703664</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>1265610</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>26.91</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>32.78</v>
       </c>
     </row>
@@ -1742,13 +1828,18 @@
       <c r="F18" t="n">
         <v>3994535</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>1200138</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>30.04</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>18.7</v>
       </c>
     </row>
@@ -1781,13 +1872,18 @@
       <c r="F19" t="n">
         <v>4656702</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>780325</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>16.76</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>18.7</v>
       </c>
     </row>
@@ -1820,13 +1916,18 @@
       <c r="F20" t="n">
         <v>145778855</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>26893604</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>18.45</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>18.7</v>
       </c>
     </row>
@@ -1859,13 +1960,18 @@
       <c r="F21" t="n">
         <v>6259620</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>1452704</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>23.21</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -1898,13 +2004,18 @@
       <c r="F22" t="n">
         <v>1389712</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>215786</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>15.53</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -1937,13 +2048,18 @@
       <c r="F23" t="n">
         <v>43194104</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
         <v>5704837</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>13.21</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -1976,13 +2092,18 @@
       <c r="F24" t="n">
         <v>4873512</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
         <v>1250319</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>25.66</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -2015,13 +2136,18 @@
       <c r="F25" t="n">
         <v>45969924</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>roll before the revision</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
         <v>6123008</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>13.32</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -2054,16 +2180,21 @@
       <c r="F26" t="n">
         <v>4843590</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2025 election roll</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
         <v>415580</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>8.58</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>9.25</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>per 100 on the 2025 roll</t>
         </is>
@@ -2098,16 +2229,21 @@
       <c r="F27" t="n">
         <v>69856324</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2025 election roll</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
         <v>6494979</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>9.25</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>per 100 on the 2025 roll</t>
         </is>
@@ -2142,13 +2278,18 @@
       <c r="F28" t="n">
         <v>2405408</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2024 Lok Sabha roll</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>598153</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>24.87</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>6.83</v>
       </c>
     </row>
@@ -2181,13 +2322,18 @@
       <c r="F29" t="n">
         <v>12360295</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2024 Lok Sabha roll</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
         <v>1158176</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>9.369999999999999</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>6.83</v>
       </c>
     </row>
@@ -2220,13 +2366,18 @@
       <c r="F30" t="n">
         <v>61244303</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2024 Lok Sabha roll</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>3437047</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>5.61</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>6.83</v>
       </c>
     </row>
@@ -2259,13 +2410,18 @@
       <c r="F31" t="n">
         <v>2638106</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>January 2025 roll</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>307463</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>11.65</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>8.52</v>
       </c>
     </row>
@@ -2298,13 +2454,18 @@
       <c r="F32" t="n">
         <v>25172836</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>January 2025 roll</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>2061127</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>8.19</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>8.52</v>
       </c>
     </row>
@@ -4743,7 +4904,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4774,7 +4935,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -4805,7 +4966,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -4836,7 +4997,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -4867,7 +5028,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -4898,7 +5059,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -4929,7 +5090,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -4960,7 +5121,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -4991,7 +5152,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -5022,7 +5183,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -5053,7 +5214,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -5084,7 +5245,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -5115,7 +5276,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -5146,7 +5307,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -5177,7 +5338,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -5208,7 +5369,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -5239,7 +5400,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -5270,7 +5431,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -5301,7 +5462,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -5332,7 +5493,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -5363,7 +5524,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -5394,7 +5555,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -5425,7 +5586,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -5456,7 +5617,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -5487,7 +5648,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -5518,7 +5679,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -5549,7 +5710,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -5580,7 +5741,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5611,7 +5772,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5642,7 +5803,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5673,7 +5834,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5704,7 +5865,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5735,7 +5896,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5766,7 +5927,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5797,7 +5958,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5828,7 +5989,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5859,7 +6020,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5890,7 +6051,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>names removed at the draft</t>
+          <t>names removed in both phases</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5921,7 +6082,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5952,7 +6113,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5983,7 +6144,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6014,7 +6175,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6045,7 +6206,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6076,7 +6237,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6107,7 +6268,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6138,7 +6299,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6169,7 +6330,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6200,7 +6361,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6231,7 +6392,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6262,7 +6423,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6293,7 +6454,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6324,7 +6485,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6355,7 +6516,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -6386,7 +6547,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -6417,7 +6578,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -6448,7 +6609,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -6479,7 +6640,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -6510,7 +6671,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -6541,7 +6702,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -6572,7 +6733,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -6603,7 +6764,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -6634,7 +6795,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>fall in the roll, 2024 roll to the draft</t>
+          <t>fall in the roll, 2024 roll to the 2026 election roll</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -47755,7 +47916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C184"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -48473,7 +48634,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>People born in the state and counted living in another state at the 2011 census, as a percentage, from the census place-of-birth tables.</t>
+          <t>People born in the state and counted living in another state at the 2011 census, as a percentage, from Census table D-01 (place of birth). The curated file does not record which population the percentage is of.</t>
         </is>
       </c>
     </row>
@@ -48490,7 +48651,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>People counted living in the state at the 2011 census who were born in another state, as a percentage, from the census place-of-birth tables.</t>
+          <t>People counted living in the state at the 2011 census who were born in another state, as a percentage, from Census table D-01 (place of birth). The curated file does not record which population the percentage is of.</t>
         </is>
       </c>
     </row>
@@ -49930,12 +50091,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>roll_before</t>
+          <t>base_roll</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Electors on the roll the count is measured against, as a count, which is the roll before the revision except for Patna (the 2025 roll), Kolkata (the 2024 Lok Sabha roll) and Kochi (the January 2025 roll).</t>
+          <t>Electors on the roll the count is measured against, the roll named in base_roll_is.</t>
         </is>
       </c>
     </row>
@@ -49947,12 +50108,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>names_left_off_or_fall</t>
+          <t>base_roll_is</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Names left off the draft, or for Kolkata and Kochi the fall in the roll to the draft, as a count (Patna counts both of Bihar's phases).</t>
+          <t>Which roll base_roll is. It is the roll before the revision everywhere except Patna (the 2025 election roll), Kolkata (the 2024 Lok Sabha roll) and Kochi (the January 2025 roll).</t>
         </is>
       </c>
     </row>
@@ -49964,12 +50125,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>per_100</t>
+          <t>names_left_off_or_fall</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>names_left_off_or_fall per 100 electors on roll_before.</t>
+          <t>Names left off the draft, or for Kolkata and Kochi the fall in the roll to the draft, as a count (Patna counts both of Bihar's phases).</t>
         </is>
       </c>
     </row>
@@ -49981,12 +50142,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>state_per_100</t>
+          <t>per_100</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>The same rate for the city's whole state.</t>
+          <t>names_left_off_or_fall per 100 electors on roll_before.</t>
         </is>
       </c>
     </row>
@@ -49998,29 +50159,29 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>state_per_100</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>A note where the row's figures differ in kind, marking Hyderabad's figures as reported in the press and Patna's as per 100 on the 2025 roll.</t>
+          <t>The same rate for the city's whole state.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Reserved and general seats</t>
+          <t>Cities against their states</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>The state.</t>
+          <t>A note where the row's figures differ in kind, marking Hyderabad's figures as reported in the press and Patna's as per 100 on the 2025 roll.</t>
         </is>
       </c>
     </row>
@@ -50032,12 +50193,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>The count and its base, which is names removed in both phases per 100 on the 2025 roll for Bihar, names left off per 100 on the roll before for Tamil Nadu, Gujarat and Delhi, and the fall in the roll to the draft per 100 for West Bengal (from the 2024 roll) and Kerala (from the January 2025 roll).</t>
+          <t>The state.</t>
         </is>
       </c>
     </row>
@@ -50049,12 +50210,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>The kind of seat under the Delimitation Order of 2008, GEN for general, SC for Scheduled Castes and ST for Scheduled Tribes.</t>
+          <t>The count and its base, which is names removed in both phases per 100 on the 2025 roll for Bihar, names left off per 100 on the roll before for Tamil Nadu, Gujarat and Delhi, and the fall in the roll to the draft per 100 for West Bengal (from the 2024 roll) and Kerala (from the January 2025 roll).</t>
         </is>
       </c>
     </row>
@@ -50066,12 +50227,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>seats</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>The number of assembly seats in that category.</t>
+          <t>The kind of seat under the Delimitation Order of 2008, GEN for general, SC for Scheduled Castes and ST for Scheduled Tribes.</t>
         </is>
       </c>
     </row>
@@ -50083,12 +50244,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>rate</t>
+          <t>seats</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>The count per 100 electors across all seats in the category, in the measure named.</t>
+          <t>The number of assembly seats in that category.</t>
         </is>
       </c>
     </row>
@@ -50100,12 +50261,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>mean_gap_vs_general_seats_same_district</t>
+          <t>rate</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>The average, over the reserved seats, of each seat's rate less the rate of the general seats in its own district, in points per 100, blank for general seats.</t>
+          <t>The count per 100 electors across all seats in the category, in the measure named.</t>
         </is>
       </c>
     </row>
@@ -50117,12 +50278,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>seats_above_their_district</t>
+          <t>mean_gap_vs_general_seats_same_district</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>How many reserved seats have a higher rate than the general seats of their own district.</t>
+          <t>The average, over the reserved seats, of each seat's rate less the rate of the general seats in its own district, in points per 100, blank for general seats.</t>
         </is>
       </c>
     </row>
@@ -50134,29 +50295,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>seats_compared</t>
+          <t>seats_above_their_district</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>How many reserved seats had general seats in their district to be compared with.</t>
+          <t>How many reserved seats have a higher rate than the general seats of their own district.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Border districts against the re</t>
+          <t>Reserved and general seats</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>seats_compared</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>The state.</t>
+          <t>How many reserved seats had general seats in their district to be compared with.</t>
         </is>
       </c>
     </row>
@@ -50168,12 +50329,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>The count and its base, which is names left off per 100 on the roll before (Uttar Pradesh, Gujarat), names removed in both phases per 100 on the 2025 roll (Bihar), the fall in the roll per 100 from the 2024 roll to the draft (West Bengal) and names removed after the draft per 1,000 on the draft (Uttarakhand).</t>
+          <t>The state.</t>
         </is>
       </c>
     </row>
@@ -50185,12 +50346,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Which districts the row covers, where border is every district on the Government of India's list of Border Guarding Districts, interior the rest, interior_without_city the rest without the city's districts, and border district names one listed district.</t>
+          <t>The count and its base, which is names left off per 100 on the roll before (Uttar Pradesh, Gujarat), names removed in both phases per 100 on the 2025 roll (Bihar), the fall in the roll per 100 from the 2024 roll to the draft (West Bengal) and names removed after the draft per 1,000 on the draft (Uttarakhand).</t>
         </is>
       </c>
     </row>
@@ -50202,12 +50363,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>districts</t>
+          <t>part</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>The number of districts in the row.</t>
+          <t>Which districts the row covers, where border is every district on the Government of India's list of Border Guarding Districts, interior the rest, interior_without_city the rest without the city's districts, and border district names one listed district.</t>
         </is>
       </c>
     </row>
@@ -50219,12 +50380,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>districts</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Electors on the roll the measure divides by, summed over the districts, blank on single-district rows.</t>
+          <t>The number of districts in the row.</t>
         </is>
       </c>
     </row>
@@ -50236,12 +50397,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>The count the measure names, summed over the districts, blank on single-district rows.</t>
+          <t>Electors on the roll the measure divides by, summed over the districts, blank on single-district rows.</t>
         </is>
       </c>
     </row>
@@ -50253,12 +50414,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>rate</t>
+          <t>count</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>count per 100 electors on base, or per 1,000 for Uttarakhand.</t>
+          <t>The count the measure names, summed over the districts, blank on single-district rows.</t>
         </is>
       </c>
     </row>
@@ -50270,12 +50431,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>dead_share</t>
+          <t>rate</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>The share of the count entered as dead, as a percentage, where reasons were published (Uttar Pradesh and Gujarat), and the reason is what the officer wrote down, and nobody checked it.</t>
+          <t>count per 100 electors on base, or per 1,000 for Uttarakhand.</t>
         </is>
       </c>
     </row>
@@ -50287,12 +50448,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>shifted_absent_share</t>
+          <t>dead_share</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>The share of the count entered as shifted or absent, as a percentage, where reasons were published.</t>
+          <t>The share of the count entered as dead, as a percentage, where reasons were published (Uttar Pradesh and Gujarat), and the reason is what the officer wrote down, and nobody checked it.</t>
         </is>
       </c>
     </row>
@@ -50304,29 +50465,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>enrolled_elsewhere_share</t>
+          <t>shifted_absent_share</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>The share of the count entered as enrolled somewhere else, as a percentage, where reasons were published.</t>
+          <t>The share of the count entered as shifted or absent, as a percentage, where reasons were published.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Women, state by state and distr</t>
+          <t>Border districts against the re</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>enrolled_elsewhere_share</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Whether the row is a whole state or one district.</t>
+          <t>The share of the count entered as enrolled somewhere else, as a percentage, where reasons were published.</t>
         </is>
       </c>
     </row>
@@ -50338,12 +50499,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>level</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>The state.</t>
+          <t>Whether the row is a whole state or one district.</t>
         </is>
       </c>
     </row>
@@ -50355,12 +50516,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>The district, blank on state rows.</t>
+          <t>The state.</t>
         </is>
       </c>
     </row>
@@ -50372,12 +50533,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>The count the row's shares are of, as labelled by the build, and for West Bengal's district rows the share is in fact of the fall to the 2026 election roll while for Bihar's it is of the names removed in both phases.</t>
+          <t>The district, blank on state rows.</t>
         </is>
       </c>
     </row>
@@ -50389,12 +50550,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>women_share_of_roll</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Women as a percentage of the roll the count is taken from (the roll before for states, Bihar's draft plus phase 1 removals, the 2024 and January 2025 rolls for West Bengal and Kerala, and the draft for Uttarakhand).</t>
+          <t>The count the row's shares are of. For district rows it names the state's own measure, such as the names removed in both phases in Bihar or the fall from the 2024 roll to the 2026 election roll in West Bengal.</t>
         </is>
       </c>
     </row>
@@ -50406,12 +50567,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>women_share_of_count</t>
+          <t>women_share_of_roll</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Women as a percentage of the count named in measure.</t>
+          <t>Women as a percentage of the roll the count is taken from (the roll before for states, Bihar's draft plus phase 1 removals, the 2024 and January 2025 rolls for West Bengal and Kerala, and the draft for Uttarakhand).</t>
         </is>
       </c>
     </row>
@@ -50423,12 +50584,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>gap_points</t>
+          <t>women_share_of_count</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>women_share_of_count less women_share_of_roll, in percentage points.</t>
+          <t>Women as a percentage of the count named in measure.</t>
         </is>
       </c>
     </row>
@@ -50440,12 +50601,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>women_left_off_per_100_women</t>
+          <t>gap_points</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Women left off the draft per 100 women on the roll before, where the roll by sex is the roll before times women's share of it, on state rows only.</t>
+          <t>women_share_of_count less women_share_of_roll, in percentage points.</t>
         </is>
       </c>
     </row>
@@ -50457,12 +50618,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>men_left_off_per_100_men</t>
+          <t>women_left_off_per_100_women</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Men left off the draft per 100 men on the roll before, on state rows only.</t>
+          <t>Women left off the draft per 100 women on the roll before, where the roll by sex is the roll before times women's share of it, on state rows only.</t>
         </is>
       </c>
     </row>
@@ -50474,12 +50635,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>men_left_off_per_100_men</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>How firm the state's split by sex is (lists, exact, rounded, proxy or unverified), on state rows only.</t>
+          <t>Men left off the draft per 100 men on the roll before, on state rows only.</t>
         </is>
       </c>
     </row>
@@ -50491,29 +50652,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>The address of the source of the state's split by sex, on state rows only.</t>
+          <t>How firm the state's split by sex is (lists, exact, rounded, proxy or unverified), on state rows only.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Rural, mixed and urban district</t>
+          <t>Women, state by state and distr</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>The state.</t>
+          <t>The address of the source of the state's split by sex, on state rows only.</t>
         </is>
       </c>
     </row>
@@ -50525,12 +50686,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>What is counted, where left_off means names left off the draft per 100 on the roll before, roll_2025 means Bihar's names removed in both phases per 100 on the 2025 roll, and fall means the fall in the roll to the draft (West Bengal from the 2024 roll, Kerala from the January 2025 roll).</t>
+          <t>The state.</t>
         </is>
       </c>
     </row>
@@ -50542,12 +50703,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>district_2011</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>The district as it stood at the 2011 census, which is the unit each row adds up.</t>
+          <t>What is counted, where left_off means names left off the draft per 100 on the roll before, roll_2025 means Bihar's names removed in both phases per 100 on the 2025 roll, and fall means the fall in the roll to the draft (West Bengal from the 2024 roll, Kerala from the January 2025 roll).</t>
         </is>
       </c>
     </row>
@@ -50559,12 +50720,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>census_code</t>
+          <t>district_2011</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>The 2011 census code of that district.</t>
+          <t>The district as it stood at the 2011 census, which is the unit each row adds up.</t>
         </is>
       </c>
     </row>
@@ -50576,12 +50737,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>districts_today</t>
+          <t>census_code</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>The present districts counted under it, each under the 2011 district it was mostly made from, separated by a semicolon character.</t>
+          <t>The 2011 census code of that district.</t>
         </is>
       </c>
     </row>
@@ -50593,12 +50754,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>urban_pct_2011</t>
+          <t>districts_today</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>The share of the 2011 district's people living in towns at the 2011 census, as a percentage, from table A-01.</t>
+          <t>The present districts counted under it, each under the 2011 district it was mostly made from, separated by a semicolon character.</t>
         </is>
       </c>
     </row>
@@ -50610,12 +50771,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>band</t>
+          <t>urban_pct_2011</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>rural where urban_pct_2011 is under 20, mixed from 20 to 50, and urban above 50.</t>
+          <t>The share of the 2011 district's people living in towns at the 2011 census, as a percentage, from table A-01.</t>
         </is>
       </c>
     </row>
@@ -50627,12 +50788,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>roll_before</t>
+          <t>band</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Electors on the roll the count is measured against, summed over the districts, as a count.</t>
+          <t>rural where urban_pct_2011 is under 20, mixed from 20 to 50, and urban above 50.</t>
         </is>
       </c>
     </row>
@@ -50644,12 +50805,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>roll_before</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Names left off, or the fall in the roll, summed over the districts, as a count.</t>
+          <t>Electors on the roll the count is measured against, summed over the districts, as a count.</t>
         </is>
       </c>
     </row>
@@ -50661,29 +50822,29 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>per_100</t>
+          <t>count</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>count per 100 electors on roll_before.</t>
+          <t>Names left off, or the fall in the roll, summed over the districts, as a count.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>Rural, mixed and urban district</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>per_100</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>The state, one of the four that published their rolls by constituency (Tamil Nadu, Kerala, West Bengal and Uttarakhand).</t>
+          <t>count per 100 electors on roll_before.</t>
         </is>
       </c>
     </row>
@@ -50695,12 +50856,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>The assembly constituency number.</t>
+          <t>The state, one of the four that published their rolls by constituency (Tamil Nadu, Kerala, West Bengal and Uttarakhand).</t>
         </is>
       </c>
     </row>
@@ -50712,12 +50873,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>constituency</t>
+          <t>ac</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>The assembly constituency's name.</t>
+          <t>The assembly constituency number.</t>
         </is>
       </c>
     </row>
@@ -50729,12 +50890,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>constituency</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>The district the constituency lies in.</t>
+          <t>The assembly constituency's name.</t>
         </is>
       </c>
     </row>
@@ -50746,12 +50907,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>earlier_roll</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>The earliest roll in the row, which is the roll of 27 October 2025 worked out as the draft plus the names left off for Tamil Nadu, the January 2025 final roll for Kerala, the 2024 Lok Sabha roll for West Bengal and blank for Uttarakhand.</t>
+          <t>The district the constituency lies in.</t>
         </is>
       </c>
     </row>
@@ -50763,12 +50924,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>left_off_draft</t>
+          <t>earlier_roll</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Names left off the draft, as a count, given by constituency only in Tamil Nadu.</t>
+          <t>The earliest roll in the row, which is the roll of 27 October 2025 worked out as the draft plus the names left off for Tamil Nadu, the January 2025 final roll for Kerala, the 2024 Lok Sabha roll for West Bengal and blank for Uttarakhand.</t>
         </is>
       </c>
     </row>
@@ -50780,12 +50941,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>left_off_draft</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Electors on the draft roll (19 December 2025 in Tamil Nadu, 23 December 2025 in Kerala, 16 December 2025 in West Bengal, July 2026 in Uttarakhand).</t>
+          <t>Names left off the draft, as a count, given by constituency only in Tamil Nadu.</t>
         </is>
       </c>
     </row>
@@ -50797,12 +50958,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>added_after_draft</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Claims admitted after the draft, as a count, Uttarakhand only, from the Chief Electoral Officer's PN 63/2026.</t>
+          <t>Electors on the draft roll (19 December 2025 in Tamil Nadu, 23 December 2025 in Kerala, 16 December 2025 in West Bengal, July 2026 in Uttarakhand).</t>
         </is>
       </c>
     </row>
@@ -50814,12 +50975,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>removed_after_draft</t>
+          <t>added_after_draft</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Objections admitted after the draft, as a count, Uttarakhand only, from PN 63/2026.</t>
+          <t>Claims admitted after the draft, as a count, Uttarakhand only, from the Chief Electoral Officer's PN 63/2026.</t>
         </is>
       </c>
     </row>
@@ -50831,12 +50992,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>later_roll</t>
+          <t>removed_after_draft</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>The latest roll in the row, the final roll of 23 February 2026 in Tamil Nadu, 21 February 2026 in Kerala and 3 October 2026 in Uttarakhand, and the roll at the 2026 nominations in West Bengal.</t>
+          <t>Objections admitted after the draft, as a count, Uttarakhand only, from PN 63/2026.</t>
         </is>
       </c>
     </row>
@@ -50848,12 +51009,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>change_draft_to_later</t>
+          <t>later_roll</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>later_roll less draft, a net change that counts new voters added after the draft as well as names put back.</t>
+          <t>The latest roll in the row, the final roll of 23 February 2026 in Tamil Nadu, 21 February 2026 in Kerala and 3 October 2026 in Uttarakhand, and the roll at the 2026 nominations in West Bengal.</t>
         </is>
       </c>
     </row>
@@ -50865,12 +51026,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>change_earlier_to_later</t>
+          <t>change_draft_to_later</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>later_roll less earlier_roll, as a count, which is negative where the roll fell.</t>
+          <t>later_roll less draft, a net change that counts new voters added after the draft as well as names put back.</t>
         </is>
       </c>
     </row>
@@ -50882,10 +51043,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
+          <t>change_earlier_to_later</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>later_roll less earlier_roll, as a count, which is negative where the roll fell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
           <t>change_earlier_to_later_per_100</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>change_earlier_to_later per 100 electors on earlier_roll.</t>
         </is>

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>69856324</v>
+        <v>69846731</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>16316534</v>
+        <v>16314914</v>
       </c>
       <c r="F18" t="n">
         <v>1624329</v>
@@ -3610,13 +3610,13 @@
         <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>58383380</v>
+        <v>58375407</v>
       </c>
       <c r="F19" t="n">
         <v>5286230</v>
       </c>
       <c r="G19" t="n">
-        <v>9.050000000000001</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="20">
@@ -3639,7 +3639,7 @@
         <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>53539790</v>
+        <v>53531817</v>
       </c>
       <c r="F20" t="n">
         <v>4870650</v>
@@ -3668,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>13.9</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="22">
@@ -17164,13 +17164,13 @@
         </is>
       </c>
       <c r="H226" t="n">
-        <v>1127532</v>
+        <v>1125912</v>
       </c>
       <c r="I226" t="n">
         <v>156727</v>
       </c>
       <c r="J226" t="n">
-        <v>13.9</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="227">
@@ -17290,13 +17290,13 @@
         </is>
       </c>
       <c r="H229" t="n">
-        <v>2902355</v>
+        <v>2894382</v>
       </c>
       <c r="I229" t="n">
         <v>210711</v>
       </c>
       <c r="J229" t="n">
-        <v>7.26</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="230">
@@ -48634,7 +48634,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>People born in the state and counted living in another state at the 2011 census, as a percentage, from Census table D-01 (place of birth). The curated file does not record which population the percentage is of.</t>
+          <t>People born in the state and counted in another Indian state at the 2011 census, as a percentage of the state's own population counted in 2011, from Census table D-01 (place of birth). For Bihar that is 79,49,853 over 10,40,99,452, or 7.64.</t>
         </is>
       </c>
     </row>
@@ -48651,7 +48651,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>People counted living in the state at the 2011 census who were born in another state, as a percentage, from Census table D-01 (place of birth). The curated file does not record which population the percentage is of.</t>
+          <t>People counted in the state at the 2011 census who were born in another Indian state, as a percentage of the state's own population counted in 2011, from Census table D-01 (place of birth). People born outside India are not counted. For Bihar that is 10,66,526 over 10,40,99,452, or 1.02.</t>
         </is>
       </c>
     </row>

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -21,8 +21,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Border districts against the re" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Women, state by state and distr" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rural, mixed and urban district" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every constituency in four stat" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protests and disputes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every constituency in four stat" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -964,33 +965,68 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Protests and disputes</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Published table</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Every court case, resolution, protest, Form 7 dispute and software change on the disputes page, with its source</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Press items are what the outlet reported. Allegations are the party's. Nothing here says what anyone intended.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>data/india/disputes.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>Every constituency in four stat</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Published table</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>constituency</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>738</v>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Every constituency of Tamil Nadu, Kerala, West Bengal and Uttarakhand in one table</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Each state measures a different thing, named in the state's rows. Nothing is added across states. Only Uttarakhand has gross additions and deletions.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>data/india/ac_change.csv</t>
         </is>
@@ -19284,6 +19320,6095 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H155"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>what_happened</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>commission_reply</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Counsel for ADR and other petitioners mentioned seven petitions against the Bihar revision, and the Court let them be filed during the vacation and listed them for 10 July 2025.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/35785/35785_2025_11_801_62247_Order_07-Jul-2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Supreme Court of India (judgment of 27.05.2026, 2026 INSC 564, para 10.8)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The Court issued notice to the Commission and said the petitions raised three questions about its power, its method and the timing before the Bihar election, according to the account in the Court's 2026 judgment.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/35785/35785_2025_1_1501_71617_Judgement_27-May-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>The Court recorded the Commission's agreement to publish, district by district and searchable by EPIC number, the list of about 65 lakh electors left off the Bihar draft roll with the reason for each.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/35785/35785_2025_2_34_63142_Order_14-Aug-2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The Court directed the Commission to accept Aadhaar as proof of identity for the Bihar revision and said it is no proof of citizenship.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/35785/35785_2025_2_26_63969_Order_08-Sep-2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The Court recorded that about 1.40 crore people in West Bengal had been sent notices and directed that names in the logical discrepancy list be displayed at panchayat, block and ward offices.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_30_67603_Order_19-Jan-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>The order records that Chief Minister Mamata Banerjee appeared in her own petition on 4 February 2026, and the Court directed the 8,505 officers the state offered to report to the district officers.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_40_68501_Order_09-Feb-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The Court recorded the Chief Justice of the Calcutta High Court's report that over 10,16,000 objections had been disposed of, and directed that appeals against the judicial officers' orders go to tribunals of former Chief Justices and judges.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_42_69352_Order_10-Mar-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>After seven judicial officers deciding SIR objections were surrounded at a BDO office in Maldah district, the Court directed central forces for them and directed the Commission to give the inquiry to an independent agency such as the CBI or the NIA.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2026/19822/19822_2026_1_51_69596_Order_02-Apr-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>The Court directed that appeals the tribunals decided by 21 or 27 April 2026, before polling, be given effect in a supplementary roll, and said a pending appeal gave no right to vote.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_53_70166_Order_13-Apr-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The Supreme Court's judgment of 27 May 2026 records that some petitions, W.P.(C) 855 of 2025 among them, were filed in support of the revision and asked for it to be held at regular intervals.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/35785/35785_2025_1_1501_71617_Judgement_27-May-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Supreme Court of India (2026 INSC 564)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>The Court held the Bihar revision lawful under section 21(3) of the Representation of the People Act read with Article 324 and said declining to enrol someone does not declare that person not to be a citizen.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/35785/35785_2025_1_1501_71617_Judgement_27-May-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Supreme Court of India (2026 INSC 564, para 186(h))</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>The Court directed the Commission to refer within four weeks the cases it deleted as non-citizens to the authority under the Citizenship Act and allowed people in Bihar wrongly deleted as absent, dead, shifted or duplicate to seek judicial review.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/35785/35785_2025_1_1501_71617_Judgement_27-May-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>High Court for the State of Telangana (order reproduced by LiveLaw)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>A Charminar voter asked the High Court to restore his family's deleted names, and the Court dismissed the petition and told him to use the revision then under way.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/pdf_upload/2026/07/01/wp201882026-683463.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LiveLaw</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Trinamool Congress MP Mahua Moitra asked the Supreme Court to quash the Commission's order of 24 June 2025 and to stop it from ordering the same revision in other states, LiveLaw reported.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/amp/top-stories/trinamool-mp-mahua-moitra-moves-supreme-court-against-electoral-roll-revision-in-bihar-296665</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LiveLaw</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>A former AIADMK MLA asked the Madras High Court to order a re-verification of 229 booths in T. Nagar, and the Court adjourned the case after the Commission said the revision would begin within a week, LiveLaw reported.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/amp/high-court/madras-high-court/madras-high-court-eci-tells-tamil-nadu-sir-electoral-rolls-will-commence-in-a-week-307729</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>The Week</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>A PIL asked the Calcutta High Court to have the West Bengal revision use the current roll in place of the 2002 roll and to protect booth level officers, and the Court asked the Commission for an affidavit, The Week reported.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/news/india/2025/11/06/calcutta-high-court-asks-ec-to-submit-affidavit-on-pil-challenging-sir-in-west-bengal.amp.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>The Leaflet</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The Court issued notice on the petitions against the second phase in Tamil Nadu and West Bengal and asked the High Courts to hold back their own cases on the revision, The Leaflet reported.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://theleaflet.in/amp/story/leaflet-reports/supreme-court-seeks-ecis-response-on-pleas-challenging-sir-in-tamil-nadu-west-bengal</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SCC Online</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>The Kerala government asked the High Court to put off the revision until the local body elections ended, and the Court dismissed the petition because the Supreme Court had asked High Courts to hold back such cases, SCC Online reported.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.scconline.com/blog/?p=366827</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>National Herald</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>On a TVK application saying 35 to 40 booth level officers had died under work pressure, the Court suggested that states provide more staff and cut working hours in proportion, National Herald reported.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.nationalheraldindia.com/amp/story/politics/supreme-court-issues-directions-to-ease-blo-workload-in-sir-exercise</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LiveLaw</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>The Kerala government and leaders of the IUML, Congress and CPI(M) asked for more time for enumeration forms, and the Court put off a decision to 18 December, LiveLaw reported.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/amp/top-stories/supreme-court-refuses-to-extend-kerala-sir-deadline-will-decide-on-december-18-312715</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LiveLaw</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>A PIL asked the Allahabad High Court to apply the Commission's revision guidelines to Uttar Pradesh's panchayat rolls, and the Court dismissed it, LiveLaw reported.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/amp/high-court/allahabad-high-court/allahabad-high-court-rejects-pil-eci-sir-guidelines-up-three-tier-panchayat-roll-revision-513775</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LawTrend</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>The Surat district Congress president and a Seva Dal organiser asked the Gujarat High Court to reject objections not filed under the rules, to act against false objections and to halt the revision, LawTrend reported.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://lawtrend.in/?p=336152</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Verdictum</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Residents displaced by a 2023 demolition said they were left out of the Uttar Pradesh revision, and the Court sent them to the district election officer with liberty to go to the Allahabad High Court, Verdictum reported.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.verdictum.in/court-updates/supreme-court/declines-plea-displaced-lucknow-akbar-nagar-residents-voter-roll-exclusion-up-sir-1608410</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Supreme Court Observer</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Counsel told the Court that 136 of nearly 27 lakh appeals had been decided, and the Court declined fresh grievances and sent the parties to the Chief Justice of the Calcutta High Court, Supreme Court Observer reported.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.scobserver.in/reports/west-bengal-sir-sc-pushes-sir-disputes-to-calcutta-hc-as-appeal-backlog-mounts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Telangana Today</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Adivasi Sena asked the Telangana High Court to have non-tribal voters it called ineligible removed from the rolls of the Fifth Schedule Areas during the revision, and the Court sought replies, Telangana Today reported.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://telanganatoday.com/telangana-hc-seeks-response-on-plea-against-non-tribal-voters-in-scheduled-areas</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Telangana Today</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Petitioners asked the Telangana High Court to strike the state's Family Register Certificate from the revision's list of documents, and the Court gave the Commission time and listed the case for 12 August, Telangana Today reported.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://telanganatoday.com/telangana-hc-takes-up-plea-on-family-register-certificate-as-voter-eligibility-proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LiveLaw</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>A PIL asked the Delhi High Court for special arrangements so homeless and displaced people could enrol in the revision, and the Court reserved its order and said it would not monitor the policy, LiveLaw reported.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/high-court/delhi-high-court/delhi-sir-include-homeless-demolition-displaced-voters-govt-policy-decision-546448</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LiveLaw</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>A man deleted in the revision said it was blocking his passport renewal, and the Calcutta High Court told the appellate tribunal to decide his appeal within two weeks without going into the merits, LiveLaw reported.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/high-court/calcutta-high-court/calcutta-high-court-directs-sir-tribunal-to-expeditiously-decide-plea-of-saudi-resident-unable-to-renew-passport-over-voter-list-deletion-546623</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LiveLaw</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Delhi Congress president Devender Yadav challenged the Form 6 declaration that deleted voters must sign as first-time applicants, and he withdrew the petition after the Court told him to file it as a PIL, LiveLaw reported.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/high-court/delhi-high-court/delhi-sir-high-court-refuses-to-entertain-plea-against-first-time-applicant-declaration-for-deleted-voters-says-file-pil-549522</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ThePrint (PTI)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Activists Anjali Bhardwaj and Amrita Johri asked for the list of Delhi voters sent notices and the criteria for logical discrepancies, and the bench told the Commission to look at extra safeguards, ThePrint reported.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/delhi-sir-sc-says-notices-going-to-people-mechanically-asks-ec-to-adopt-additional-safeguards/3049910/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>In the courts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LiveLaw</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>A petition asked the Court to quash 14 decisions it said the Chief Election Commissioner took alone, and the Court issued notice, tagged it with a similar case and said it had not approved any modified Form 6, LiveLaw reported.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/top-stories/supreme-court-says-modified-form-6-not-approved-by-it-election-commission-pleas-against-cec-gyanesh-kumar-unilateral-sir-decisions-553100</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Resolutions in the Assemblies</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>The Week (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>The Week, carrying a PTI report, said the Jharkhand Assembly passed a resolution opposing the SIR, moved by Parliamentary Affairs Minister Radhakrishna Kishore on behalf of the INDIA bloc. The BJP opposed it. When a Congress member asked for a vote, the Speaker ruled that it stood passed because the ruling coalition had a majority.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/26/cal40-jh-assembly-ld-sir.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Resolutions in the Assemblies</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Siasat Daily (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>The Siasat Daily, carrying a PTI report, said the Kerala Assembly unanimously passed a resolution moved by Chief Minister Pinarayi Vijayan against the SIR in the state, with the Congress-led opposition backing it.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.siasat.com/kerala-assembly-passes-unanimous-resolution-against-sir-3277487/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that a Bihar bandh called by the INDIA bloc parties against the SIR disrupted life across much of the state, with Rahul Gandhi and Tejashwi Yadav taking part.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/!state/bihar-band-effect-in-different-district-of-bihar-election-2025-enn25070904786</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Deccan Herald (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Deccan Herald, carrying a PTI report, said opposition members protested against the SIR inside the Bihar Assembly on the first day of its monsoon session, with CPI(ML) Liberation legislators wearing black.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/bihar/anti-sir-protests-rock-bihar-assembly-on-inaugural-day-of-monsoon-session-3640011</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that INDIA bloc MPs protested at the Makar Dwar of Parliament against the Bihar SIR for a fifth day running and demanded that it be rolled back.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/!bharat/several-mps-of-the-india-bloc-parties-protest-against-sir-enn25072801958</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>The Wire</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>The Wire reported that Delhi Police detained opposition MPs, among them Mallikarjun Kharge and Rahul Gandhi, when their march from Parliament to the Election Commission against the Bihar SIR was stopped, and that they were released in the afternoon.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>The Wire reported that the Commission had written to Jairam Ramesh the day before asking for the names of 30 members for a meeting “due to limitation of space”.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://thewire.in/government/opposition-mps-including-rahul-gandhi-detained-on-their-way-to-election-commission</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that Rahul Gandhi began a 16-day Vote Adhikar Yatra from Sasaram against the SIR in Bihar, due to end with a rally in Patna on 1 September. The Congress leader alleged that the SIR was being done to steal votes.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/!state/rahul-gandhi-kicks-off-vote-adhikar-yatra-in-bihar-to-protect-electoral-rights-enn25081702682</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>The News Minute</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>The News Minute reported that an all-party meeting chaired by Chief Minister M.K. Stalin, attended by nearly 50 parties, resolved to approach the Supreme Court against the SIR in Tamil Nadu. The AIADMK and the BJP were not invited and several other parties stayed away.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.thenewsminute.com/tamil-nadu/tamil-nadu-all-party-meeting-opposes-sir-decides-to-approach-sc</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that Chief Minister Mamata Banerjee led a procession in Kolkata against the SIR. She called the SIR an assault on people's existence and democratic rights.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/state/mamata-leads-massive-kolkata-rally-against-sir-enn25110406838</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Akashvani News (All India Radio)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Akashvani News reported that the DMK and its alliance partners held protest demonstrations across Tamil Nadu against the SIR, with MPs, MLAs and district functionaries taking part.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.newsonair.gov.in/dmk-allies-protest-against-sir-revision-in-tamil-nadu</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>The Tribune reported that Mamata Banerjee led a three-km march from Bongaon to Thakurnagar in North 24 Parganas against the SIR, after addressing a rally at Bangaon.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>The Tribune reported that the Commission granted a five-member TMC delegation a meeting on 28 November.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/top-headlines/mamata-leads-anti-sir-march-ec-to-meet-tmc-leaders-on-nov-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Siasat Daily (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The Siasat Daily, carrying a PTI report, said the united opposition held a protest at Chachal in Guwahati against alleged irregularities in the draft rolls of Assam's Special Revision. Assam Congress president Gaurav Gogoi accused Chief Minister Himanta Biswa Sarma of misusing the Election Commission.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>The report said the Commission stated that the flagged names had not yet been deleted and would only be processed after formal applications in the claims and objections period.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.siasat.com/opposition-in-assam-protests-vote-theft-through-sr-slams-himanta-bjp-3334019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that trade unions, women's groups, student bodies and Dalit and minority rights groups protested against the SIR at Freedom Park in Bengaluru under the banner My Vote, My Right, and urged the state government to take a stand.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/state/citizens-protest-special-intensive-revision-in-bengaluru-enn26020705793</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that Mamata Banerjee ended her sit-in against the SIR on its fifth day after the Supreme Court ordered appellate tribunals to hear appeals against exclusions in West Bengal. She said the protest was suspended temporarily.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/state/mamata-lifts-dharna-against-flaws-in-sir-hails-sc-order-on-forming-appellate-body-enn26031006780</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that a Congress delegation led by Kumari Selja staged a sit-in outside the Election Commission headquarters in Delhi over the SIR in Uttarakhand after saying it was not allowed into the premises.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/bharat/congress-alleges-irregularities-in-sir-in-uttarakhand-seeks-election-commission-intervention-enn26082006661</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Business Today reported that Congress workers protested in several states demanding the resignation of Chief Election Commissioner Gyanesh Kumar over the handling of the SIR, after The Indian Express reported objections recorded by two Election Commissioners.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Business Today reported that the Commission rejected the characterisation of these exchanges as institutional dissent and said final decisions on the SIR were unanimous.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.businesstoday.in/india/story/congress-protests-against-cec-gyanesh-kumar-spread-across-india-gaurav-gogoi-detained-in-guwahati-557894-2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Business Today reported that police detained Assam Congress president and MP Gaurav Gogoi during a protest in Guwahati demanding the Chief Election Commissioner's resignation.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.businesstoday.in/india/story/congress-protests-against-cec-gyanesh-kumar-spread-across-india-gaurav-gogoi-detained-in-guwahati-557894-2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>The Quint</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>The Quint reported that police detained protesters from civil society groups and student organisations at Jantar Mantar, among them CPI(ML) Liberation general secretary Dipankar Bhattacharya, as they demanded the Chief Election Commissioner's resignation and a rollback of the SIR.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.thequint.com/news/jantar-mantar-protest-gyanesh-kumar-resignation-mass-detentions</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ThePrint (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ThePrint, carrying a PTI report, said police detained Uttar Pradesh Congress president Ajay Rai and hundreds of party workers in Lucknow after they were stopped while marching to demand the Chief Election Commissioner's resignation.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/congress-workers-protest-against-cec-in-lucknow-clash-with-police/3053574/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ThePrint (ANI)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ThePrint, carrying an ANI report, said police used water cannons on Congress workers in Patna who were protesting against the Chief Election Commissioner as part of the party's nationwide programme over the SIR.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>The report said the Commission described operational queries and internal feedback as part of the normal functioning of a multi-member body and said all final SIR decisions were unanimous.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://theprint.in/politics/gyanesh-its-done-bro-youth-congress-marches-to-jantar-mantar-water-cannons-in-bihar-punjab/3053510/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ThePrint (ANI)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ThePrint, carrying an ANI report, said police used water cannons on Punjab Congress workers demonstrating in Chandigarh as part of the party's protests over the SIR.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://theprint.in/politics/gyanesh-its-done-bro-youth-congress-marches-to-jantar-mantar-water-cannons-in-bihar-punjab/3053510/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ThePrint (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ThePrint, carrying a PTI report, said the Himachal Pradesh Congress protested outside the Election Commission office in Shimla, burned an effigy of the Chief Election Commissioner and raised slogans against the SIR.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/hp-congress-protests-in-shimla-demands-cec-gyanesh-kumars-removal-arrest/3053573/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Meghalaya</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>UNI</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>UNI reported that Congress workers in Shillong, led by state Congress president Vincent H. Pala, burned an effigy of the Chief Election Commissioner and demanded his removal amid the row over the SIR.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.uniindia.com/east-india/politics-meghalaya-cong-gyanesh-kumar-resignation/192544</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Asianet Newsable</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Asianet Newsable reported that the Uttarakhand Congress marched in Dehradun, surrounded the Election Commission office and burned an effigy of the Chief Election Commissioner. The party raised concerns over how names were added and deleted and how objections were disposed of.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://newsable.asianetnews.com/india/uttarakhand-congress-gheraos-ec-office-demands-cec-s-resignation-articleshow-bgnhevg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ThePrint (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ThePrint, carrying a PTI report, said the Karnataka Congress, with Chief Minister D.K. Shivakumar and former Chief Minister Siddaramaiah, protested at Freedom Park in Bengaluru against the SIR and demanded the Chief Election Commissioner's resignation.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>The Election Commission, however, has asserted that its official orders, decisions and administrative directions have full legal sanction, and that differing views and observations are a normal part of deliberations within any institution.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/karnataka-cong-protests-against-sir-demands-cec-gyanesh-kumars-resignation-2/3054130/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ThePrint (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ThePrint, carrying a PTI report, said police used water cannons and detained former Chief Minister Ashok Gehlot and state Congress chief Govind Singh Dotasra during a march to the State Election Commission office in Jaipur over alleged SIR irregularities.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/gehlot-dotasra-detained-during-cong-protest-in-jaipur-over-sir-row/3055754/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>The South First</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>The South First reported that more than a dozen civil society groups held a day-long protest at Dharna Chowk in Hyderabad, demanding that the SIR be scrapped and the Chief Election Commissioner resign.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://thesouthfirst.com/telangana/attempt-to-kill-democracy-hyderabad-civil-society-protests-sir-demands-cec-gyanesh-kumars-resignation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Free Press Journal</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>The Free Press Journal reported that Uddhav Thackeray of the Shiv Sena (UBT) and Raj Thackeray of the MNS led the Virat Garjana Morcha in Mumbai seeking the Chief Election Commissioner's resignation. Raj Thackeray demanded that the SIR in Maharashtra be cancelled.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/garjana-morcha-uddhav-raj-thackeray-lead-protest-seeking-gyanesh-kumars-resignation-scrapping-of-maharashtra-sir</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>The Wire</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>The Wire reported that police stopped an INDIA bloc march from Parliament to the Election Commission, and that opposition MPs held a sit-in at the All India Radio building until police detained Rahul Gandhi and Priyanka Gandhi Vadra that night.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://thewire.in/politics/india-bloc-opposition-parties-march-nirvachan-sadan-election-commission-rahul-gandhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Deccan Herald (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Deccan Herald, carrying a PTI report, said AAP workers and members of other parties protested outside the Delhi Chief Electoral Officer's office demanding the Chief Election Commissioner's resignation over alleged SIR irregularities. It said AAP had earlier protested at Jantar Mantar and India Gate.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/delhi/aap-protests-outside-delhi-ceo-office-over-sir-seeks-gyanesh-kumars-resignation-4173541</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Protests by parties and groups</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>The Tribune</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>The Tribune reported that Delhi leaders of the INDIA bloc marched to the Election Commission office and gave the Delhi Chief Electoral Officer a memorandum demanding that the SIR be cancelled and excluded eligible voters be restored. It said police detained Delhi Congress president Devender Yadav at a separate protest at Jantar Mantar.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/delhi/india-bloc-leaders-march-to-ec-office-in-delhi-seek-rollback-of-sir/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Booth officers' protests</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>The News Minute</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>The News Minute reported that hundreds of booth level officers across Kerala stayed away from SIR work on a strike call after the death of a BLO in Kannur, and that employee and teacher action councils marched to collectorates.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>The News Minute reported that Kerala's Chief Electoral Officer said he had not received any complaints regarding work pressure from BLOs.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.thenewsminute.com/kerala/officers-suicide-blos-across-kerala-boycott-sir-work-citing-deadline-stress</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Booth officers' protests</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Deccan Herald (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Deccan Herald, carrying a PTI report, said the Federation of Revenue Associations of Tamil Nadu began a statewide boycott of SIR work over workload, staff shortages, deadline pressure and poor training.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/tamil-nadu/tamil-nadu-revenue-employees-association-begin-boycott-of-sir-work-3801680</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Booth officers' protests</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Deccan Herald (Press Trust of India)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Deccan Herald, carrying a PTI report, said booth level officers marching under the BLO Adhikar Raksha Committee clashed with police outside the West Bengal Chief Electoral Officer's office in Kolkata over SIR workload.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Deccan Herald reported that Chief Electoral Officer Manoj Agarwal described the BLOs as the "real heroes" of the exercise.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/west-bengal/blos-protest-outside-bengal-ceos-office-over-excessive-work-pressure-ec-calls-them-real-heroes-3808529</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Booth officers' protests</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>The Wire</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>The Wire reported that nearly 250 primary school teachers working as booth level officers stopped work and held a sit-in at a data uploading centre in Ahmedabad, alleging threats and pressure during the SIR.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://thewire.in/government/ahmedabad-250-blos-stage-protest-citing-threats-pressure-abuse-and-late-night-calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Booth officers' protests</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Amar Ujala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Amar Ujala reported that teachers' organisations in Uttar Pradesh, among them the Uttar Pradeshiya Prathmik Shikshak Sangh, objected to the deaths of teachers and staff on SIR duty and demanded jobs and compensation for their families.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/lucknow/up-teachers-organizations-angry-over-the-deaths-of-blos-opened-a-front-the-teacher-made-a-video-saying-2025-12-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-07-05</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported the Commission saying that about 87 per cent of Bihar's 7.96 crore voters had been given semi-filled enumeration forms on the first booth officer visit.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://deccanchronicle.com/nation/bihar-voter-roll-revision-semi-filled-forms-distributed-to-87-voters-1889439</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LiveLaw</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>LiveLaw reported that the Association for Democratic Reforms told the Supreme Court that enumeration forms in Bihar were being uploaded by officials without voters' knowledge or consent. This is ADR's allegation in a court filing.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>LiveLaw reported that ADR filed the rejoinder in reply to the Commission's counter-affidavit.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.livelaw.in/top-stories/bihar-sir-blos-mass-uploading-enumeration-forms-without-voters-knowledge-or-consent-adr-tells-supreme-court-298898</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>National Herald</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>National Herald reported that Trinamool workers stopped a vehicle in Khatra, Bankura said to carry thousands of pre-filled Form 7s, that police seized it and began an inquiry, and that both parties traded allegations over bulk Form 7s on the last day for filing.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>National Herald reported that the BJP alleged its workers were attacked and prevented from filing forms inside government offices.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.nationalheraldindia.com/politics/form-7-flashpoint-bengal-sees-clashes-rival-claims-of-voter-roll-sabotage</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Scroll reported that Rajasthan Congress president Govind Singh Dotasra alleged that computer-printed Form 7s were distributed in every constituency and that booth agents' signatures were forged, and demanded a forensic inquiry. These are the Congress's allegations.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Scroll reported that BJP minister Gautam Dak said a voter proposed for removal gets time to be heard and that the Congress wanted to create a dispute.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://scroll.in/latest/1090094/scroll_in</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Scroll reported that during Assam's Special Revision a booth officer in Karimganj North was handed objections against 133 voters on forms she described as half printed and half handwritten, and that hearings were suspended in three Nagaon constituencies after complaints of fake Form 7s.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Scroll quoted a senior Commission official in Guwahati saying a voter can file any number of objections but that an ERO reviews them individually when one person files more than five.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://scroll.in/article/1090187/scroll_in</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Scroll reported that at least seven people named as objectors on Form 7s in Assam, some of them BJP booth agents and members, said they had not filed the objections.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Scroll quoted BJP MP Kamakhya Prasad Tasa as saying anyone can file objections and that it is for the Election Commission to take a final call.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://scroll.in/article/1090212/bjp-workers-in-assam-say-their-names-used-to-seek-mass-voter-deletion-without-their-knowledge</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that Assam Chief Minister Himanta Biswa Sarma told reporters he had told BJP members to keep filing complaints against people he called 'Miyas' and to fill Form 7s wherever possible during the Special Revision.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/bjp-complaints-against-miyas-practice-politics-of-polarisation-assam-cm-himanta-10498937/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ETV Bharat</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that Bhopal's Collector ordered a probe after a man named as objector on Form 7s in Bhopal South-West denied filing them, and that officials found incorrect or fake objector details in several of the district's 9,037 Form 7s.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ETV Bharat quoted District Election Officer Kaushlendra Vikram Singh saying no one's name would be removed without verification.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/state/fake-objections-filed-to-delete-voter-names-in-bhopal-probe-ordered-enn26013005659</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Frontline</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Frontline reported that Congress general secretary K. C. Venugopal wrote to the Commission on 29 January alleging misuse of Form 7 in several states, and that the Commission said there was no limit on forms per voter but that an ERO must verify when one person files more than five.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Scroll reported on 23 January 2026 that a senior Commission official in Guwahati gave the same rule.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://frontline.thehindu.com/politics/form-seven-voter-deletion-india-election-commission-bjp/article70582295.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Scroll (PTI)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Scroll reported, citing PTI, that after Assam's final roll the Chief Minister said several deletions had been made on complaints filed by BJP workers.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://scroll.in/latest/1090665/scroll_in</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Newslaundry</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Newslaundry reported that the 15,663 Form 7s in Somnath were filed by 269 people, each filing 50 or more, that copies it reviewed had the voter's details printed in English and the objector's details handwritten in Gujarati, and that six of the objectors filed affidavits saying they had not filed them.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Newslaundry reported that the District Election Officer, V. N. Upadhyay, said he had deployed six AEROs to verify the objections and assured that no name would be deleted arbitrarily.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://newslaundry.com/2026/02/11/inside-the-organised-attempt-to-delete-15000-voters-in-gujarats-somnath</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>The Quint</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>The Quint reported that thousands of Form 7s in Alwar were filed in the names of BJP booth agents, several of whom said their signatures were forged, and that no FIR or inquiry had been announced a month later.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>The Quint reported that calls to the District Magistrate and Sub-Divisional Magistrate for comment went unanswered.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.thequint.com/elections/muslim-voters-alwar-rolls-ec-probe-avoidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>National Herald</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>National Herald reported that the Commission wrote to West Bengal's Chief Electoral Officer to send all Form 7 objections to EROs by 16 February and dispose of them by statutory procedure, and that it had taken cognisance of reports of Form 7 records being burnt.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://www.nationalheraldindia.com/politics/form-7-controversy-deepens-strain-on-sir-phase-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Siasat (citing The Indian Express)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Siasat reported, citing The Indian Express, that Form 7s against 544 voters of a Shamli village were found with a booth officer, said to have been already printed with the voters' EPIC numbers, and that the District Magistrate said the forms were fake and the probe found nothing.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DM Arvind Kumar Chauhan ordered a probe and later said that the case “didn’t have any substance.” “We got an investigation done and found nothing,” he added.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.siasat.com/sir-544-muslim-voters-marked-for-deletion-in-up-village-leads-to-one-man-3438394/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Deccan Herald</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Deccan Herald reported that the Gujarat High Court issued notice to the Commission and the state on two petitions seeking a Special Investigation Team inquiry into Form 7 objections filed during the SIR.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Deccan Herald reported that the matter was posted for further hearing on 7 July.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/gujarat/petitions-seek-investigation-into-thousands-of-fake-objection-pleas-during-sir-gujarat-high-court-issues-notice-3996966</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported Hyderabad's District Election Officer R. V. Karnan explaining that booth officers would hand out enumeration forms already printed with each elector's details and photograph, which the elector completes and signs.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/enumeration-form-must-for-draft-electoral-roll-1965489</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported that the Telangana BJP alleged to the Chief Electoral Officer that booth officers in Hyderabad were handing enumeration forms in bulk to AIMIM leaders at party camps and letting them upload filled forms. This is the BJP's allegation.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/bjp-lodges-complaint-against-officials-allegedly-favouring-aimim-1969157</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported that the BJP alleged that some booth officers in Serilingampally uploaded the blank back of enumeration forms to the Commission's app without the voter's details, and asked the Chief Electoral Officer for a probe. This is the BJP's allegation.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/sir-bjp-urges-ceo-to-conduct-probe-into-allegations-1975019</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>The Hindu reported that the Supreme Court agreed to consider an application by Congress MP Tanuj Punia alleging that Form 7 objections in the Uttar Pradesh SIR were filed with false particulars, forged signatures and in the names of people who later denied filing them. The application cited one person filing objections against 32 electors in Hata, Kushinagar, and a UP Congress claim of 700 to 800 objections in four Khalilabad booths.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/uttar-pradesh/form-7-misuse-supreme-court-to-consider-congress-mps-plea-alleging-targeted-deletions-in-up/article71314187.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>The Pioneer</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>The Pioneer reported that an Uttarakhand Congress delegation told the Chief Electoral Officer that one person had filed objections against about 6,400 voters and about 1,200 people had filed more than ten each. These are the Congress's figures.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>The Pioneer reported that CEO V. V. R. C. Purushottam said the revision followed the rules and that observers had been sent to districts with many objections, and that Additional CEO Vijay Kumar Jogdande said an ERO must scrutinise cases where one person seeks to remove more than five names.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://dailypioneer.com/news/uttarakhand-congress-alleges-form-7-misuse-to-delete-voters-during-sir-approaches-ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Newslaundry</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Newslaundry reported that 35 people named as objectors on 1,657 Form 7s in Jhabrera, 31 of them BJP booth agents, said in affidavits that their names, EPIC numbers and signatures had been misused.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Newslaundry quoted the Jhabrera ERO saying the objections were cancelled after those named sought to withdraw them and the voters would not be deleted, and that the Election Commission would not order any investigation and those whose names were misused should file an FIR.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.newslaundry.com/2026/08/28/exclusive-bjp-agents-identities-misused-to-file-mass-objections-against-haridwars-muslim-voters</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported, in a story datelined Hyderabad that does not say whether the figure covers the state or the district, that the Commission had received close to 50,000 Form 7 applications against entries in the draft roll, and that parties at a meeting chaired by Hyderabad's District Election Officer asked for the Form 10 lists by Assembly constituency.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported that officials gave parties the total number of applications at a meeting at the GHMC office but did not share figures by Assembly constituency.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/50000-forms-filed-seeking-deletion-of-votes-1984663</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Newslaundry</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Newslaundry reported from its investigation in Uttarakhand that numerous applications were filed to remove Muslim voters from the rolls, many in the names of people it said were associated with the BJP. It reported that some people named as objectors later filed affidavits saying they had never filed the objections and that their names, EPIC numbers and signatures had been used fraudulently.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://www.newslaundry.com/2026/09/09/uttarakhand-sir-who-is-targeting-muslim-voters</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>The Hindu reported that Form 10 lists published for 21 to 27 September showed four people in Delhi filing more than ten applications a day through the Commission's ECINET portal, which does not enforce the limit of ten a day for booth agents.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>The Hindu reported that the office of Delhi's Chief Electoral Officer did not respond to a request for comment.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/cities/Delhi/party-appointed-blas-bypass-eci-cap-for-10-applications-a-day-through-its-own-portal-for-deletions/article71524945.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>The Hindu reported that as of September 28, 4,000 Form 7 applications seeking deletion of names had been filed in Karnataka, which it said mostly targeted Muslim voters. It reported that ten people filed Form 7s seeking deletion of 1,363 names in Babaleshwar in one day, often on forms with the voters' details already printed and only the objector's name handwritten. Civil society groups and the Karnataka Congress demanded that the Commission lodge criminal complaints.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>V. Anbukumar, CEO, Karnataka, was not available for comment.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/karnataka/civil-society-groups-congress-demand-firs-over-bulk-form-7s-seeking-deletion-of-names/article71524777.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Telangana Today</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Telangana Today reported that the Chief Electoral Officer, C. Sudharshan Reddy, said 28,753 Form 7 applications had been filed in Telangana, about 5,000 of them in Hyderabad, and that forms received in bulk would be examined with special care.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://telanganatoday.com/nearly-29000-form-7-applications-filed-during-telangana-sir</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Siasat</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Siasat reported that the Telangana Congress complained to the Chief Electoral Officer that a BJP booth agent in Musheerabad had filed Form 7 applications against a Congress booth agent and about 30 members of his family, on forms that were printed in advance. This is the Congress's allegation.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Siasat reported that the Congress asked for an investigation to establish the facts, including a forensic examination of whether the forms came from a common source.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.siasat.com/telangana-sir-congress-alleges-vote-deletion-bid-in-musheerabad-3551155/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>The New Indian Express</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>The New Indian Express reported that the Commission wrote to election officials in Bengaluru that bulk Form 7 applications had come to its notice, with allegations that some were not authentic. It reported that the Commission directed Electoral Registration Officers to act against applicants who knowingly make false declarations, after an inquiry under Rule 20 of the Registration of Electors Rules, 1960.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/states/karnataka/2026/Oct/01/karnataka-sir-eci-flags-bulk-form-7-claims-orders-action-against-false-declarations</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>The South First</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>The South First reported that it had seen a Form 7 from a polling station in Aliyabad, in Bahadurpura, with the voter's details printed and the objector's part left blank. The Congress alleged that such forms had been handed to BJP booth agents through the party's constituency in-charges.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>The South First reported that the Chief Electoral Officer, C. Sudharshan Reddy, said at a press briefing that officials would thoroughly verify all Form 7 applications before making any decision.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://thesouthfirst.com/telangana/after-musheerabad-telangana-congress-says-it-found-more-pre-printed-form-7s-aimed-at-deleting-muslim-voters-in-bahadurpura/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Vartha Bharati</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vartha Bharati reported, quoting the Chief Electoral Officer's office, that Karnataka received 8,85,952 Form 6, 4,648 Form 6A, 84,900 Form 7 and 11,78,028 Form 8 applications between 16 June and 1 October, and that 35,60,833 hearings had been held, with 7,82,304 pending.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>The figures are a running count while hearings continue. Karnataka's final roll is due on 27 October 2026.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://english.varthabharati.in/karnataka/karnataka-4343-lakh-sir-notices-delivered-84900-form-7-applications-received-so-far-2279694</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>The News Minute (citing The Hindu)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>The News Minute reported that five FIRs were registered in Belagavi, Bidar and Mysuru over Form 7s alleged to carry false information or forged signatures, and that in Belagavi the voters' details had been filled in beforehand with the objector's name handwritten or blank.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>The News Minute reported that Karnataka CEO V. Anbu Kumar said that although 84,900 Form 7s had been received, no one had been taken off the rolls.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.thenewsminute.com/karnataka/five-firs-filed-across-karnataka-over-alleged-misuse-of-form-7-bjp-threatens-protest</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported, citing Congress sources, that a BJP booth agent brought 15 pre-printed Form 7s to the booth officer at booth 173 in Goshamahal and that the booth officer refused to accept them.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported that the District Election Officer had reportedly directed the Musheerabad ERO to file criminal cases against the booth agent there.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/sir-15-pre-printed-form-7-now-appear-in-goshamahal-constituency-1993058</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>The News Minute</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>The News Minute reported that AIMIM president Asaduddin Owaisi alleged that Form 7s were being filed to remove Muslim voters and warned of protests, and that Congress leaders said the pre-printed forms found in Goshamahal and Bahadurpura were unsigned and were not accepted by booth officers.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://www.thenewsminute.com/telangana/owaisi-says-hyderabad-will-see-massive-protests-if-eci-doesnt-act-on-form-7-misuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>The News Minute</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>The News Minute reported that Karnataka BJP leaders asked the state police chief to review the FIRs against party workers, saying filing several Form 7s is not by itself a crime and the rules set no limit on their number.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>The News Minute reported that Deputy Chief Minister G. Parameshwara said ministers had gone to the CEO's office to submit a memorandum.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://www.thenewsminute.com/karnataka/karnataka-bjp-leaders-meet-dgp-seek-review-of-firs-over-form-7-filings</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Siasat (PTI)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Siasat reported, citing PTI, that Hyderabad's District Election Officer R. V. Karnan said the Form 7s in Goshamahal and Musheerabad were not received in bulk and were rejected, the Goshamahal forms because they were unsigned and the Musheerabad ones because the electors were found living at the address.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Siasat reported that BJP state president N. Ramchander Rao said no BJP booth agents had submitted any such Form 7 applications, and that the Chief Electoral Officer had said bulk forms from a party had to be properly enquired into and verified.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://www.siasat.com/contested-form-7s-rejected-no-bulk-filings-telangana-deo-3552749/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>The News Minute</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>The News Minute quoted a memo of 5 October in which the Chief Electoral Officer, C. Sudharshan Reddy, told District Election Officers that bulk Form 7 applications had been filed and that EROs should act under Section 31 of the Representation of the People Act against anyone who knowingly made a false declaration.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Siasat reported that the CEO said this action would follow an inquiry. The memo itself was not found on the CEO Telangana website.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.thenewsminute.com/telangana/telangana-sir-congress-seeks-sit-probe-into-alleged-form-7-misuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>The South First</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>The South First reported that the Telangana Congress asked the Hyderabad Police Commissioner to register an FIR and set up a Special Investigation Team over pre-filled Form 7s in three constituencies, and to examine the BJP's role. These are the Congress's allegations.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>The South First reported that the Congress said the Police Commissioner had assured it he would study the matter and take action.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://thesouthfirst.com/telangana/sir-telangana-ceo-orders-action-over-bulk-form-7-filings-congress-seeks-sit-probe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle (ANI)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported that Asaduddin Owaisi alleged that pre-printed Form 7s seeking the deletion of 122 electors, all Muslim, were submitted at booth 28 in Goshamahal in the name of a BJP supporter, and that the booth officer refused them. This is AIMIM's allegation.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Siasat reported on 5 October, citing PTI, that BJP state president N. Ramchander Rao said no BJP booth agents had submitted any such Form 7 applications.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/goshamahal-voter-deletion-row-owaisi-seeks-eci-action-1993544</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Telangana Today</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Telangana Today reported that Chikkadpally police were checking the forms, signatures and voter details in the Musheerabad case and whether similar forms were filed elsewhere, and that the forms had reportedly been rejected.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://telanganatoday.com/police-probe-fake-form-7-applications-seeking-deletion-of-31-voters-in-musheerabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Form 7 objections and pre-printed forms</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported that the Musheerabad ERO filed a police complaint, and Chikkadpally police registered a case, against a BJP booth agent who tried to submit 30 pre-printed Form 7s, the first such case in Telangana.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported that the Congress welcomed the case and asked the police to find who printed and supplied the forms.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/first-fir-related-to-form-7-1993718</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Election Commission of India (PIB)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>The Commission announced in May 2025 that it was building ECINET, one platform to bring together more than 40 of its apps and websites for voters, election officials and other users.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126682</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Supreme Court of India</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>The Supreme Court recorded, from the documents before it, what the logical discrepancy category in West Bengal covered and that about 1.36 crore voters fell in it.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_30_67603_Order_19-Jan-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Election Commission of India (PIB)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>The Commission launched ECINET formally on 22 January 2026 and said its trial version had already been used during the Bihar election and the SIR.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2217429</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Meghalaya</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Chief Electoral Officer, Meghalaya</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Meghalaya's Chief Electoral Officer listed six checks that ECINET used to flag mapping discrepancies in the third phase, among them a sibling age gap under nine months.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://meghalaya.gov.in/sites/default/files/press_release/EL_63_2026_50.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Election Commission of India (PIB)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>After its full meeting on 26 September 2026 the Commission said field officers have access to ECINET by role, set up a committee with an independent expert to check ECINET against the law, and said new IT modules would first go to a committee of officers.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2315309&amp;reg=3&amp;lang=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Free Press Journal</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Booth officers in Bhopal told the Free Press Journal they were asked to upload 100 forms a day and could not, because the booth officers' app server was down or very slow.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/bhopal/mp-special-intensive-revision-100-forms-a-day-blos-complain-of-impossible-targets-voters-cant-find-old-records</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>West Bengal; Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported, from internal Commission records it acquired, that the Commission's software initially flagged 1.31 crore voters in West Bengal and 2.35 crore in Madhya Pradesh for logical discrepancies, and that officials had no written instructions on how to resolve them. It reported that no criteria for deciding which flagged voters to summon had been made public.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>The Collective said the Commission did not answer its question on how flagged voters were chosen, and that questions sent to the Commission and three state offices on testing and procedure went unanswered.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/ecis-software-branded-3-66-crore-voters-as-suspects</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that on 29 December 2025 the West Bengal Chief Electoral Officer's office told state officials in writing that the logical discrepancy software was faulty because the 2002 roll had not been digitised accurately.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>The Collective said the Commission and the West Bengal Chief Electoral Officer did not reply to its questions on the WhatsApp instructions.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/ecis-top-wb-officer-sent-orders-to-state-officials-on-whatsapp</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Siasat (IANS, citing officials of the Chief Electoral Officer, West Bengal)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Officials of West Bengal's Chief Electoral Officer told IANS that the logical discrepancy check caught people who had falsely linked themselves to unrelated voters, and gave examples they said were found at hearings.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://www.siasat.com/west-bengal-sir-eci-explains-why-logical-discrepancy-cases-are-high-3328210/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>The New Indian Express</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>The New Indian Express reported that the Android version of the booth officers' app was updated 31 times between 13 November 2025 and 20 January 2026, with no user manual for the updates, and that officials relied on the app to learn what the revision allowed.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Jan/24/blo-app-underwent-30-changes-in-two-months-in-tamil-nadu</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>The New Indian Express</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>The same report quoted a Chennai booth officer who said the app often froze on her phone, so that data was lost or finished work had to be done again.</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Jan/24/blo-app-underwent-30-changes-in-two-months-in-tamil-nadu</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that hearing notices in West Bengal were generated in bulk by the Commission's software for logical discrepancies, and that two EROs it spoke to, with a few deputies, were signing 4,000 to 5,000 printed notices each day. It reported that the software transliterated names from Bengali into English before matching, so that spellings such as Xalxo and Khalkho triggered a discrepancy. The Collective said this showed the Commission had misled the Supreme Court, where it said there was no automated generation of notices.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>The Collective said the Commission had not responded by publication. It set its finding against the Commission's submission to the Court that "There is no automated generation of notices" and that officers were "signing them off after application of mind".</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/eci-misled-the-sc-on-sir-in-west-bengal</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that in West Bengal the logical discrepancy check flagged five kinds of mismatch, from spelling differences between the Bengali 2002 roll and the English draft to age gaps with parents and grandparents.</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>The Collective said it sent detailed questions to the Commission and had no answer by publication.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that a registration officer showed its reporter that the button to clear voters with a name mismatch had disappeared from ERONET since that morning, so such cases now needed the district officer's approval.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>The Collective said it sent detailed questions to the Commission and had no answer by publication.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that the online Form 6 on the Commission's ECINET portal carried a new declaration asking whether the applicant or their parents or grandparents were in the electoral roll of the last SIR, although the statutory form had not been amended. It reported that the section was not marked mandatory but applicants could not proceed to submission without completing it, and that the downloadable Form 6 on the same portal did not include it.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>The EC did not respond to a request for comment and Legislative Department Secretary Rajiv Mani could not be reached despite repeated attempts.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/election-commission-changes-form-6-for-new-voters-inserts-section-asking-them-about-parents-in-sir-10782435/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>The Hindu reported that 13 days into the Karnataka SIR only 0.41% of enumeration forms had been submitted online, and that voters complained of captcha failures, server errors and an ECINet search that failed to find records appearing in the published rolls. It reported that online submission required a current mobile number linked to the voter's EPIC.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Karnataka Chief Electoral Officer V. Anbu Kumar said the process was still under way. However, the CEO did not comment on the technical glitches reported by voters.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/cities/bangalore/sir-not-even-05-submit-enumeration-forms-online-amid-website-glitches/article71214116.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Deccan Chronicle reported that people filling in enumeration forms on ECINET in Telangana kept being sent back to the home page, and an official put it down to the load from voters in more than a dozen states at once.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/sir-ecinet-portal-faces-peak-hour-glitches-1973124</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>The Indian Express reported, from internal records it investigated, that on May 16 Election Commissioner Vivek Joshi recorded that Form 6 is prescribed by statute and cannot be altered without amending the Registration of Electors Rules, 1960, and that Commissioner Sukhbir Singh Sandhu concurred on May 19. It reported that the declaration was added to the online form anyway, and that on August 13 Sandhu wrote that the changes were unauthorised and illegal and must be removed immediately.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/express-exclusive/election-commission-illegal-changes-form-6-gyanesh-kumar-10889714/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that Election Commissioners Sukhbir Singh Sandhu and Vivek Joshi warned on file, from November 2025 to August 2026, that control of the electoral roll software was being centralised in the Commission's IT division. It reported that on August 14 Sandhu wrote that many Chief Electoral Officers, District Election Officers and Electoral Registration Officers had told him they lacked proper and complete access to ERONet, and that on July 29 both Commissioners wrote separately to the Cabinet Secretary about a change in work allocation.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>The Election Commission and the two ECs, Sandhu and Joshi, did not respond to calls and questionnaires emailed by The Indian Express seeking comment.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/express-exclusive/election-commission-special-intensive-revision-sir-electoral-roll-centralisation-eci-ecinet-10889738/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>The Hindu reported that up to 11 categories of logical discrepancy were being applied in the third phase of the SIR, up from four when the concept was introduced in West Bengal. They include a sibling age gap of nine months or less, which flagged a Delhi resident's twin children, and a marital mapping mismatch where a woman is linked to her father in the old roll and her husband in the new. It reported that the term has never been clearly defined in any official communication.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/the-many-categories-of-sirs-logical-discrepancy-list-keep-voters-on-toes/article71504625.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that Goa's Electoral Registration Officers heard electors flagged for logical discrepancies and found 97 of them eligible, but could not reverse the earlier decisions on ECINET because the permission was controlled from Delhi. It reported that the Goa Chief Electoral Officer's office wrote eight times in seven days asking for a rollback option, and that all 97 were missing from the final roll published on February 21 and were still missing on September 20.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Goa's Chief Electoral Officer, Sanjay Goel, told the paper the decision not to include them was the Commission's. The Indian Express later reported that the Commission said, after its meeting of 26 September, that 81 of the 97 had filled Form 6 and that the Chief Electoral Officer had been told to help include them.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/express-exclusive/election-commission-goa-sir-voter-deletion-ecinet-10891422/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>The Pioneer</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Commission officials said ECINET is decentralised, that each field officer acts through their own login, and that nobody at headquarters can perform those officers' statutory functions. ERONET is now part of ECINET.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://dailypioneer.com/news/ecinet-is-decentralised-only-designated-officials-have-access-says-eci</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>The Hindu reported that more than 350 Delhi electors had been marked ineligible within a month of hearings, about 200 of them in Vikaspuri, and officials said the marking could not be rolled back by the registration officer or the state's Chief Electoral Officer.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>The Delhi Chief Electoral Officer wrote to officers on 25 September 2026 setting a 10-point checklist before marking anyone ineligible and telling them not to delete names on flimsy or frivolous grounds.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/cities/Delhi/delhi-sir-over-350names-already-marked-ineligible-ceo-warns-against-deletion-on-flimsy-grounds/article71513195.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Outlook India (citing NDTV)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Outlook, citing NDTV, reported that Maharashtra's Chief Electoral Officer S Chockalingam asked for four changes to the ECINET software and more discretion for registration officers in logical discrepancy cases.</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>The Commission said on 26 September that several portal upgrades had already been made on inputs from state Chief Electoral Officers and that further flexibility needed by field officers would be made operational.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://www.outlookindia.com/national/maharashtra-poll-chief-seeks-more-ero-powers-as-ecinet-faces-scrutiny-over-sir</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that on the night of 29 to 30 September 2026 the Commission removed the SIR declaration from the online Form 6 on ECINET for states where the final SIR rolls have been published. It reported that the declaration remained for states where the SIR is still ongoing.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>The article cites the Commission's September 26 announcement that ‘for non-SIR period, the Forms applicable as per Rules (the Registration of Electors Rules 1960) will be used’.</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/election-commission-removes-sir-declaration-form-6-ecinet-portal-investigation-gyanesh-kumar-10899952/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>ThePrint (PTI)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Congress general secretary Jairam Ramesh alleged that by restricting registration officers' access to the ECINet roll system and overruling them in Goa, West Bengal and other states, the Commission broke the Representation of the People Act, 1950.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>PTI recalled that the Commission, under fire over objections from two of its Commissioners, had said differing views are a normal part of deliberation and that all its orders carry full legal sanction and follow established statutory procedures.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/cong-accuses-ec-of-lying-about-ecinet-calls-for-accountability/3059961/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>The Indian Express reported a letter of 29 September from the Commission’s Secretary ordering a special drive to enrol "left out and young/first time eligible electors" in the 20 states and union territories where the revision is complete, using the statutory Form 6, with the added declaration kept for the revision phase only. It reported that at a video conference with all Chief Electoral Officers, the states were told to compare the roll from before the revision with the one after, list those removed, visit them at home and help those left out fill in Form 6, with help from the parties’ booth agents.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>The letter itself was not found. The Commission’s press note of 26 September, in the timeline above, had already ordered the drive, and Uttarakhand’s Chief Electoral Officer set out its steps in a press note of 3 October.</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/election-commission-of-india-sir-left-out-voters-special-drive-10903082/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>The Hindu reported that the options reached Delhi officers on 30 September and only the ten states and union territories where the third phase was still under way, and that a case marked ineligible still could not be reversed.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>The Delhi CEO’s office and the EC did not respond to queries on why the options were introduced at this stage.</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/ec-explains-new-eronet-options-for-sir-notice-disposal-to-eros-through-demo-video-no-written-instructions-yet/article71543373.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that at a meeting on 11 August 2026 more than a dozen West Bengal appeal tribunal judges recorded that the Commission's portal did not let them serve notices, hold virtual hearings, restore a deleted voter or give appellants a copy of the order.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>The paper said it emailed the Commission and the Registrar General of the Calcutta High Court on 1 October and received no response.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/bengal-sir-tribunals-election-commission-portal-issues-deleted-voters-10908185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Hindustan Times reported that a security researcher emailed CERT-In on 8 July 2026, copied to the Commission's complaints address, about flaws in the voter-services website and the ECINET app. The worst, in the researcher's account, let anyone obtain election officials' names and mobile numbers without logging in.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>HT said neither CERT-In nor the Commission answered its questions of 5 October. On 6 October CERT-In told the researcher that one flaw, the hardcoded encryption key he rated least serious, had been fixed and that work on the rest was under progress. HT said none of the flaws related directly to registration officers' access to the roll, and that the email alleged no theft or misuse of data.</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/ecinet-flaws-were-flagged-to-poll-body-eci-cyber-security-agency-cert-in-in-july-says-researcher-101791401749277.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Congress alleged after the Hindustan Times report that ECINET was designed to centralise deletions and additions from the BJP's headquarters. This is a party's allegation. Hindustan Times had said none of the flaws it reported related directly to registration officers' access to the roll.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Scroll did not report a response from the Commission to this allegation.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://scroll.in/latest/1096252/ec-online-portal-designed-to-centralise-voter-deletions-from-bjp-headquarters-congress-alleges</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that West Bengal's Chief Electoral Officer sent instructions on a WhatsApp group of district magistrates that brought forward the enumeration deadline and asked officers to mark voters absent before the written deadline. The Trinamool Congress had first made the allegation before the Supreme Court.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>The Collective said the Commission and the West Bengal Chief Electoral Officer did not reply to its questions on the WhatsApp instructions.</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/ecis-top-wb-officer-sent-orders-to-state-officials-on-whatsapp</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that district magistrates of at least three West Bengal districts wrote to the state election office asking for a written procedure for logical discrepancy cases, and that the portal accepted only the 12 listed documents.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>The Collective reported that the officers received no response and carried on with their own methods.</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>A registration officer told The Reporters' Collective that officers were told orally to ask unmapped electors for a second document besides Aadhaar, and that the software for a time would not accept Aadhaar alone. The Collective said it could not check this claim.</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>The New Indian Express (PTI)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>PTI reported that the Commission's written instructions of 14 May 2026 for the third phase told registration officers to refer suspected foreign nationals to the authority under the Citizenship Act.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/india/2026/Jun/07/sir-ec-state-poll-machinery-to-share-details-of-suspected-foreigners-with-authorities-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>A Delhi registration officer told The Hindu that officers were first told to identify suspected foreigners during enumeration and later told in the middle of it to stop, and that many oral instructions had been taken back.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>The Delhi CEO's office and the EC did not respond to The Hindu's queries on why the new ERONET options were introduced at that stage.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/ec-explains-new-eronet-options-for-sir-notice-disposal-to-eros-through-demo-video-no-written-instructions-yet/article71543373.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>The Hindu reported that new ERONET options letting registration officers clear notice cases without a hearing or documents were explained only through an eight-minute video from the Commission's IT department, with no written instruction.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>The Delhi CEO’s office and the EC did not respond to queries on why the options were introduced at this stage.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/ec-explains-new-eronet-options-for-sir-notice-disposal-to-eros-through-demo-video-no-written-instructions-yet/article71543373.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>BBC News</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>The BBC reported that voters in villages near Patna told it the Bihar draft roll carried wrong photographs, duplicate entries and the name of a person who died more than five years earlier. It reported that in Danara village many residents were not sure officials had visited their homes.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>In response to the BBC's questions, the Election Commission shared its 24 June order on conducting the SIR and a 27 July press note outlining efforts to ensure no eligible voter was "left behind". "Further, [the commission] does not take any responsibility of any other misinformation or unsubstantiated allegations being floated around by some vested interests," it added. The BBC also noted the commission has said BLOs worked "very responsibly".</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/news/articles/c3wnx7689l5o</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>The Wire</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>The Wire reported that Mintu Paswan of Ara, Bhojpur, who had been declared dead in the Bihar draft roll, appeared alive in the Supreme Court on 12 August 2025, produced by petitioner Yogendra Yadav. Paswan told The Wire he had filled the enumeration form and that the BLO came to his house only after he complained.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Senior advocate Rakesh Dwivedi, for the Commission, called the production of Paswan "drama". The bench of Justices Surya Kant and Joymalya Bagchi said there may have been an "inadvertent error", which could be rectified.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://m.thewire.in/article/government/declared-dead-in-draft-electoral-roll-bihar-voter-appears-in-supreme-court</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Scroll reported that its analysis found 200 booths across 58 constituencies in 26 Bihar districts where between 324 and 641 names were deleted from the draft roll, 77,454 in all. It reported that most deleted voters its team met in 10 of those booths had been marked absent or shifted though they had lived at their addresses for years, and that interviews with 17 BLOs showed no consistent procedure for deciding deletions.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Parth Gupta, electoral registration officer for Purnia, acknowledged that Jhurana Das should not have been asked for her parents' documents, and said, “Please provide her details and I will look into it.” Scroll also reported that Election Commission spokespersons and Bihar Chief Electoral Officer Vinod Singh Gunjiyal did not respond to requests for comment.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://scroll.in/article/1086533/how-booth-level-officers-in-bihar-are-deleting-voters-arbitrarily</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that a top Commission official and four Bihar EROs confirmed to it that the Commission did not run its de-duplication software during the Bihar SIR and did not give state officials access to it. It quoted the official saying the focus was on document collection. It reported that its own earlier analysis of the final roll found 14.35 lakh suspect duplicate entries.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>The Collective said the Commission and Bihar's Chief Electoral Officer did not answer its emailed questions. In person, the Chief Electoral Officer told its reporter "We cannot share this information with you" and said the Supreme Court was hearing the matter.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/eci-skipped-its-fraud-busting-software-lakhs-of-duplicates</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Newslaundry</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Newslaundry reported that several voters in Delhi's Okhla constituency whose names were removed before the SIR began said they got no notice or hearing and learnt of the deletion only when they tried to take part in the SIR. It reported that 34,644 names were deleted in Okhla during the 2026 mapping phase, against 9,170 in all of 2025.</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Delhi Chief Electoral Officer Ashok Kumar said that no voter had been deleted without an inquiry and an opportunity for a hearing.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://www.newslaundry.com/2026/09/24/i-didnt-know-my-name-was-deleted-voters-in-okhla-on-the-pre-sir-clean-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Deaths reported during the revision</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Kerala; Rajasthan; Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>The Indian Express reported the deaths of two BLOs. The family of Aneesh George in Kannur, Kerala, alleged he was under pressure to finish by December 4, and police said a note found on Mukesh Jangid in Jaipur said he faced extreme pressure from his supervisor and was told he would be suspended if he did not meet his SIR target. It also reported that revenue employees in Tamil Nadu announced a statewide boycott of SIR work over workload.</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Kannur District Collector Arun K Vijayan's report indicated that the BLO was not under any work pressure. The Indian Express said its multiple calls and messages to Rajasthan CEO Naveen got no response.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/two-suicides-blo-protests-threaten-to-disrupt-sir-in-tamil-nadu-kerala-rajasthan-10371492/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Deaths reported during the revision</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that two women assistant BLOs died of heart attacks in Tapi and Vadodara districts, bringing BLO deaths in Gujarat that week to four. The husband of one, Usha Solanki, said she was a heart patient who had asked to be excused from BLO duty, which the Vadodara Collector disputed.</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Vadodara District Collector Anil Dhameliya said, “We checked with the institute as well as with the local officials. She had not made any official request to be excused (from BLO duty)… We have learnt now that she was suffering from a heart ailment and had episodes of fainting in her institute as well.” He also said, “We have been cautious about ensuring that there is no excessive workload on the BLOs and therefore, we have appointed additional staff to assist in the process.” An unnamed government official said, “With a large workforce of over two lakh involved in the SIR work, these deaths can be termed as natural. Linking these to SIR is not justified and logical.”</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/ahmedabad/blo-deaths-gujarat-sir-work-pressure-10380699/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Deaths reported during the revision</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>BBC News</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>The BBC reported that 10 BLOs it spoke to in Uttar Pradesh and West Bengal said they worked 14 to 15 hours a day with little rest, and that families linked the deaths of more than a dozen poll workers, by alleged suicide or heart attack, to election work stress. The BBC said it had not independently verified the causes of death. It reported BLOs saying the SIR app crashed often and that many had not been paid.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>The BBC said the Commission did not answer its questions. It cited media reports of a court affidavit in which the Commission called claims linking booth officers' deaths to the revision "false, exaggerated and politically motivated".</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/news/articles/cy7v05exgdvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Deaths reported during the revision</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that Kanchan Kumar Mondal, 75, died of cardiac arrest, according to hospital sources, after falling ill in a queue for an SIR hearing at the Rampurhat-1 block office in Birbhum. His wife and family alleged the SIR process had caused him excessive stress and held the Election Commission responsible. It also reported that Madan Ghosh died of cardiac arrest at an SIR hearing in Howrah the previous day.</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/kolkata/elderly-man-dies-cardiac-arrest-sir-hearing-kin-allege-stress-10466884/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Deaths reported during the revision</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>The New Indian Express (citing PTI)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>The New Indian Express, citing PTI, reported that police in Purulia registered an FIR on a complaint by the son of Durjan Majhi, 82, who died allegedly by suicide on 29 December hours before he was due at an SIR hearing. An officer was quoted as saying the case included charges of abetment of suicide and criminal conspiracy against Election Commission officials, with no official named. The family alleged he acted out of anxiety over the SIR.</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/india/2026/Jan/21/fir-against-eci-in-west-bengal-over-alleged-suicide-of-elderly-man-due-to-sir-anxiety</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -47910,13 +54035,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C185"/>
+  <dimension ref="A1:C193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -50851,136 +56976,136 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>Protests and disputes</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>section</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>The state, one of the four that published their rolls by constituency (Tamil Nadu, Kerala, West Bengal and Uttarakhand).</t>
+          <t>The section of the disputes page the item sits in, such as the courts, Form 7 objections or changes to the software.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>Protests and disputes</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>The assembly constituency number.</t>
+          <t>The date of the order, resolution or report, as the source gives it.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>Protests and disputes</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>constituency</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>The assembly constituency's name.</t>
+          <t>The state or union territory the item concerns, or India for the revision as a whole.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>Protests and disputes</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>The district the constituency lies in.</t>
+          <t>Document when the item quotes the court, the Assembly or the Commission itself, report when it quotes a named press report.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>Protests and disputes</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>earlier_roll</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>The earliest roll in the row, which is the roll of 27 October 2025 worked out as the draft plus the names left off for Tamil Nadu, the January 2025 final roll for Kerala, the 2024 Lok Sabha roll for West Bengal and blank for Uttarakhand.</t>
+          <t>The court, body or outlet the item comes from.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>Protests and disputes</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>left_off_draft</t>
+          <t>what_happened</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Names left off the draft, as a count, given by constituency only in Tamil Nadu.</t>
+          <t>One sentence saying what the source records or reports, attributed to it.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>Protests and disputes</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>commission_reply</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Electors on the draft roll (19 December 2025 in Tamil Nadu, 23 December 2025 in Kerala, 16 December 2025 in West Bengal, July 2026 in Uttarakhand).</t>
+          <t>The Commission's or the official's reply as the same source reported it, where there was one.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>Protests and disputes</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>added_after_draft</t>
+          <t>url</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Claims admitted after the draft, as a count, Uttarakhand only, from the Chief Electoral Officer's PN 63/2026.</t>
+          <t>Address of the source.</t>
         </is>
       </c>
     </row>
@@ -50992,12 +57117,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>removed_after_draft</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Objections admitted after the draft, as a count, Uttarakhand only, from PN 63/2026.</t>
+          <t>The state, one of the four that published their rolls by constituency (Tamil Nadu, Kerala, West Bengal and Uttarakhand).</t>
         </is>
       </c>
     </row>
@@ -51009,12 +57134,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>later_roll</t>
+          <t>ac</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>The latest roll in the row, the final roll of 23 February 2026 in Tamil Nadu, 21 February 2026 in Kerala and 3 October 2026 in Uttarakhand, and the roll at the 2026 nominations in West Bengal.</t>
+          <t>The assembly constituency number.</t>
         </is>
       </c>
     </row>
@@ -51026,12 +57151,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>change_draft_to_later</t>
+          <t>constituency</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>later_roll less draft, a net change that counts new voters added after the draft as well as names put back.</t>
+          <t>The assembly constituency's name.</t>
         </is>
       </c>
     </row>
@@ -51043,12 +57168,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>change_earlier_to_later</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>later_roll less earlier_roll, as a count, which is negative where the roll fell.</t>
+          <t>The district the constituency lies in.</t>
         </is>
       </c>
     </row>
@@ -51060,10 +57185,146 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
+          <t>earlier_roll</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>The earliest roll in the row, which is the roll of 27 October 2025 worked out as the draft plus the names left off for Tamil Nadu, the January 2025 final roll for Kerala, the 2024 Lok Sabha roll for West Bengal and blank for Uttarakhand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>left_off_draft</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Names left off the draft, as a count, given by constituency only in Tamil Nadu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Electors on the draft roll (19 December 2025 in Tamil Nadu, 23 December 2025 in Kerala, 16 December 2025 in West Bengal, July 2026 in Uttarakhand).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>added_after_draft</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Claims admitted after the draft, as a count, Uttarakhand only, from the Chief Electoral Officer's PN 63/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>removed_after_draft</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Objections admitted after the draft, as a count, Uttarakhand only, from PN 63/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>later_roll</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>The latest roll in the row, the final roll of 23 February 2026 in Tamil Nadu, 21 February 2026 in Kerala and 3 October 2026 in Uttarakhand, and the roll at the 2026 nominations in West Bengal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>change_draft_to_later</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>later_roll less draft, a net change that counts new voters added after the draft as well as names put back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>change_earlier_to_later</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>later_roll less earlier_roll, as a count, which is negative where the roll fell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
           <t>change_earlier_to_later_per_100</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>change_earlier_to_later per 100 electors on earlier_roll.</t>
         </is>

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -60787,7 +60787,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>The Chief Electoral Officer's district and constituency tables of the draft, as published by DeshGujarat on 20 December 2025: 5,08,43,436 before; 18,07,278 death, 9,69,662 untraceable or absent, 40,25,553 permanently shifted, 3,81,470 already enrolled and 1,89,364 other. Shifted, absent or other is absent plus shifted plus other.</t>
+          <t>The Chief Electoral Officer's district and constituency tables of the draft, as published by DeshGujarat on 20 December 2025: 5,08,43,436 before. 18,07,278 death, 9,69,662 untraceable or absent, 40,25,553 permanently shifted, 3,81,470 already enrolled and 1,89,364 other. Shifted, absent or other is absent plus shifted plus other.</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -61228,7 +61228,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>The total is the roll before the revision (press note of 16 December 2025) less the draft roll (fact sheet of 21 February 2026), for 199 seats; Anta, which held a by-election, was revised later. The reasons were published only in lakh and sum to 41.79 lakh.</t>
+          <t>The total is the roll before the revision (press note of 16 December 2025) less the draft roll (fact sheet of 21 February 2026), for 199 seats. Anta, which held a by-election, was revised later. The reasons were published only in lakh and sum to 41.79 lakh.</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -63196,7 +63196,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>CEO Uttarakhand press note 2026/36 of 14.07.2026: 79,60,762 on 08.06.2026, 71,33,785 on the draft; absent or shifted 6,33,573, deceased 1,24,173, enrolled at more than one place 61,454, others 7,777. Shifted, absent or other is absent or shifted plus others.</t>
+          <t>CEO Uttarakhand press note 2026/36 of 14.07.2026: 79,60,762 on 08.06.2026, 71,33,785 on the draft. Absent or shifted 6,33,573, deceased 1,24,173, enrolled at more than one place 61,454, others 7,777. Shifted, absent or other is absent or shifted plus others.</t>
         </is>
       </c>
       <c r="Y24" t="n">
@@ -63790,7 +63790,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Only shares of the electorate were reported (absent 22.5%, shifted 4.6%, dead 1.7%, duplicate 0.6%); not converted to counts.</t>
+          <t>Only shares of the electorate were reported (absent 22.5%, shifted 4.6%, dead 1.7%, duplicate 0.6%). Not converted to counts.</t>
         </is>
       </c>
       <c r="AA29" t="n">
@@ -64057,7 +64057,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>CEO Mizoram press note of 4 July 2026: 21,295 dead, 8,333 untraceable, 13,978 shifted, 2,248 already enrolled and 309 others, 46,163 in all; the final press note of 7 September gives 46,162 not received, which is kept as the total.</t>
+          <t>CEO Mizoram press note of 4 July 2026: 21,295 dead, 8,333 untraceable, 13,978 shifted, 2,248 already enrolled and 309 others, 46,163 in all. The final press note of 7 September gives 46,162 not received, which is kept as the total.</t>
         </is>
       </c>
       <c r="AA31" t="n">
@@ -64257,7 +64257,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Draft roll not yet published; rescheduled to 12 December 2026.</t>
+          <t>Draft roll not yet published. Rescheduled to 12 December 2026.</t>
         </is>
       </c>
       <c r="AE33" t="n">
@@ -72623,7 +72623,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Removals by sex from a press analysis that cites no primary source; the draft roll by sex is the Chief Electoral Officer's.</t>
+          <t>Removals by sex from a press analysis that cites no primary source. The draft roll by sex is the Chief Electoral Officer's.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -72823,7 +72823,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Frozen roll and draft roll by sex (general electors); removals add to the total exactly.</t>
+          <t>Frozen roll and draft roll by sex (general electors). Removals add to the total exactly.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -72903,7 +72903,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Before and draft rolls by sex, from the Chief Electoral Officer; removals add to the total exactly.</t>
+          <t>Before and draft rolls by sex, from the Chief Electoral Officer. Removals add to the total exactly.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -72943,7 +72943,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Roll before (15 July 2026) and draft by sex from the official statement reported by PTI; removals by sex are the difference.</t>
+          <t>Roll before (15 July 2026) and draft by sex from the official statement reported by PTI. Removals by sex are the difference.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -22,8 +22,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Women, state by state and distr" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rural, mixed and urban district" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protests and disputes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every constituency in four stat" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTI replies" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every constituency in four stat" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1000,33 +1001,68 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>RTI replies</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Published table</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>application</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Every application under the Right to Information Act about the revision whose reply was published or reported, with what was asked and what came back</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>A list of the applications that were reported. No authority publishes how many were filed. Each answer is what the outlet reported.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>data/india/rti.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>Every constituency in four stat</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Published table</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>constituency</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>738</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Every constituency of Tamil Nadu, Kerala, West Bengal and Uttarakhand in one table</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Each state measures a different thing, named in the state's rows. Nothing is added across states. Only Uttarakhand has gross additions and deletions.</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>data/india/ac_change.csv</t>
         </is>
@@ -28008,6 +28044,744 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>authority</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>applicant</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>filed</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>replied</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>asked</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>rti_section</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>All India</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Election Commission of India</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>a transparency activist, co-convenor of the National Campaign for People's Right to Information</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A copy of any independent appraisal or study on which the Commission decided to begin the SIR across the country in 2025, and the files, notings and records on that decision, with time to inspect them.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>no record held</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>The Times of India reported that the CPIO pointed to the guidelines of 24 June 2025 and said no further information was available, and The News Minute reported that on first appeal the Commission's Principal Secretary wrote that the Commission had not taken any decision on a nationwide SIR in 2025.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>The News Minute</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://www.thenewsminute.com/news/who-decided-on-nationwide-sir-ecs-rti-response-raises-questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>All India</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Election Commission of India</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>My Vote, My Right (a coalition of civil society groups)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>The definition of 'logical discrepancy' in any official document and the number of notices issued to electors in the 10 States and UTs where the SIR was complete.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>no record held</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>The News Minute reported that the Commission said the information was not available with it and might be with the CEOs of the States and UTs.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>The News Minute</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://www.thenewsminute.com/karnataka/eci-has-no-record-of-what-constitutes-logical-discrepancy-in-sir-rti-reply-shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Election Commission of India</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>a transparency activist, co-convenor of the National Campaign for People's Right to Information</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>The order or notification for the 2003 intensive revision of Bihar's rolls and the guidelines for that revision, including the forms and documents required.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>not supplied</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Deccan Herald and The Times of India reported that the CPIO sent only the link to the 2025 SIR guidelines of 24 June 2025 and gave nothing on the 2003 revision.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Deccan Herald</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/election-commission-refuses-to-provide-2003-bihar-sir-order-on-rti-query-3701142</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>All India</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Election Commission of India</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>All files, notings, correspondence, minutes, presentations and drafts on the SIR ordered on 24 June 2025, and a list of the files recording it.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>not supplied</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that the Commission replied with a link to a page of 'comprehensive instructions' dated 14 July 2025 that the outlet could not open, and did not name any file on the decision.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/blog/a-dead-weblink-eci-refuses-to-share-its-records-under-rti-law</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Election Commission of India</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>a Trinamool Congress leader</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>95</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Technical documents on the 'logical discrepancy' module in ERONET used for the West Bengal SIR, its logic and parameters, procurement and testing records, file notings, instructions to EROs, and the number of electors flagged under each sub-category.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>refused</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Deccan Herald (PTI) reported that the Commission held the software questions exempt under Section 8(1)(d), said no module or separate procurement had been made for the West Bengal SIR, and directed the question on flagged electors to the EROs.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8(1)(d)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Deccan Herald (PTI)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/west-bengal/tmcs-saket-gokhale-says-ec-withholding-details-of-sir-software-cites-rti-response-4157888</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>All India</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ministry of Law and Justice, transferred to the Election Commission of India</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Whether the Commission sought the Law Ministry's legal opinion on the SIR and, if so, the full paper trail of files, correspondence, memos, notes and presentations.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>transferred</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that the Ministry said it keeps no record of such advice and transferred the request to the Commission, which replied on 20 August 2025 that it had no information.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/blog/a-dead-weblink-eci-refuses-to-share-its-records-under-rti-law</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CEO Bihar, transferred to the 38 DEOs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>a transparency activist</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>How many times EROs sent speed post notices to absent or shifted electors during the SIR, how many replies they received and how many notices came back undelivered.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>transferred</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that the CEO sent the application to all 38 district election offices and that after eleven months only the Dulhin Bazar subdivision of Patna and the Hajipur district office had replied, the first saying it sent no speed post notices and the second saying electors were marked from the BLOs' door to door survey.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/blog/follow-regulations-during-sir-not-in-bihar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>All India</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Election Commission of India</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>an independent writer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>110</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>File notings on the decision to begin the second phase of the SIR and the minutes of all meetings held on it.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>partly supplied</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>The Wire reported that after a first appeal the Commission supplied two pages of file notings showing the proposal initiated by an Under Secretary on 27 October 2025 and approved the same day, and supplied no minutes of meetings.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>The Wire</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>https://thewire.in/government/if-voter-rolls-were-properly-maintained-would-sir-be-needed-rti-records-tell-the-story</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO West Bengal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>a Congress Member of Parliament from West Bengal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Figures on appeals before the SIR appellate tribunals in West Bengal, received, decided, allowed and rejected, district by district.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>supplied</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>The Wire reported a 28 page reply, Memo No. 8551/Home (Elec), showing that as of 7 August 2026 the tribunals had received 38,10,620 appeals and decided 82,782, of which 75,443 ended in inclusion and 7,339 in exclusion, with a footnote that the total mixes appeals against inclusion and against exclusion.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>The Wire</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>https://thewire.in/rights/rti-reveals-bengal-tribunal-decided-on-just-2-17-sir-appeals-over-37-lakh-still-in-limbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Election Commission of India</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>a petitioner in the Calcutta High Court</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>The circular or notification under which the SIR was carried out in West Bengal and any record the Commission holds on foreign nationals on the roll.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>appeal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that the CPIO gave no information, that the first appellate authority directed disclosure within seven days and warned on 9 February 2026, and that on 18 March 2026 the Calcutta High Court directed the CPIO to supply the information within seven days.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ETV Bharat Bangla</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/bn/state/calcutta-high-court-directs-election-commission-of-india-to-answer-rti-over-sir-circular-in-west-bengal-west-bengal-news-wbs26031805380</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>All India</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Election Commission of India, CEO Delhi, CEO West Bengal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Internet Freedom Foundation</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>The criteria for flagging 'logical discrepancies' and their version history, contracts for ERONET 2.0, ECINET and roll digitisation, Election Commissioners' recorded objections and minutes, data retention and sharing, and State-wise counts of electors excluded, noticed, deleted and restored on appeal.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Internet Freedom Foundation said it had filed the applications and would publish the responses and appeal any refusal.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Internet Freedom Foundation</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>https://internetfreedom.in/iff-filed-rti-applications-seeking-what-the-election-commission-has-not-disclosed-about-the-sir/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -56634,13 +57408,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C197"/>
+  <dimension ref="A1:C211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -59779,7 +60553,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -59789,209 +60563,447 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>The state, one of the four that published their rolls by constituency (Tamil Nadu, Kerala, West Bengal and Uttarakhand).</t>
+          <t>The state the application concerns, or All India for one about the revision as a whole.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>authority</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>The assembly constituency number.</t>
+          <t>The public authority the application went to, such as the Election Commission or a state's Chief Electoral Officer.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>constituency</t>
+          <t>applicant</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>The assembly constituency's name.</t>
+          <t>The organisation that filed it, or the applicant's role. No private person is named.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>filed</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>The district the constituency lies in.</t>
+          <t>The date the application was filed, where it was reported.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>earlier_roll</t>
+          <t>replied</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>The earliest roll in the row, which is the roll of 27 October 2025 worked out as the draft plus the names left off for Tamil Nadu, the January 2025 final roll for Kerala, the 2024 Lok Sabha roll for West Bengal and blank for Uttarakhand.</t>
+          <t>The date of the reply, where it was reported.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>left_off_draft</t>
+          <t>days</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Names left off the draft, as a count, given by constituency only in Tamil Nadu.</t>
+          <t>Days from the application to the reply, where both dates were reported. The Act allows 30.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>asked</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Electors on the draft roll (19 December 2025 in Tamil Nadu, 23 December 2025 in Kerala, 16 December 2025 in West Bengal, July 2026 in Uttarakhand).</t>
+          <t>What the application asked for.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>added_after_draft</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Claims admitted after the draft, as a count, Uttarakhand only, from the Chief Electoral Officer's PN 63/2026.</t>
+          <t>What became of it: no record held, refused, transferred, partly supplied, supplied, appeal, no reply in time or pending.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>removed_after_draft</t>
+          <t>answer</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Objections admitted after the draft, as a count, Uttarakhand only, from PN 63/2026.</t>
+          <t>What the authority said or did, as reported.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>later_roll</t>
+          <t>rti_section</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>The latest roll in the row, the final roll of 23 February 2026 in Tamil Nadu, 21 February 2026 in Kerala and 3 October 2026 in Uttarakhand, and the roll at the 2026 nominations in West Bengal.</t>
+          <t>The section of the Act cited for a refusal, if any.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>change_draft_to_later</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>later_roll less draft, a net change that counts new voters added after the draft as well as names put back.</t>
+          <t>primary if the reply itself was read, press if the item rests on a report.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Every constituency in four stat</t>
+          <t>RTI replies</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>change_earlier_to_later</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>later_roll less earlier_roll, as a count, which is negative where the roll fell.</t>
+          <t>The outlet that published the reply or reported it.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
+          <t>RTI replies</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>The date of that publication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>RTI replies</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>The address of the source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
           <t>Every constituency in four stat</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>The state, one of the four that published their rolls by constituency (Tamil Nadu, Kerala, West Bengal and Uttarakhand).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>The assembly constituency number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>constituency</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>The assembly constituency's name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>The district the constituency lies in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>earlier_roll</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>The earliest roll in the row, which is the roll of 27 October 2025 worked out as the draft plus the names left off for Tamil Nadu, the January 2025 final roll for Kerala, the 2024 Lok Sabha roll for West Bengal and blank for Uttarakhand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>left_off_draft</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Names left off the draft, as a count, given by constituency only in Tamil Nadu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Electors on the draft roll (19 December 2025 in Tamil Nadu, 23 December 2025 in Kerala, 16 December 2025 in West Bengal, July 2026 in Uttarakhand).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>added_after_draft</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Claims admitted after the draft, as a count, Uttarakhand only, from the Chief Electoral Officer's PN 63/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>removed_after_draft</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Objections admitted after the draft, as a count, Uttarakhand only, from PN 63/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>later_roll</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>The latest roll in the row, the final roll of 23 February 2026 in Tamil Nadu, 21 February 2026 in Kerala and 3 October 2026 in Uttarakhand, and the roll at the 2026 nominations in West Bengal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>change_draft_to_later</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>later_roll less draft, a net change that counts new voters added after the draft as well as names put back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>change_earlier_to_later</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>later_roll less earlier_roll, as a count, which is negative where the roll fell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Every constituency in four stat</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
         <is>
           <t>change_earlier_to_later_per_100</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>change_earlier_to_later per 100 electors on earlier_roll.</t>
         </is>

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -63327,13 +63327,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>33800000</v>
+        <v>33826448</v>
       </c>
       <c r="E17" t="n">
         <v>7339235</v>
       </c>
       <c r="F17" t="n">
-        <v>21.71</v>
+        <v>21.7</v>
       </c>
       <c r="G17" t="n">
         <v>922229</v>
@@ -63354,7 +63354,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>rounded</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -63369,7 +63369,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Electors before the revision reported rounded (3.38 crore).</t>
+          <t>Removals and reasons from The Indian Express. The roll before the revision, 3,38,26,448, is from Telangana Today of 9 October 2026, from the Chief Electoral Officer's information, with 2,64,87,213 enumeration forms submitted and 73,39,235 left off (https://telanganatoday.com/telangana-sir-18-12-lakh-voters-face-exclusion-from-final-electoral-list).</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -79507,7 +79507,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>26460765</v>
+        <v>26487213</v>
       </c>
       <c r="D3" t="n">
         <v>9288180</v>

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -21011,7 +21011,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Activists Anjali Bhardwaj and Amrita Johri asked for the list of Delhi voters sent notices and the criteria for logical discrepancies, and the bench told the Commission to look at extra safeguards, ThePrint reported.</t>
+          <t>Two transparency activists who had petitioned the Court asked for the list of Delhi voters sent notices and the criteria for logical discrepancies, and the bench told the Commission to look at extra safeguards, ThePrint reported.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -24646,22 +24646,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Chatra; West Singhbhum; Deoghar</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Jharkhand</t>
+          <t>Election Commission; Electoral Registration Officer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Form 7; Form 8</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -24671,22 +24671,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>The Wire</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Of 13,443 Form 7 applications for deletion in Jharkhand, 4,790 came from the Chatra Assembly seat, about 36% of the state's total, in figures the Chief Electoral Officer released on 1 October, The Wire reported, citing the Hindustan Times. West Singhbhum had 1,906 and Deoghar 1,099.</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>The Wire reported that the Chief Electoral Officer said the Chatra figures were checked with the district administration and no bulk applications beyond the limit were found, and that address changes on Form 8 generate Form 7 entries automatically.</t>
+          <t>The New Indian Express reported that the Commission wrote to election officials in Bengaluru that bulk Form 7 applications had come to its notice, with allegations that some were not authentic. It reported that the Commission directed Electoral Registration Officers to act against applicants who knowingly make false declarations, after an inquiry under Rule 20 of the Registration of Electors Rules, 1960.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/rights/sir-single-jharkhand-assembly-constituency-accounts-for-over-a-third-of-voter-deletion-requests</t>
+          <t>https://www.newindianexpress.com/states/karnataka/2026/Oct/01/karnataka-sir-eci-flags-bulk-form-7-claims-orders-action-against-false-declarations</t>
         </is>
       </c>
     </row>
@@ -24698,27 +24693,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hyderabad; Bahadurpura; Aliyabad</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Election Commission; Electoral Registration Officer</t>
+          <t>Congress; BJP; Chief Electoral Officer, Telangana</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Form 7; Police and FIRs</t>
+          <t>Form 7; Pre-printed forms</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -24728,17 +24723,22 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>The South First</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>The New Indian Express reported that the Commission wrote to election officials in Bengaluru that bulk Form 7 applications had come to its notice, with allegations that some were not authentic. It reported that the Commission directed Electoral Registration Officers to act against applicants who knowingly make false declarations, after an inquiry under Rule 20 of the Registration of Electors Rules, 1960.</t>
+          <t>The South First reported that it had seen a Form 7 from a polling station in Aliyabad, in Bahadurpura, with the voter's details printed and the objector's part left blank. The Congress alleged that such forms had been handed to BJP booth agents through the party's constituency in-charges.</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>The South First reported that the Chief Electoral Officer, C. Sudharshan Reddy, said at a press briefing that officials would thoroughly verify all Form 7 applications before making any decision.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/karnataka/2026/Oct/01/karnataka-sir-eci-flags-bulk-form-7-claims-orders-action-against-false-declarations</t>
+          <t>https://thesouthfirst.com/telangana/after-musheerabad-telangana-congress-says-it-found-more-pre-printed-form-7s-aimed-at-deleting-muslim-voters-in-bahadurpura/</t>
         </is>
       </c>
     </row>
@@ -24755,22 +24755,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Hyderabad; Bahadurpura; Aliyabad</t>
+          <t>Chatra; West Singhbhum; Deoghar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Congress; BJP; Chief Electoral Officer, Telangana</t>
+          <t>Chief Electoral Officer, Jharkhand</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms</t>
+          <t>Form 7; Form 8</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -24780,22 +24780,22 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>The South First</t>
+          <t>The Wire</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>The South First reported that it had seen a Form 7 from a polling station in Aliyabad, in Bahadurpura, with the voter's details printed and the objector's part left blank. The Congress alleged that such forms had been handed to BJP booth agents through the party's constituency in-charges.</t>
+          <t>Of 13,443 Form 7 applications for deletion in Jharkhand, 4,790 came from the Chatra Assembly seat, about 36% of the state's total, in figures the Chief Electoral Officer released on 1 October, The Wire reported, citing the Hindustan Times. West Singhbhum had 1,906 and Deoghar 1,099.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>The South First reported that the Chief Electoral Officer, C. Sudharshan Reddy, said at a press briefing that officials would thoroughly verify all Form 7 applications before making any decision.</t>
+          <t>The Wire reported that the Chief Electoral Officer said the Chatra figures were checked with the district administration and no bulk applications beyond the limit were found, and that address changes on Form 8 generate Form 7 entries automatically.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://thesouthfirst.com/telangana/after-musheerabad-telangana-congress-says-it-found-more-pre-printed-form-7s-aimed-at-deleting-muslim-voters-in-bahadurpura/</t>
+          <t>https://m.thewire.in/article/rights/sir-single-jharkhand-assembly-constituency-accounts-for-over-a-third-of-voter-deletion-requests</t>
         </is>
       </c>
     </row>

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -62354,6 +62354,12 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="P9" t="n">
+        <v>343801</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>108807</v>
+      </c>
       <c r="S9" t="n">
         <v>18730914</v>
       </c>
@@ -62629,7 +62635,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>41492</v>
+        <v>42719</v>
       </c>
       <c r="Q11" t="n">
         <v>16619</v>
@@ -72531,7 +72537,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/india/2026/Apr/11/up-final-voter-list-at-1339-crore-after-revision-over-2-crore-names-deleted</t>
+          <t>https://www.instagram.com/p/DXEa2dkEuo7/</t>
         </is>
       </c>
     </row>
@@ -72797,6 +72803,12 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>343801</v>
+      </c>
+      <c r="G9" t="n">
+        <v>108807</v>
+      </c>
       <c r="I9" t="n">
         <v>18730914</v>
       </c>
@@ -72811,12 +72823,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>net only</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/eci-publishes-final-electoral-roll-for-chhattisgarh-total-voters-at-18730914</t>
+          <t>https://ceochhattisgarh.nic.in/assets/pdf%20files/PN21.02.2026FinalPublicationofERollChhattisgarh.pdf</t>
         </is>
       </c>
     </row>
@@ -72890,7 +72902,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>41492</v>
+        <v>42719</v>
       </c>
       <c r="G11" t="n">
         <v>16619</v>
@@ -72909,7 +72921,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -27536,12 +27536,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>The Wire reported that Mintu Paswan of Ara, Bhojpur, who had been declared dead in the Bihar draft roll, appeared alive in the Supreme Court on 12 August 2025, produced by petitioner Yogendra Yadav. Paswan told The Wire he had filled the enumeration form and that the BLO came to his house only after he complained.</t>
+          <t>The Wire reported that a voter from Ara, Bhojpur, who had been declared dead in the Bihar draft roll, appeared alive in the Supreme Court on 12 August 2025, produced by petitioner Yogendra Yadav. The voter told The Wire he had filled the enumeration form and that the BLO came to his house only after he complained.</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Senior advocate Rakesh Dwivedi, for the Commission, called the production of Paswan "drama". The bench of Justices Surya Kant and Joymalya Bagchi said there may have been an "inadvertent error", which could be rectified.</t>
+          <t>Senior advocate Rakesh Dwivedi, for the Commission, called the production of the voter "drama". The bench of Justices Surya Kant and Joymalya Bagchi said there may have been an "inadvertent error", which could be rectified.</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -27598,7 +27598,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Parth Gupta, electoral registration officer for Purnia, acknowledged that Jhurana Das should not have been asked for her parents' documents, and said, “Please provide her details and I will look into it.” Scroll also reported that Election Commission spokespersons and Bihar Chief Electoral Officer Vinod Singh Gunjiyal did not respond to requests for comment.</t>
+          <t>Parth Gupta, electoral registration officer for Purnia, acknowledged that one deleted voter should not have been asked for her parents' documents, and said, “Please provide her details and I will look into it.” Scroll also reported that Election Commission spokespersons and Bihar Chief Electoral Officer Vinod Singh Gunjiyal did not respond to requests for comment.</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>The Indian Express reported the deaths of two BLOs. The family of Aneesh George in Kannur, Kerala, alleged he was under pressure to finish by December 4, and police said a note found on Mukesh Jangid in Jaipur said he faced extreme pressure from his supervisor and was told he would be suspended if he did not meet his SIR target. It also reported that revenue employees in Tamil Nadu announced a statewide boycott of SIR work over workload.</t>
+          <t>The Indian Express reported the deaths of two BLOs. The family of a BLO in Kannur, Kerala, alleged he was under pressure to finish by December 4, and police said a note found on a BLO in Jaipur said he faced extreme pressure from his supervisor and was told he would be suspended if he did not meet his SIR target. It also reported that revenue employees in Tamil Nadu announced a statewide boycott of SIR work over workload.</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -27863,7 +27863,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>The Indian Express reported that two women assistant BLOs died of heart attacks in Tapi and Vadodara districts, bringing BLO deaths in Gujarat that week to four. The husband of one, Usha Solanki, said she was a heart patient who had asked to be excused from BLO duty, which the Vadodara Collector disputed.</t>
+          <t>The Indian Express reported that two women assistant BLOs died of heart attacks in Tapi and Vadodara districts, bringing BLO deaths in Gujarat that week to four. The husband of one said she was a heart patient who had asked to be excused from BLO duty, which the Vadodara Collector disputed.</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>The Indian Express reported that Kanchan Kumar Mondal, 75, died of cardiac arrest, according to hospital sources, after falling ill in a queue for an SIR hearing at the Rampurhat-1 block office in Birbhum. His wife and family alleged the SIR process had caused him excessive stress and held the Election Commission responsible. It also reported that Madan Ghosh died of cardiac arrest at an SIR hearing in Howrah the previous day.</t>
+          <t>The Indian Express reported that a 75-year-old man died of cardiac arrest, according to hospital sources, after falling ill in a queue for an SIR hearing at the Rampurhat-1 block office in Birbhum. His wife and family alleged the SIR process had caused him excessive stress and held the Election Commission responsible. It also reported that an elderly man died of cardiac arrest at an SIR hearing in Howrah the previous day.</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -28024,7 +28024,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>The New Indian Express, citing PTI, reported that police in Purulia registered an FIR on a complaint by the son of Durjan Majhi, 82, who died allegedly by suicide on 29 December hours before he was due at an SIR hearing. An officer was quoted as saying the case included charges of abetment of suicide and criminal conspiracy against Election Commission officials, with no official named. The family alleged he acted out of anxiety over the SIR.</t>
+          <t>The New Indian Express, citing PTI, reported that police in Purulia registered an FIR on a complaint by the son of an 82-year-old man who died allegedly by suicide on 29 December hours before he was due at an SIR hearing. An officer was quoted as saying the case included charges of abetment of suicide and criminal conspiracy against Election Commission officials, with no official named. The family alleged he acted out of anxiety over the SIR.</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -63126,17 +63126,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-draft-electoral-rolls-sir-2-crore-voters-excluded-claims-objections-portal-10857667/</t>
+          <t>https://ceoelection.maharashtra.gov.in/Downloads/PDF/Notification/Press%20Note%20English_31.08.2026%20Draft%20Roll.pdf</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Electors before (9,78,54,049), the draft (7,71,65,562) and the names left off (2,06,88,487) are the Chief Electoral Officer's press note of 31 August 2026, which gives no numbers by reason. The reasons are as reported in lakh by the press and sum 10,513 more than the total. Includes 2.23 lakh "others".</t>
+          <t>Electors before (9,78,54,049), the draft (7,71,65,562) and the names left off (2,06,88,487) are the Chief Electoral Officer's press note of 31 August 2026, which gives no numbers by reason. The reasons are as The Indian Express reported them in lakh, and sum 10,513 more than the total. Includes 2.23 lakh "others".</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -63369,7 +63369,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Removals and reasons from The Indian Express. The roll before the revision, 3,38,26,448, is from Telangana Today of 9 October 2026, from the Chief Electoral Officer's information, with 2,64,87,213 enumeration forms submitted and 73,39,235 left off (https://telanganatoday.com/telangana-sir-18-12-lakh-voters-face-exclusion-from-final-electoral-list).</t>
+          <t>Removals and reasons from The Indian Express. The roll before the revision, 3,38,26,448, is from Telangana Today of 9 October 2026, from the Chief Electoral Officer's information, with 2,64,87,213 enumeration forms submitted and 73,39,235 left off.</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -63464,17 +63464,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/delhi-news/delhi-sir-narrows-gender-gap-as-voter-roll-shrinks-328-101788200888661.html</t>
+          <t>https://ceodelhi.gov.in/PDFFolders/2026/Draft_PublicationSIR31Aug2026.pdf</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>The Chief Electoral Officer's press note of 31 August 2026, quoted to the elector by Hindustan Times and Business Standard. Claims and objections extended to 30 October 2026.</t>
+          <t>The Chief Electoral Officer's press note of 31 August 2026, which Hindustan Times and Business Standard also quoted to the elector. Claims and objections extended to 30 October 2026.</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -73875,7 +73875,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer's statement of the roll before and the draft by sex.</t>
+          <t>The roll before by sex as Hindustan Times quoted the Chief Electoral Officer</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -73975,7 +73975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -74824,29 +74824,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Using its powers under Article 142, and with the parties' consent, the Court gave the deciding of claims and objections about inclusion to judicial officers of West Bengal, helped by judicial officers from Jharkhand and Odisha, acting "for and on behalf of this Court". This account of the order comes from the Court's orders of 2 and 13 April 2026.</t>
+          <t>Using its powers under Article 142, and with the parties' consent, the Court gave the deciding of claims and objections about inclusion to judicial officers of West Bengal, acting "for and on behalf of this Court". This account of the order comes from the Court's orders of 2 and 13 April 2026.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Supreme Court order of 13.04.2026</t>
+          <t>Supreme Court order of 02.04.2026 | Supreme Court order of 13.04.2026</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_53_70166_Order_13-Apr-2026.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2026/19822/19822_2026_1_51_69596_Order_02-Apr-2026.pdf | https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_53_70166_Order_13-Apr-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>State election officer</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -74856,34 +74856,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>West Bengal's final roll, with 60 lakh held back</t>
+          <t>Judges from Jharkhand and Odisha, and no appeal to officials</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>The final roll was published with 60,06,675 names marked "under adjudication". They were to be added by a supplementary list if the judicial officers approved them.</t>
+          <t>A further order set out the work given to the judicial officers and said their orders could not be appealed before any executive or administrative officer. Judicial officers from Odisha and Jharkhand joined those of West Bengal, and by 10 March there were 200 of them beside more than 500 from West Bengal. This account of the order comes from the Court's order of 10 March 2026.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CEO West Bengal, press note CEO/PN-05/2026</t>
+          <t>Supreme Court order of 10.03.2026</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://ceowestbengal.wb.gov.in/Downloads/News/Final%20Press%20Note%20CEO-PN-05-2026.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_42_69352_Order_10-Mar-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>State election officer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -74893,29 +74893,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Appeals go to tribunals</t>
+          <t>West Bengal's final roll, with 60 lakh held back</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>No executive officer could hear an appeal against an order of the judicial officers. Appeals were to go to tribunals of former Chief Justices and judges, which the Commission would notify in consultation with the Chief Justice of the Calcutta High Court.</t>
+          <t>The final roll was published with 60,06,675 names marked "under adjudication". They were to be added by a supplementary list if the judicial officers approved them.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Supreme Court order of 10.03.2026</t>
+          <t>CEO West Bengal, press note CEO/PN-05/2026</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_42_69352_Order_10-Mar-2026.pdf</t>
+          <t>https://ceowestbengal.wb.gov.in/Downloads/News/Final%20Press%20Note%20CEO-PN-05-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -74930,140 +74930,140 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nineteen tribunals</t>
+          <t>Appeals go to tribunals</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nineteen appellate tribunals were at work. Appeals decided by 21 and 27 April were to take effect through a supplementary roll before polling, and a pending appeal gave no right to vote.</t>
+          <t>No executive officer could hear an appeal against an order of the judicial officers. Appeals were to go to tribunals of former Chief Justices and judges, which the Commission would notify in consultation with the Chief Justice of the Calcutta High Court.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Supreme Court order of 13.04.2026</t>
+          <t>Supreme Court order of 10.03.2026</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_53_70166_Order_13-Apr-2026.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_42_69352_Order_10-Mar-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phase III</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The rest of the country</t>
+          <t>Nineteen tribunals</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The revision was ordered in 16 states and 3 union territories, covering the whole country except Himachal Pradesh, Jammu and Kashmir and Ladakh, whose dates would be announced later. Eight separate schedules were set. After the draft, notices would go to those who could not be linked to the last intensive revision (the no-mapping list) and to those whose link showed a discrepancy. Lists of those sent notices were to be published.</t>
+          <t>Nineteen appellate tribunals were at work. Appeals decided by 21 and 27 April were to take effect through a supplementary roll before polling, and a pending appeal gave no right to vote.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ECI press note ECI/PN/086/2026 of 14.05.2026 (PIB) | Copy of the ECI order of 14.05.2026 (district site)</t>
+          <t>Supreme Court order of 13.04.2026</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2260955&amp;reg=3&amp;lang=1 | https://cdn.s3waas.gov.in/s3ffeabd223de0d4eacb9a3e6e53e5448d/uploads/2026/05/17797105172741.pdf</t>
+          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_53_70166_Order_13-Apr-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Phase III</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The Supreme Court upholds the revision</t>
+          <t>The rest of the country</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The Court disposed of the petitions. It held that the revision has its legal basis in section 21(3) of the Representation of the People Act read with Article 324, that it was proportionate, and that its document list, with Aadhaar added, was not arbitrary. The Commission may enquire into citizenship only for electoral purposes and must refer doubtful cases to the competent authority of the Central Government. People domiciled in Bihar whose names were wrongly deleted as absent, dead, shifted or duplicate may seek judicial review.</t>
+          <t>The revision was ordered in 16 states and 3 union territories, covering the whole country except Himachal Pradesh, Jammu and Kashmir and Ladakh, whose dates would be announced later. Eight separate schedules were set. After the draft, notices would go to those who could not be linked to the last intensive revision (the no-mapping list) and to those whose link showed a discrepancy. Lists of those sent notices were to be published.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Supreme Court, judgment of 27.05.2026, 2026 INSC 564</t>
+          <t>ECI press note ECI/PN/086/2026 of 14.05.2026 (PIB) | Copy of the ECI order of 14.05.2026 (district site)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2025/35785/35785_2025_1_1501_71617_Judgement_27-May-2026.pdf</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2260955&amp;reg=3&amp;lang=1 | https://cdn.s3waas.gov.in/s3ffeabd223de0d4eacb9a3e6e53e5448d/uploads/2026/05/17797105172741.pdf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>State election officer</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phase III</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mizoram avoids Sundays</t>
+          <t>The Supreme Court upholds the revision</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>At its Chief Electoral Officer's request, Mizoram's draft moved from Sunday 5 July to 4 July 2026, and its final roll from Sunday 6 September to 7 September.</t>
+          <t>The Court disposed of the petitions. It held that the revision has its legal basis in section 21(3) of the Representation of the People Act read with Article 324, that it was proportionate, and that its document list, with Aadhaar added, was not arbitrary. The Commission may enquire into citizenship only for electoral purposes and must refer doubtful cases to the competent authority of the Central Government. People domiciled in Bihar whose names were wrongly deleted as absent, dead, shifted or duplicate may seek judicial review.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CEO Mizoram press note of 04.07.2026 | CEO Mizoram press releases</t>
+          <t>Supreme Court, judgment of 27.05.2026, 2026 INSC 564</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://ceo.mizoram.gov.in/storage/press-releases/July_2026/01KWPBBZRST6PJEWCKV628GVGK.pdf | https://ceo.mizoram.gov.in/show-all-data/press-release</t>
+          <t>https://api.sci.gov.in/supremecourt/2025/35785/35785_2025_1_1501_71617_Judgement_27-May-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -75078,29 +75078,29 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Karnataka three weeks later</t>
+          <t>Mizoram avoids Sundays</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Karnataka's draft came out on 24 August 2026 instead of 5 August. Enumeration ran to 17 August, claims to 23 September, and the final roll is due on 27 October instead of 7 October.</t>
+          <t>At its Chief Electoral Officer's request, Mizoram's draft moved from Sunday 5 July to 4 July 2026, and its final roll from Sunday 6 September to 7 September.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CEO Karnataka press note of 24.08.2026</t>
+          <t>CEO Mizoram press note of 04.07.2026 | CEO Mizoram press releases</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://ceo.karnataka.gov.in/uploads/PRESS%20NOTE%2024th%20Aug.pdf</t>
+          <t>https://ceo.mizoram.gov.in/storage/press-releases/July_2026/01KWPBBZRST6PJEWCKV628GVGK.pdf | https://ceo.mizoram.gov.in/show-all-data/press-release</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -75115,34 +75115,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Maharashtra four weeks later</t>
+          <t>Karnataka three weeks later</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maharashtra's draft came out on 31 August 2026 instead of 5 August. Claims run to 30 September, and the final roll is due on 4 November instead of 7 October.</t>
+          <t>Karnataka's draft came out on 24 August 2026 instead of 5 August. Enumeration ran to 17 August, claims to 23 September, and the final roll is due on 27 October instead of 7 October.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CEO Maharashtra press note of 31.08.2026</t>
+          <t>CEO Karnataka press note of 24.08.2026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://ceoelection.maharashtra.gov.in/Downloads/PDF/Notification/Press%20Note%20English_31.08.2026%20Draft%20Roll.pdf</t>
+          <t>https://ceo.karnataka.gov.in/uploads/PRESS%20NOTE%2024th%20Aug.pdf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>State election officer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -75152,29 +75152,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Documents at the door, and a drive for those left off</t>
+          <t>Maharashtra four weeks later</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>For people sent notices as unmapped or for logical discrepancies, BLOs would collect documents at home and upload them for the registration officer, so these people need not come to the office. A hearing would be held only in exceptional cases, as the registration officer decides, preferably online, and a family member authorised by the elector could attend. The Commission said the declaration attached to Form 6 for the revision had been upheld by the Supreme Court, and that outside the revision the forms in the Registration of Electors Rules, 1960 apply. Claims were extended in Delhi to 30 October and in Maharashtra to 12 October 2026. Where the revision was complete, in 20 states and union territories, anyone left out during it or after, and any young or first-time voter, could ask the registration officer to be added under continuous updation, and the Chief Electoral Officers, district officers and registration officers were to launch a special drive at once to enrol them.</t>
+          <t>Maharashtra's draft came out on 31 August 2026 instead of 5 August. Claims run to 30 September, and the final roll is due on 4 November instead of 7 October.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ECI press note ECI/PN/120/2026 of 26.09.2026 | ECI press release of 26.09.2026 (PIB)</t>
+          <t>CEO Maharashtra press note of 31.08.2026</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.eci.gov.in/eci/public/api/document?id=17536 | https://www.pib.gov.in/PressReleasePage.aspx?PRID=2315309&amp;reg=3&amp;lang=1</t>
+          <t>https://ceoelection.maharashtra.gov.in/Downloads/PDF/Notification/Press%20Note%20English_31.08.2026%20Draft%20Roll.pdf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -75189,29 +75189,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Andhra Pradesh and Meghalaya extended</t>
+          <t>Documents at the door, and a drive for those left off</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Andhra Pradesh's notices run to 10 October and its final roll is due on 16 October 2026. Meghalaya's final roll moves to 26 October 2026.</t>
+          <t>For people sent notices as unmapped or for logical discrepancies, BLOs would collect documents at home and upload them for the registration officer, so these people need not come to the office. A hearing would be held only in exceptional cases, as the registration officer decides, preferably online, and a family member authorised by the elector could attend. The Commission said the declaration attached to Form 6 for the revision had been upheld by the Supreme Court, and that outside the revision the forms in the Registration of Electors Rules, 1960 apply. Claims were extended in Delhi to 30 October and in Maharashtra to 12 October 2026. Where the revision was complete, in 20 states and union territories, anyone left out during it or after, and any young or first-time voter, could ask the registration officer to be added under continuous updation, and the Chief Electoral Officers, district officers and registration officers were to launch a special drive at once to enrol them.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ECI press release of 30.09.2026 (PIB)</t>
+          <t>ECI press note ECI/PN/120/2026 of 26.09.2026 | ECI press release of 26.09.2026 (PIB)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2317352&amp;reg=3&amp;lang=1</t>
+          <t>https://www.eci.gov.in/eci/public/api/document?id=17536 | https://www.pib.gov.in/PressReleasePage.aspx?PRID=2315309&amp;reg=3&amp;lang=1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -75226,57 +75226,94 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>The drive after the revision, in writing</t>
+          <t>Andhra Pradesh and Meghalaya extended</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>The Commission wrote to every Chief Electoral Officer setting out a special drive to enrol electors left off and young or first-time voters. Booth officers are to compare the current roll with the roll from before the revision, list everyone who was on the first and is missing from the second, visit them at home and help those found eligible fill in Form 6. The Commission asked them to cover at least 20 to 25 electors a week, so the work ends in about a month. The lists go to the booth agents of the recognised parties and then to the registration officer, who decides each case under the 1950 Act and the 1960 Rules. Booth camps are to be held, and special camps for people in night shelters, labour colonies and the homeless. The letter says anyone not on the roll, or whose name was deleted, can apply to be enrolled at any time.</t>
+          <t>Andhra Pradesh's notices run to 10 October and its final roll is due on 16 October 2026. Meghalaya's final roll moves to 26 October 2026.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ECI letter No. 23/2025/ERS(Vol-II) of 01.10.2026 to all Chief Electoral Officers</t>
+          <t>ECI press release of 30.09.2026 (PIB)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.eci.gov.in/eci/public/api/document?id=17541</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2317352&amp;reg=3&amp;lang=1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Election Commission</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Phase III</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>The drive after the revision, in writing</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>The Commission wrote to every Chief Electoral Officer setting out a special drive to enrol electors left off and young or first-time voters. Booth officers are to compare the current roll with the roll from before the revision, list everyone who was on the first and is missing from the second, visit them at home and help those found eligible fill in Form 6. The Commission asked them to cover at least 20 to 25 electors a week, so the work ends in about a month. The lists go to the booth agents of the recognised parties and then to the registration officer, who decides each case under the 1950 Act and the 1960 Rules. Booth camps are to be held, and special camps for people in night shelters, labour colonies and the homeless. The letter says anyone not on the roll, or whose name was deleted, can apply to be enrolled at any time.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ECI letter No. 23/2025/ERS(Vol-II) of 01.10.2026 to all Chief Electoral Officers</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.eci.gov.in/eci/public/api/document?id=17541</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>State election officer</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Phase III</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>A drive to find the names left off</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>When it published Uttarakhand's final roll, the state's Chief Electoral Officer set out the Commission's directions for what follows. Booth officers are to compare the roll from before the revision with the current one and list the electors who were on the first and are missing from the second. They are to visit them at home and help those still eligible fill in Form 6. The lists are to be shared with the booth agents of the recognised parties, and booth and special camps held, including for people in night shelters, labour colonies and the homeless.</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>CEO Uttarakhand, press note PN 63/2026 of 03.10.2026</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://cdnbbsr.s3waas.gov.in/s3cbf8710b43df3f2c1553e649403426df/uploads/2026/10/202610031173939115.pdf</t>
         </is>
@@ -79555,17 +79592,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7133785</v>
+        <v>9753577</v>
       </c>
       <c r="D4" t="n">
-        <v>2430000</v>
+        <v>3312919</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -79573,7 +79610,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -79582,53 +79619,56 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
-        </is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1379785</v>
       </c>
       <c r="K4" t="n">
-        <v>1904380</v>
+        <v>1933134</v>
       </c>
       <c r="L4" t="n">
-        <v>97186</v>
+        <v>350</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/india/2026/Aug/06/2027-lakh-voter-notices-trigger-political-row-in-uttarakhand-amid-electoral-roll-revision</t>
+          <t>https://www.hindustantimes.com/india-news/why-did-jaishankar-rekha-gupta-kejriwal-get-sir-notices-full-list-of-prominent-names-in-delhi-electoral-row-101789967719972.html</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/india/2026/Aug/06/2027-lakh-voter-notices-trigger-political-row-in-uttarakhand-amid-electoral-roll-revision</t>
+          <t>https://www.hindustantimes.com/india-news/why-did-jaishankar-rekha-gupta-kejriwal-get-sir-notices-full-list-of-prominent-names-in-delhi-electoral-row-101789967719972.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>9753577</v>
+        <v>54376756</v>
       </c>
       <c r="D5" t="n">
-        <v>3312919</v>
+        <v>17100000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>published</t>
+          <t>sum</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>31.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -79637,56 +79677,56 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1379785</v>
+        <v>1300000</v>
       </c>
       <c r="K5" t="n">
-        <v>1933134</v>
+        <v>15800000</v>
       </c>
       <c r="L5" t="n">
-        <v>350</v>
+        <v>2000</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/why-did-jaishankar-rekha-gupta-kejriwal-get-sir-notices-full-list-of-prominent-names-in-delhi-electoral-row-101789967719972.html</t>
+          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Feb/24/electorate-shrinks-by-over-10-per-cent-in-tamil-nadus-103-constituencies</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/why-did-jaishankar-rekha-gupta-kejriwal-get-sir-notices-full-list-of-prominent-names-in-delhi-electoral-row-101789967719972.html</t>
+          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Feb/24/electorate-shrinks-by-over-10-per-cent-in-tamil-nadus-103-constituencies</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>54376756</v>
+        <v>450282</v>
       </c>
       <c r="D6" t="n">
-        <v>17100000</v>
+        <v>137814</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sum</t>
+          <t>published</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>31.4</v>
+        <v>30.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -79695,48 +79735,45 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1300000</v>
+        <v>69461</v>
       </c>
       <c r="K6" t="n">
-        <v>15800000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2000</v>
+        <v>68353</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Feb/24/electorate-shrinks-by-over-10-per-cent-in-tamil-nadus-103-constituencies</t>
+          <t>https://www.tribuneindia.com/news/chandigarh/sir-1-37-lakh-electors-to-get-notice-over-missing-linkage-discrepancies/</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Feb/24/electorate-shrinks-by-over-10-per-cent-in-tamil-nadus-103-constituencies</t>
+          <t>https://www.tribuneindia.com/news/chandigarh/sir-1-37-lakh-electors-to-get-notice-over-missing-linkage-discrepancies/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Arunachal Pradesh</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>450282</v>
+        <v>718046</v>
       </c>
       <c r="D7" t="n">
-        <v>137814</v>
+        <v>218588</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -79744,11 +79781,11 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -79758,40 +79795,43 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>69461</v>
+        <v>85175</v>
       </c>
       <c r="K7" t="n">
-        <v>68353</v>
+        <v>133413</v>
+      </c>
+      <c r="L7" t="n">
+        <v>28899</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/chandigarh/sir-1-37-lakh-electors-to-get-notice-over-missing-linkage-discrepancies/</t>
+          <t>https://ceoarunachal.nic.in/componenthelper/getcomponentfile/68</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/chandigarh/sir-1-37-lakh-electors-to-get-notice-over-missing-linkage-discrepancies/</t>
+          <t>https://ceoarunachal.nic.in/componenthelper/getcomponentfile/68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arunachal Pradesh</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>718046</v>
+        <v>2169243</v>
       </c>
       <c r="D8" t="n">
-        <v>218588</v>
+        <v>651735</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -79799,11 +79839,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>press</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -79813,43 +79853,43 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>85175</v>
+        <v>222786</v>
       </c>
       <c r="K8" t="n">
-        <v>133413</v>
+        <v>428949</v>
       </c>
       <c r="L8" t="n">
-        <v>28899</v>
+        <v>1194</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://ceoarunachal.nic.in/componenthelper/getcomponentfile/68</t>
+          <t>https://www.syllad.com/over-93-sir-notice-cases-resolved-blos-to-facilitate-electors-at-doorstep-meghalaya-ceo/</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://ceoarunachal.nic.in/componenthelper/getcomponentfile/68</t>
+          <t>https://www.syllad.com/over-93-sir-notice-cases-resolved-blos-to-facilitate-electors-at-doorstep-meghalaya-ceo/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>2169243</v>
+        <v>433294</v>
       </c>
       <c r="D9" t="n">
-        <v>651735</v>
+        <v>124519</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -79857,11 +79897,11 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>28.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -79871,43 +79911,43 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>222786</v>
+        <v>72135</v>
       </c>
       <c r="K9" t="n">
-        <v>428949</v>
+        <v>52384</v>
       </c>
       <c r="L9" t="n">
-        <v>1194</v>
+        <v>16485</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.syllad.com/over-93-sir-notice-cases-resolved-blos-to-facilitate-electors-at-doorstep-meghalaya-ceo/</t>
+          <t>https://www.sikkim.gov.in/media/news-announcement/news-info?name=Final+Electoral+Roll+under+SIR+2026+Published+in+Sikkim</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://www.syllad.com/over-93-sir-notice-cases-resolved-blos-to-facilitate-electors-at-doorstep-meghalaya-ceo/</t>
+          <t>https://www.sikkim.gov.in/media/news-announcement/news-info?name=Final+Electoral+Roll+under+SIR+2026+Published+in+Sikkim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>433294</v>
+        <v>22101249</v>
       </c>
       <c r="D10" t="n">
-        <v>124519</v>
+        <v>6324116</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -79915,11 +79955,11 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>press</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -79929,43 +79969,35 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>72135</v>
+        <v>1403205</v>
       </c>
       <c r="K10" t="n">
-        <v>52384</v>
-      </c>
-      <c r="L10" t="n">
-        <v>16485</v>
+        <v>4555227</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.sikkim.gov.in/media/news-announcement/news-info?name=Final+Electoral+Roll+under+SIR+2026+Published+in+Sikkim</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>https://www.sikkim.gov.in/media/news-announcement/news-info?name=Final+Electoral+Roll+under+SIR+2026+Published+in+Sikkim</t>
+          <t>https://timesofindia.indiatimes.com/city/ranchi/jharkhand-electoral-roll-verification-notices-to-be-issued-to-63-24-lakh-voters/articleshow/133009630.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>22101249</v>
+        <v>7133785</v>
       </c>
       <c r="D11" t="n">
-        <v>6324116</v>
+        <v>2027000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -79973,7 +80005,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -79982,7 +80014,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -79990,15 +80022,20 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>1403205</v>
-      </c>
       <c r="K11" t="n">
-        <v>4555227</v>
+        <v>1904380</v>
+      </c>
+      <c r="L11" t="n">
+        <v>97186</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/ranchi/jharkhand-electoral-roll-verification-notices-to-be-issued-to-63-24-lakh-voters/articleshow/133009630.cms</t>
+          <t>https://www.newindianexpress.com/india/2026/Aug/06/2027-lakh-voter-notices-trigger-political-row-in-uttarakhand-amid-electoral-roll-revision</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/india/2026/Aug/06/2027-lakh-voter-notices-trigger-political-row-in-uttarakhand-amid-electoral-roll-revision</t>
         </is>
       </c>
     </row>

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -73887,7 +73887,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The roll before by sex as Hindustan Times quoted the Chief Electoral Officer</t>
+          <t>The roll before by sex as Hindustan Times quoted the Chief Electoral Officer, which the press note of 31 August 2026 does not give. The draft by sex is the Chief Electoral Officer's table of the same date.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">

--- a/downloads/india-all-states.xlsx
+++ b/downloads/india-all-states.xlsx
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L165"/>
+  <dimension ref="A1:L188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -21251,27 +21251,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Resolutions in the Assemblies</t>
+          <t>In the courts</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Telangana High Court</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jharkhand Assembly; INDIA bloc; BJP</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Assembly resolution</t>
+          <t>Notices and hearings; Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -21281,44 +21286,59 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>The Week (Press Trust of India)</t>
+          <t>LiveLaw</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>The Week, carrying a PTI report, said the Jharkhand Assembly passed a resolution opposing the SIR, moved by Parliamentary Affairs Minister Radhakrishna Kishore on behalf of the INDIA bloc. The BJP opposed it. When a Congress member asked for a vote, the Speaker ruled that it stood passed because the ruling coalition had a majority.</t>
+          <t>The Telangana High Court asked the Commission why one petitioner was left off the roll without a notice and what happened to the other after his hearing, LiveLaw reported. The petition challenges notices over minor discrepancies and the automated matching used in the revision. The case was listed again for 13 October.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>The Commission's counsel sought time for instructions. She said the second petitioner was sent a notice over a mismatch in his father's name and heard on 15 September, and that the first could file Form 6.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/26/cal40-jh-assembly-ld-sir.html</t>
+          <t>https://www.livelaw.in/high-court/telangana-high-court/telangana-high-court-sir-notice-ai-response-voter-roll-553094</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Resolutions in the Assemblies</t>
+          <t>In the courts</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Bombay High Court at Goa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kerala Assembly; CPI(M); Congress</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Assembly resolution</t>
+          <t>Form 8; Deletions</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -21328,44 +21348,59 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Siasat Daily (Press Trust of India)</t>
+          <t>ThePrint (PTI)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The Siasat Daily, carrying a PTI report, said the Kerala Assembly unanimously passed a resolution moved by Chief Minister Pinarayi Vijayan against the SIR in the state, with the Congress-led opposition backing it.</t>
+          <t>The Bombay High Court at Goa adjourned the St Cruz family's petition by a week at the Commission's request, after the Commission said orders the Supreme Court might pass could bear on it. The judges took the view that the Supreme Court's orders may not have a direct bearing, PTI reported, and the Commission's advocate told reporters the Supreme Court had asked High Courts to defer such hearings.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>The Commission's counsel also said "what is under challenge is the rejection of Form 8" and that it "cannot be looked at in isolation."</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/kerala-assembly-passes-unanimous-resolution-against-sir-3277487/</t>
+          <t>https://theprint.in/india/goa-hc-adjourns-hearing-on-plea-challenging-voter-deletion-as-eci-points-out-sc-cases/3063371/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Protests by parties and groups</t>
+          <t>In the courts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Kolkata; Howrah</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>INDIA bloc; Congress; RJD</t>
+          <t>Election Commission; Chief Electoral Officer, West Bengal</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Protest and march</t>
+          <t>Adjudication and appeals; Deletions</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -21375,39 +21410,54 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>LiveLaw</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ETV Bharat reported that a Bihar bandh called by the INDIA bloc parties against the SIR disrupted life across much of the state, with Rahul Gandhi and Tejashwi Yadav taking part.</t>
+          <t>Five electors removed from West Bengal's roll applied to the Supreme Court for their appeals to be decided before the Kolkata and Howrah municipal elections, LiveLaw reported. They also asked for a Special Investigation Team to examine how the revision's decisions were made. The application cites the Commission's affidavits as showing 1.7 lakh appeals pending from Kolkata and Howrah.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>None was reported. The applicants say the Chief Electoral Officer has not published the criteria for logical discrepancies.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/bihar-band-effect-in-different-district-of-bihar-election-2025-enn25070904786</t>
+          <t>https://www.livelaw.in/top-stories/supreme-court-5-deleted-voters-plea-for-expeditious-decision-on-appeals-against-exclusion-appellate-tribunals-howrah-kolkata-municipal-elections-553788</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Protests by parties and groups</t>
+          <t>In the courts</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CPI(ML) Liberation; INDIA bloc</t>
+          <t>CPI(M); Union Government; Cockroach Janta Party</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -21422,44 +21472,59 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Deccan Herald (Press Trust of India)</t>
+          <t>LiveLaw</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Deccan Herald, carrying a PTI report, said opposition members protested against the SIR inside the Bihar Assembly on the first day of its monsoon session, with CPI(ML) Liberation legislators wearing black.</t>
+          <t>The Supreme Court told the Centre not to stop all trains and Metro services in Delhi before the 10 October protests against the Chief Election Commissioner, and to run them in a regulated way, LiveLaw reported. The petition was brought by CPI(M) General Secretary MA Baby and others against the closure of 57 Metro stations and the cancellation of trains due at New Delhi and Nizamuddin. The order said the notifications appeared to be overreaching, and ETV Bharat reported that the bench also asked the Centre to reconsider Jantar Mantar as the designated protest site.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>The order records that the Solicitor General "has fairly agreed to impress upon the authorities to reassess such prohibitions." He said the impression that the whole city had been shut "is far from the truth."</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/bihar/anti-sir-protests-rock-bihar-assembly-on-inaugural-day-of-monsoon-session-3640011</t>
+          <t>https://www.livelaw.in/top-stories/dont-completely-stop-trainsmetro-in-delhi-allow-services-in-regulated-manner-supreme-court-to-centre-on-oct-10-protests-553920</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Protests by parties and groups</t>
+          <t>In the courts</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Kolkata; Howrah</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>INDIA bloc</t>
+          <t>Election Commission; Appellate tribunal (West Bengal)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Protest and march</t>
+          <t>Adjudication and appeals; Schedule and deadlines</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -21469,44 +21534,54 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>LiveLaw</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>ETV Bharat reported that INDIA bloc MPs protested at the Makar Dwar of Parliament against the Bihar SIR for a fifth day running and demanded that it be rolled back.</t>
+          <t>Counsel for electors removed in West Bengal asked the Supreme Court to hear their plea before the Kolkata and Howrah municipal elections and to let appellants vote, LiveLaw reported. The Chief Justice said the Court would try to list it on 16 October, or else on 29 October, and suggested the tribunals take up appeals for inclusion first and appeals seeking deletion last. Counsel told the Court that nearly 1.70 lakh appeals from the two municipal areas were pending.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No submission by the Commission was reported. The figures put to the Court were counsel's, partly drawn from the Commission's affidavits.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/several-mps-of-the-india-bloc-parties-protest-against-sir-enn25072801958</t>
+          <t>https://www.livelaw.in/amp/top-stories/we-are-conscious-supreme-court-to-consider-plea-to-prioritise-sir-deleted-voters-appeals-ahead-of-kolkata-howrah-municipal-elections-553845</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Protests by parties and groups</t>
+          <t>In the courts</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>INDIA bloc; Congress; Police; Election Commission</t>
+          <t>Election Commission; State Election Commission, Andhra Pradesh</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protest and march; Police and FIRs</t>
+          <t>Schedule and deadlines</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -21516,49 +21591,54 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>The Wire</t>
+          <t>LiveLaw</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>The Wire reported that Delhi Police detained opposition MPs, among them Mallikarjun Kharge and Rahul Gandhi, when their march from Parliament to the Election Commission against the Bihar SIR was stopped, and that they were released in the afternoon.</t>
+          <t>The Supreme Court, hearing a challenge to the Andhra Pradesh High Court's order for local body elections within six weeks, said the elections should use the revised roll if it is published before the polls are notified, and the existing roll if it is not. It said the roll in force applies until the Commission publishes the revised list and that the revision cannot be a reason to delay the polls.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>The Wire reported that the Commission had written to Jairam Ramesh the day before asking for the names of 30 members for a meeting “due to limitation of space”.</t>
+          <t>The bench noted that the Election Commission had proposed to publish the final roll on 16 October 2026. Senior Advocate K Parameshwar, for the State Election Commission, said the rolls in force continue until the Commission publishes a fresh list.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://thewire.in/government/opposition-mps-including-rahul-gandhi-detained-on-their-way-to-election-commission</t>
+          <t>https://www.livelaw.in/top-stories/andhra-pradesh-local-body-elections-conduct-polls-as-per-old-rolls-if-sir-not-complete-before-notification-supreme-court-553872</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Protests by parties and groups</t>
+          <t>In the courts</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sasaram; Patna</t>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Union Government; Police; Delhi Metro Rail Corporation</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -21573,44 +21653,49 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>Outlook</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>ETV Bharat reported that Rahul Gandhi began a 16-day Vote Adhikar Yatra from Sasaram against the SIR in Bihar, due to end with a rally in Patna on 1 September. The Congress leader alleged that the SIR was being done to steal votes.</t>
+          <t>A contempt plea filed in the Supreme Court on 10 October alleged that the Centre and Delhi authorities defied the Court's order of 9 October, keeping 57 Metro stations shut and cancelling Delhi-bound trains before the protest against the Chief Election Commissioner, Outlook reported. The plea also said no traffic advisory had been published in newspapers. No hearing had been reported by 10 October.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>No reply from the officials named or from the government was reported.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/rahul-gandhi-kicks-off-vote-adhikar-yatra-in-bihar-to-protect-electoral-rights-enn25081702682</t>
+          <t>https://www.outlookindia.com/national/supreme-court-contempt-plea-alleges-delhi-authorities-defied-order-on-metro-train-curbs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Protests by parties and groups</t>
+          <t>Resolutions in the Assemblies</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>DMK; AIADMK; BJP</t>
+          <t>Jharkhand Assembly; INDIA bloc; BJP</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Protest and march</t>
+          <t>Assembly resolution</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -21620,49 +21705,44 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>The News Minute</t>
+          <t>The Week (Press Trust of India)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>The News Minute reported that an all-party meeting chaired by Chief Minister M.K. Stalin, attended by nearly 50 parties, resolved to approach the Supreme Court against the SIR in Tamil Nadu. The AIADMK and the BJP were not invited and several other parties stayed away.</t>
+          <t>The Week, carrying a PTI report, said the Jharkhand Assembly passed a resolution opposing the SIR, moved by Parliamentary Affairs Minister Radhakrishna Kishore on behalf of the INDIA bloc. The BJP opposed it. When a Congress member asked for a vote, the Speaker ruled that it stood passed because the ruling coalition had a majority.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/tamil-nadu/tamil-nadu-all-party-meeting-opposes-sir-decides-to-approach-sc</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/26/cal40-jh-assembly-ld-sir.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Protests by parties and groups</t>
+          <t>Resolutions in the Assemblies</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Kolkata</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trinamool Congress</t>
+          <t>Kerala Assembly; CPI(M); Congress</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Protest and march</t>
+          <t>Assembly resolution</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -21672,17 +21752,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>Siasat Daily (Press Trust of India)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ETV Bharat reported that Chief Minister Mamata Banerjee led a procession in Kolkata against the SIR. She called the SIR an assault on people's existence and democratic rights.</t>
+          <t>The Siasat Daily, carrying a PTI report, said the Kerala Assembly unanimously passed a resolution moved by Chief Minister Pinarayi Vijayan against the SIR in the state, with the Congress-led opposition backing it.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/state/mamata-leads-massive-kolkata-rally-against-sir-enn25110406838</t>
+          <t>https://www.siasat.com/kerala-assembly-passes-unanimous-resolution-against-sir-3277487/</t>
         </is>
       </c>
     </row>
@@ -21694,17 +21774,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DMK</t>
+          <t>INDIA bloc; Congress; RJD</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -21719,17 +21799,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Akashvani News (All India Radio)</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Akashvani News reported that the DMK and its alliance partners held protest demonstrations across Tamil Nadu against the SIR, with MPs, MLAs and district functionaries taking part.</t>
+          <t>ETV Bharat reported that a Bihar bandh called by the INDIA bloc parties against the SIR disrupted life across much of the state, with Rahul Gandhi and Tejashwi Yadav taking part.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/dmk-allies-protest-against-sir-revision-in-tamil-nadu</t>
+          <t>https://www.etvbharat.com/en/!state/bihar-band-effect-in-different-district-of-bihar-election-2025-enn25070904786</t>
         </is>
       </c>
     </row>
@@ -21741,22 +21821,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Bongaon; Thakurnagar; North 24 Parganas</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trinamool Congress; Election Commission</t>
+          <t>CPI(ML) Liberation; INDIA bloc</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -21771,22 +21846,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>The Tribune</t>
+          <t>Deccan Herald (Press Trust of India)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>The Tribune reported that Mamata Banerjee led a three-km march from Bongaon to Thakurnagar in North 24 Parganas against the SIR, after addressing a rally at Bangaon.</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>The Tribune reported that the Commission granted a five-member TMC delegation a meeting on 28 November.</t>
+          <t>Deccan Herald, carrying a PTI report, said opposition members protested against the SIR inside the Bihar Assembly on the first day of its monsoon session, with CPI(ML) Liberation legislators wearing black.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/top-headlines/mamata-leads-anti-sir-march-ec-to-meet-tmc-leaders-on-nov-28</t>
+          <t>https://www.deccanherald.com/india/bihar/anti-sir-protests-rock-bihar-assembly-on-inaugural-day-of-monsoon-session-3640011</t>
         </is>
       </c>
     </row>
@@ -21798,27 +21868,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Assam</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Guwahati</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Congress; Election Commission; Government of Assam</t>
+          <t>INDIA bloc</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Protest and march; Deletions</t>
+          <t>Protest and march</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -21828,22 +21893,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Siasat Daily (Press Trust of India)</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>The Siasat Daily, carrying a PTI report, said the united opposition held a protest at Chachal in Guwahati against alleged irregularities in the draft rolls of Assam's Special Revision. Assam Congress president Gaurav Gogoi accused Chief Minister Himanta Biswa Sarma of misusing the Election Commission.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>The report said the Commission stated that the flagged names had not yet been deleted and would only be processed after formal applications in the claims and objections period.</t>
+          <t>ETV Bharat reported that INDIA bloc MPs protested at the Makar Dwar of Parliament against the Bihar SIR for a fifth day running and demanded that it be rolled back.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/opposition-in-assam-protests-vote-theft-through-sr-slams-himanta-bjp-3334019/</t>
+          <t>https://www.etvbharat.com/en/!bharat/several-mps-of-the-india-bloc-parties-protest-against-sir-enn25072801958</t>
         </is>
       </c>
     </row>
@@ -21855,27 +21915,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Karnataka</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trade unions; Civil society groups</t>
+          <t>INDIA bloc; Congress; Police; Election Commission</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Protest and march</t>
+          <t>Protest and march; Police and FIRs</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -21885,17 +21940,22 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>The Wire</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ETV Bharat reported that trade unions, women's groups, student bodies and Dalit and minority rights groups protested against the SIR at Freedom Park in Bengaluru under the banner My Vote, My Right, and urged the state government to take a stand.</t>
+          <t>The Wire reported that Delhi Police detained opposition MPs, among them Mallikarjun Kharge and Rahul Gandhi, when their march from Parliament to the Election Commission against the Bihar SIR was stopped, and that they were released in the afternoon.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>The Wire reported that the Commission had written to Jairam Ramesh the day before asking for the names of 30 members for a meeting “due to limitation of space”.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/state/citizens-protest-special-intensive-revision-in-bengaluru-enn26020705793</t>
+          <t>https://thewire.in/government/opposition-mps-including-rahul-gandhi-detained-on-their-way-to-election-commission</t>
         </is>
       </c>
     </row>
@@ -21907,22 +21967,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sasaram; Patna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trinamool Congress</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Protest and march; Adjudication and appeals</t>
+          <t>Protest and march</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -21937,12 +22002,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>ETV Bharat reported that Mamata Banerjee ended her sit-in against the SIR on its fifth day after the Supreme Court ordered appellate tribunals to hear appeals against exclusions in West Bengal. She said the protest was suspended temporarily.</t>
+          <t>ETV Bharat reported that Rahul Gandhi began a 16-day Vote Adhikar Yatra from Sasaram against the SIR in Bihar, due to end with a rally in Patna on 1 September. The Congress leader alleged that the SIR was being done to steal votes.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/state/mamata-lifts-dharna-against-flaws-in-sir-hails-sc-order-on-forming-appellate-body-enn26031006780</t>
+          <t>https://www.etvbharat.com/en/!state/rahul-gandhi-kicks-off-vote-adhikar-yatra-in-bihar-to-protect-electoral-rights-enn25081702682</t>
         </is>
       </c>
     </row>
@@ -21954,17 +22019,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Congress; Election Commission</t>
+          <t>DMK; AIADMK; BJP</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -21979,17 +22044,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>The News Minute</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>ETV Bharat reported that a Congress delegation led by Kumari Selja staged a sit-in outside the Election Commission headquarters in Delhi over the SIR in Uttarakhand after saying it was not allowed into the premises.</t>
+          <t>The News Minute reported that an all-party meeting chaired by Chief Minister M.K. Stalin, attended by nearly 50 parties, resolved to approach the Supreme Court against the SIR in Tamil Nadu. The AIADMK and the BJP were not invited and several other parties stayed away.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/bharat/congress-alleges-irregularities-in-sir-in-uttarakhand-seeks-election-commission-intervention-enn26082006661</t>
+          <t>https://www.thenewsminute.com/tamil-nadu/tamil-nadu-all-party-meeting-opposes-sir-decides-to-approach-sc</t>
         </is>
       </c>
     </row>
@@ -22001,22 +22066,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Congress; Election Commission</t>
+          <t>Trinamool Congress</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Protest and march; Commission's independence</t>
+          <t>Protest and march</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -22026,22 +22096,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Business Today reported that Congress workers protested in several states demanding the resignation of Chief Election Commissioner Gyanesh Kumar over the handling of the SIR, after The Indian Express reported objections recorded by two Election Commissioners.</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Business Today reported that the Commission rejected the characterisation of these exchanges as institutional dissent and said final decisions on the SIR were unanimous.</t>
+          <t>ETV Bharat reported that Chief Minister Mamata Banerjee led a procession in Kolkata against the SIR. She called the SIR an assault on people's existence and democratic rights.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/congress-protests-against-cec-gyanesh-kumar-spread-across-india-gaurav-gogoi-detained-in-guwahati-557894-2026-09-25</t>
+          <t>https://www.etvbharat.com/en/state/mamata-leads-massive-kolkata-rally-against-sir-enn25110406838</t>
         </is>
       </c>
     </row>
@@ -22053,27 +22118,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Assam</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Guwahati</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Congress; Police</t>
+          <t>DMK</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Protest and march; Commission's independence</t>
+          <t>Protest and march</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -22083,17 +22143,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Akashvani News (All India Radio)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Business Today reported that police detained Assam Congress president and MP Gaurav Gogoi during a protest in Guwahati demanding the Chief Election Commissioner's resignation.</t>
+          <t>Akashvani News reported that the DMK and its alliance partners held protest demonstrations across Tamil Nadu against the SIR, with MPs, MLAs and district functionaries taking part.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/congress-protests-against-cec-gyanesh-kumar-spread-across-india-gaurav-gogoi-detained-in-guwahati-557894-2026-09-25</t>
+          <t>https://www.newsonair.gov.in/dmk-allies-protest-against-sir-revision-in-tamil-nadu</t>
         </is>
       </c>
     </row>
@@ -22105,22 +22165,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Bongaon; Thakurnagar; North 24 Parganas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Civil society groups; CPI(ML) Liberation; Police</t>
+          <t>Trinamool Congress; Election Commission</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Protest and march; Commission's independence</t>
+          <t>Protest and march</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -22130,17 +22195,22 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>The Quint</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>The Quint reported that police detained protesters from civil society groups and student organisations at Jantar Mantar, among them CPI(ML) Liberation general secretary Dipankar Bhattacharya, as they demanded the Chief Election Commissioner's resignation and a rollback of the SIR.</t>
+          <t>The Tribune reported that Mamata Banerjee led a three-km march from Bongaon to Thakurnagar in North 24 Parganas against the SIR, after addressing a rally at Bangaon.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>The Tribune reported that the Commission granted a five-member TMC delegation a meeting on 28 November.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://www.thequint.com/news/jantar-mantar-protest-gyanesh-kumar-resignation-mass-detentions</t>
+          <t>https://www.tribuneindia.com/news/top-headlines/mamata-leads-anti-sir-march-ec-to-meet-tmc-leaders-on-nov-28</t>
         </is>
       </c>
     </row>
@@ -22152,27 +22222,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Guwahati</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Congress; Police</t>
+          <t>Congress; Election Commission; Government of Assam</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Protest and march; Commission's independence</t>
+          <t>Protest and march; Deletions</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -22182,17 +22252,22 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ThePrint (Press Trust of India)</t>
+          <t>Siasat Daily (Press Trust of India)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>ThePrint, carrying a PTI report, said police detained Uttar Pradesh Congress president Ajay Rai and hundreds of party workers in Lucknow after they were stopped while marching to demand the Chief Election Commissioner's resignation.</t>
+          <t>The Siasat Daily, carrying a PTI report, said the united opposition held a protest at Chachal in Guwahati against alleged irregularities in the draft rolls of Assam's Special Revision. Assam Congress president Gaurav Gogoi accused Chief Minister Himanta Biswa Sarma of misusing the Election Commission.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>The report said the Commission stated that the flagged names had not yet been deleted and would only be processed after formal applications in the claims and objections period.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/congress-workers-protest-against-cec-in-lucknow-clash-with-police/3053574/</t>
+          <t>https://www.siasat.com/opposition-in-assam-protests-vote-theft-through-sr-slams-himanta-bjp-3334019/</t>
         </is>
       </c>
     </row>
@@ -22204,27 +22279,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Patna</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Congress; Police; Election Commission</t>
+          <t>Trade unions; Civil society groups</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Protest and march; Commission's independence</t>
+          <t>Protest and march</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -22234,22 +22309,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ThePrint (ANI)</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ThePrint, carrying an ANI report, said police used water cannons on Congress workers in Patna who were protesting against the Chief Election Commissioner as part of the party's nationwide programme over the SIR.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>The report said the Commission described operational queries and internal feedback as part of the normal functioning of a multi-member body and said all final SIR decisions were unanimous.</t>
+          <t>ETV Bharat reported that trade unions, women's groups, student bodies and Dalit and minority rights groups protested against the SIR at Freedom Park in Bengaluru under the banner My Vote, My Right, and urged the state government to take a stand.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/gyanesh-its-done-bro-youth-congress-marches-to-jantar-mantar-water-cannons-in-bihar-punjab/3053510/</t>
+          <t>https://www.etvbharat.com/en/state/citizens-protest-special-intensive-revision-in-bengaluru-enn26020705793</t>
         </is>
       </c>
     </row>
@@ -22261,27 +22331,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Punjab</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Chandigarh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Congress; Police</t>
+          <t>Trinamool Congress</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Protest and march</t>
+          <t>Protest and march; Adjudication and appeals</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -22291,17 +22356,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ThePrint (ANI)</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ThePrint, carrying an ANI report, said police used water cannons on Punjab Congress workers demonstrating in Chandigarh as part of the party's protests over the SIR.</t>
+          <t>ETV Bharat reported that Mamata Banerjee ended her sit-in against the SIR on its fifth day after the Supreme Court ordered appellate tribunals to hear appeals against exclusions in West Bengal. She said the protest was suspended temporarily.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/gyanesh-its-done-bro-youth-congress-marches-to-jantar-mantar-water-cannons-in-bihar-punjab/3053510/</t>
+          <t>https://www.etvbharat.com/en/state/mamata-lifts-dharna-against-flaws-in-sir-hails-sc-order-on-forming-appellate-body-enn26031006780</t>
         </is>
       </c>
     </row>
@@ -22313,27 +22378,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Shimla</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Congress; Election Commission</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Protest and march; Commission's independence</t>
+          <t>Protest and march</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -22343,17 +22403,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ThePrint (Press Trust of India)</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>ThePrint, carrying a PTI report, said the Himachal Pradesh Congress protested outside the Election Commission office in Shimla, burned an effigy of the Chief Election Commissioner and raised slogans against the SIR.</t>
+          <t>ETV Bharat reported that a Congress delegation led by Kumari Selja staged a sit-in outside the Election Commission headquarters in Delhi over the SIR in Uttarakhand after saying it was not allowed into the premises.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/hp-congress-protests-in-shimla-demands-cec-gyanesh-kumars-removal-arrest/3053573/</t>
+          <t>https://www.etvbharat.com/en/bharat/congress-alleges-irregularities-in-sir-in-uttarakhand-seeks-election-commission-intervention-enn26082006661</t>
         </is>
       </c>
     </row>
@@ -22370,17 +22430,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Shillong</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Congress; Election Commission</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -22395,17 +22450,22 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>UNI</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>UNI reported that Congress workers in Shillong, led by state Congress president Vincent H. Pala, burned an effigy of the Chief Election Commissioner and demanded his removal amid the row over the SIR.</t>
+          <t>Business Today reported that Congress workers protested in several states demanding the resignation of Chief Election Commissioner Gyanesh Kumar over the handling of the SIR, after The Indian Express reported objections recorded by two Election Commissioners.</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Business Today reported that the Commission rejected the characterisation of these exchanges as institutional dissent and said final decisions on the SIR were unanimous.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/east-india/politics-meghalaya-cong-gyanesh-kumar-resignation/192544</t>
+          <t>https://www.businesstoday.in/india/story/congress-protests-against-cec-gyanesh-kumar-spread-across-india-gaurav-gogoi-detained-in-guwahati-557894-2026-09-25</t>
         </is>
       </c>
     </row>
@@ -22417,27 +22477,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Dehradun</t>
+          <t>Guwahati</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>Congress; Police</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Protest and march; Deletions; Form 7</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -22447,17 +22507,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Asianet Newsable</t>
+          <t>Business Today</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Asianet Newsable reported that the Uttarakhand Congress marched in Dehradun, surrounded the Election Commission office and burned an effigy of the Chief Election Commissioner. The party raised concerns over how names were added and deleted and how objections were disposed of.</t>
+          <t>Business Today reported that police detained Assam Congress president and MP Gaurav Gogoi during a protest in Guwahati demanding the Chief Election Commissioner's resignation.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>https://newsable.asianetnews.com/india/uttarakhand-congress-gheraos-ec-office-demands-cec-s-resignation-articleshow-bgnhevg</t>
+          <t>https://www.businesstoday.in/india/story/congress-protests-against-cec-gyanesh-kumar-spread-across-india-gaurav-gogoi-detained-in-guwahati-557894-2026-09-25</t>
         </is>
       </c>
     </row>
@@ -22469,22 +22529,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Karnataka</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Congress; Election Commission</t>
+          <t>Civil society groups; CPI(ML) Liberation; Police</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -22499,22 +22554,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ThePrint (Press Trust of India)</t>
+          <t>The Quint</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ThePrint, carrying a PTI report, said the Karnataka Congress, with Chief Minister D.K. Shivakumar and former Chief Minister Siddaramaiah, protested at Freedom Park in Bengaluru against the SIR and demanded the Chief Election Commissioner's resignation.</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>The Election Commission, however, has asserted that its official orders, decisions and administrative directions have full legal sanction, and that differing views and observations are a normal part of deliberations within any institution.</t>
+          <t>The Quint reported that police detained protesters from civil society groups and student organisations at Jantar Mantar, among them CPI(ML) Liberation general secretary Dipankar Bhattacharya, as they demanded the Chief Election Commissioner's resignation and a rollback of the SIR.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/karnataka-cong-protests-against-sir-demands-cec-gyanesh-kumars-resignation-2/3054130/</t>
+          <t>https://www.thequint.com/news/jantar-mantar-protest-gyanesh-kumar-resignation-mass-detentions</t>
         </is>
       </c>
     </row>
@@ -22526,17 +22576,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -22546,7 +22596,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Protest and march</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -22561,12 +22611,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ThePrint, carrying a PTI report, said police used water cannons and detained former Chief Minister Ashok Gehlot and state Congress chief Govind Singh Dotasra during a march to the State Election Commission office in Jaipur over alleged SIR irregularities.</t>
+          <t>ThePrint, carrying a PTI report, said police detained Uttar Pradesh Congress president Ajay Rai and hundreds of party workers in Lucknow after they were stopped while marching to demand the Chief Election Commissioner's resignation.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/gehlot-dotasra-detained-during-cong-protest-in-jaipur-over-sir-row/3055754/</t>
+          <t>https://theprint.in/india/congress-workers-protest-against-cec-in-lucknow-clash-with-police/3053574/</t>
         </is>
       </c>
     </row>
@@ -22578,17 +22628,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Patna</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>INDIA bloc; Congress; Election Commission</t>
+          <t>Congress; Police; Election Commission</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -22603,17 +22658,22 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>The Wire</t>
+          <t>ThePrint (ANI)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Leaders of the INDIA bloc, 33 of them from 19 parties, agreed a plan of district marches from 2 to 8 October, a march of opposition MPs to the Commission on 6 October, a meeting with the President in the second week of October and five rallies including one in Delhi on 1 November, The Wire reported. Congress president Mallikarjun Kharge said the Commission was being used as a puppet by the Prime Minister and the Home Minister.</t>
+          <t>ThePrint, carrying an ANI report, said police used water cannons on Congress workers in Patna who were protesting against the Chief Election Commissioner as part of the party's nationwide programme over the SIR.</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>The report said the Commission described operational queries and internal feedback as part of the normal functioning of a multi-member body and said all final SIR decisions were unanimous.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/politics/ec-played-like-a-puppet-india-bloc-seals-roadmap-to-ramp-up-anti-sir-agitation</t>
+          <t>https://theprint.in/politics/gyanesh-its-done-bro-youth-congress-marches-to-jantar-mantar-water-cannons-in-bihar-punjab/3053510/</t>
         </is>
       </c>
     </row>
@@ -22625,27 +22685,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Civil society groups</t>
+          <t>Congress; Police</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Protest and march; Commission's independence</t>
+          <t>Protest and march</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -22655,17 +22715,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>The South First</t>
+          <t>ThePrint (ANI)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>The South First reported that more than a dozen civil society groups held a day-long protest at Dharna Chowk in Hyderabad, demanding that the SIR be scrapped and the Chief Election Commissioner resign.</t>
+          <t>ThePrint, carrying an ANI report, said police used water cannons on Punjab Congress workers demonstrating in Chandigarh as part of the party's protests over the SIR.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>https://thesouthfirst.com/telangana/attempt-to-kill-democracy-hyderabad-civil-society-protests-sir-demands-cec-gyanesh-kumars-resignation/</t>
+          <t>https://theprint.in/politics/gyanesh-its-done-bro-youth-congress-marches-to-jantar-mantar-water-cannons-in-bihar-punjab/3053510/</t>
         </is>
       </c>
     </row>
@@ -22677,22 +22737,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Shimla</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT); MNS</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -22707,17 +22767,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Free Press Journal</t>
+          <t>ThePrint (Press Trust of India)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>The Free Press Journal reported that Uddhav Thackeray of the Shiv Sena (UBT) and Raj Thackeray of the MNS led the Virat Garjana Morcha in Mumbai seeking the Chief Election Commissioner's resignation. Raj Thackeray demanded that the SIR in Maharashtra be cancelled.</t>
+          <t>ThePrint, carrying a PTI report, said the Himachal Pradesh Congress protested outside the Election Commission office in Shimla, burned an effigy of the Chief Election Commissioner and raised slogans against the SIR.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/garjana-morcha-uddhav-raj-thackeray-lead-protest-seeking-gyanesh-kumars-resignation-scrapping-of-maharashtra-sir</t>
+          <t>https://theprint.in/india/hp-congress-protests-in-shimla-demands-cec-gyanesh-kumars-removal-arrest/3053573/</t>
         </is>
       </c>
     </row>
@@ -22729,22 +22789,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Meghalaya</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Shillong</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>INDIA bloc; Congress; Police</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Protest and march; Police and FIRs</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -22754,17 +22819,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The Wire</t>
+          <t>UNI</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>The Wire reported that police stopped an INDIA bloc march from Parliament to the Election Commission, and that opposition MPs held a sit-in at the All India Radio building until police detained Rahul Gandhi and Priyanka Gandhi Vadra that night.</t>
+          <t>UNI reported that Congress workers in Shillong, led by state Congress president Vincent H. Pala, burned an effigy of the Chief Election Commissioner and demanded his removal amid the row over the SIR.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://thewire.in/politics/india-bloc-opposition-parties-march-nirvachan-sadan-election-commission-rahul-gandhi</t>
+          <t>https://www.uniindia.com/east-india/politics-meghalaya-cong-gyanesh-kumar-resignation/192544</t>
         </is>
       </c>
     </row>
@@ -22776,27 +22841,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Dehradun</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>INDIA bloc; Election Commission</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Protest and march; Commission's independence</t>
+          <t>Protest and march; Deletions; Form 7</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -22806,22 +22871,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Deccan Herald</t>
+          <t>Asianet Newsable</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Opposition MPs of the INDIA bloc marched from Parliament to the Commission's headquarters to press for the Chief Election Commissioner's removal, and asked for 240 MPs to meet the three Commissioners at Parliament House Annexe, Deccan Herald reported.</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>The Commission said no party had sought an appointment until 4 pm, that a meeting of 240 MPs away from its premises was unusual and could not be accepted, and that the MPs declined its offer to send its senior-most officer on duty to receive their memorandum, Deccan Herald reported.</t>
+          <t>Asianet Newsable reported that the Uttarakhand Congress marched in Dehradun, surrounded the Election Commission office and burned an effigy of the Chief Election Commissioner. The party raised concerns over how names were added and deleted and how objections were disposed of.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/cec-row-ec-refuses-oppositions-demand-for-meeting-4172987</t>
+          <t>https://newsable.asianetnews.com/india/uttarakhand-congress-gheraos-ec-office-demands-cec-s-resignation-articleshow-bgnhevg</t>
         </is>
       </c>
     </row>
@@ -22833,17 +22893,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AAP; Chief Electoral Officer, Delhi</t>
+          <t>Congress; Election Commission</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -22858,17 +22923,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Deccan Herald (Press Trust of India)</t>
+          <t>ThePrint (Press Trust of India)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Deccan Herald, carrying a PTI report, said AAP workers and members of other parties protested outside the Delhi Chief Electoral Officer's office demanding the Chief Election Commissioner's resignation over alleged SIR irregularities. It said AAP had earlier protested at Jantar Mantar and India Gate.</t>
+          <t>ThePrint, carrying a PTI report, said the Karnataka Congress, with Chief Minister D.K. Shivakumar and former Chief Minister Siddaramaiah, protested at Freedom Park in Bengaluru against the SIR and demanded the Chief Election Commissioner's resignation.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>The Election Commission, however, has asserted that its official orders, decisions and administrative directions have full legal sanction, and that differing views and observations are a normal part of deliberations within any institution.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/delhi/aap-protests-outside-delhi-ceo-office-over-sir-seeks-gyanesh-kumars-resignation-4173541</t>
+          <t>https://theprint.in/india/karnataka-cong-protests-against-sir-demands-cec-gyanesh-kumars-resignation-2/3054130/</t>
         </is>
       </c>
     </row>
@@ -22880,22 +22950,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>INDIA bloc; Chief Electoral Officer, Delhi; Congress; Police</t>
+          <t>Congress; Police</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Protest and march; Deletions</t>
+          <t>Protest and march</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -22905,49 +22980,44 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>The Tribune</t>
+          <t>ThePrint (Press Trust of India)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>The Tribune reported that Delhi leaders of the INDIA bloc marched to the Election Commission office and gave the Delhi Chief Electoral Officer a memorandum demanding that the SIR be cancelled and excluded eligible voters be restored. It said police detained Delhi Congress president Devender Yadav at a separate protest at Jantar Mantar.</t>
+          <t>ThePrint, carrying a PTI report, said police used water cannons and detained former Chief Minister Ashok Gehlot and state Congress chief Govind Singh Dotasra during a march to the State Election Commission office in Jaipur over alleged SIR irregularities.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/delhi/india-bloc-leaders-march-to-ec-office-in-delhi-seek-rollback-of-sir/</t>
+          <t>https://theprint.in/india/gehlot-dotasra-detained-during-cong-protest-in-jaipur-over-sir-row/3055754/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Booth officers' protests</t>
+          <t>Protests by parties and groups</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kerala</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Kannur</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Booth level officers; Teachers' unions; Chief Electoral Officer, Kerala</t>
+          <t>INDIA bloc; Congress; Election Commission</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BLO workload; Deaths; Protest and march</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -22957,49 +23027,49 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>The News Minute</t>
+          <t>The Wire</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>The News Minute reported that hundreds of booth level officers across Kerala stayed away from SIR work on a strike call after the death of a BLO in Kannur, and that employee and teacher action councils marched to collectorates.</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>The News Minute reported that Kerala's Chief Electoral Officer said he had not received any complaints regarding work pressure from BLOs.</t>
+          <t>Leaders of the INDIA bloc, 33 of them from 19 parties, agreed a plan of district marches from 2 to 8 October, a march of opposition MPs to the Commission on 6 October, a meeting with the President in the second week of October and five rallies including one in Delhi on 1 November, The Wire reported. Congress president Mallikarjun Kharge said the Commission was being used as a puppet by the Prime Minister and the Home Minister.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/kerala/officers-suicide-blos-across-kerala-boycott-sir-work-citing-deadline-stress</t>
+          <t>https://m.thewire.in/article/politics/ec-played-like-a-puppet-india-bloc-seals-roadmap-to-ramp-up-anti-sir-agitation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Booth officers' protests</t>
+          <t>Protests by parties and groups</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Federation of Revenue Associations of Tamil Nadu</t>
+          <t>Civil society groups</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BLO workload; Schedule and deadlines; Protest and march</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -23009,49 +23079,49 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Deccan Herald (Press Trust of India)</t>
+          <t>The South First</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Deccan Herald, carrying a PTI report, said the Federation of Revenue Associations of Tamil Nadu began a statewide boycott of SIR work over workload, staff shortages, deadline pressure and poor training.</t>
+          <t>The South First reported that more than a dozen civil society groups held a day-long protest at Dharna Chowk in Hyderabad, demanding that the SIR be scrapped and the Chief Election Commissioner resign.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/tamil-nadu/tamil-nadu-revenue-employees-association-begin-boycott-of-sir-work-3801680</t>
+          <t>https://thesouthfirst.com/telangana/attempt-to-kill-democracy-hyderabad-civil-society-protests-sir-demands-cec-gyanesh-kumars-resignation/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Booth officers' protests</t>
+          <t>Protests by parties and groups</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BLO Adhikar Raksha Committee; Police; Chief Electoral Officer, West Bengal</t>
+          <t>Shiv Sena (UBT); MNS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>BLO workload; Protest and march</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -23061,54 +23131,44 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Deccan Herald (Press Trust of India)</t>
+          <t>Free Press Journal</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Deccan Herald, carrying a PTI report, said booth level officers marching under the BLO Adhikar Raksha Committee clashed with police outside the West Bengal Chief Electoral Officer's office in Kolkata over SIR workload.</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Deccan Herald reported that Chief Electoral Officer Manoj Agarwal described the BLOs as the "real heroes" of the exercise.</t>
+          <t>The Free Press Journal reported that Uddhav Thackeray of the Shiv Sena (UBT) and Raj Thackeray of the MNS led the Virat Garjana Morcha in Mumbai seeking the Chief Election Commissioner's resignation. Raj Thackeray demanded that the SIR in Maharashtra be cancelled.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/west-bengal/blos-protest-outside-bengal-ceos-office-over-excessive-work-pressure-ec-calls-them-real-heroes-3808529</t>
+          <t>https://www.freepressjournal.in/mumbai/garjana-morcha-uddhav-raj-thackeray-lead-protest-seeking-gyanesh-kumars-resignation-scrapping-of-maharashtra-sir</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Booth officers' protests</t>
+          <t>Protests by parties and groups</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gujarat</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Ahmedabad</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Booth level officers; Teachers' unions</t>
+          <t>INDIA bloc; Congress; Police</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>BLO workload; Protest and march</t>
+          <t>Protest and march; Police and FIRs</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -23123,39 +23183,44 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>The Wire reported that nearly 250 primary school teachers working as booth level officers stopped work and held a sit-in at a data uploading centre in Ahmedabad, alleging threats and pressure during the SIR.</t>
+          <t>The Wire reported that police stopped an INDIA bloc march from Parliament to the Election Commission, and that opposition MPs held a sit-in at the All India Radio building until police detained Rahul Gandhi and Priyanka Gandhi Vadra that night.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://thewire.in/government/ahmedabad-250-blos-stage-protest-citing-threats-pressure-abuse-and-late-night-calls</t>
+          <t>https://thewire.in/politics/india-bloc-opposition-parties-march-nirvachan-sadan-election-commission-rahul-gandhi</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Booth officers' protests</t>
+          <t>Protests by parties and groups</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Uttar Pradeshiya Prathmik Shikshak Sangh; Teachers' unions</t>
+          <t>INDIA bloc; Election Commission</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Deaths; BLO workload</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -23165,44 +23230,49 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Amar Ujala</t>
+          <t>Deccan Herald</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Amar Ujala reported that teachers' organisations in Uttar Pradesh, among them the Uttar Pradeshiya Prathmik Shikshak Sangh, objected to the deaths of teachers and staff on SIR duty and demanded jobs and compensation for their families.</t>
+          <t>Opposition MPs of the INDIA bloc marched from Parliament to the Commission's headquarters to press for the Chief Election Commissioner's removal, and asked for 240 MPs to meet the three Commissioners at Parliament House Annexe, Deccan Herald reported.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>The Commission said no party had sought an appointment until 4 pm, that a meeting of 240 MPs away from its premises was unusual and could not be accepted, and that the MPs declined its offer to send its senior-most officer on duty to receive their memorandum, Deccan Herald reported.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/lucknow/up-teachers-organizations-angry-over-the-deaths-of-blos-opened-a-front-the-teacher-made-a-video-saying-2025-12-01</t>
+          <t>https://www.deccanherald.com/india/cec-row-ec-refuses-oppositions-demand-for-meeting-4172987</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Form 7 objections and pre-printed forms</t>
+          <t>Protests by parties and groups</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025-07-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Election Commission; Booth level officers</t>
+          <t>AAP; Chief Electoral Officer, Delhi</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-printed forms</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -23212,49 +23282,44 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>Deccan Herald (Press Trust of India)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported the Commission saying that about 87 per cent of Bihar's 7.96 crore voters had been given semi-filled enumeration forms on the first booth officer visit.</t>
+          <t>Deccan Herald, carrying a PTI report, said AAP workers and members of other parties protested outside the Delhi Chief Electoral Officer's office demanding the Chief Election Commissioner's resignation over alleged SIR irregularities. It said AAP had earlier protested at Jantar Mantar and India Gate.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://deccanchronicle.com/nation/bihar-voter-roll-revision-semi-filled-forms-distributed-to-87-voters-1889439</t>
+          <t>https://www.deccanherald.com/india/delhi/aap-protests-outside-delhi-ceo-office-over-sir-seeks-gyanesh-kumars-resignation-4173541</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Form 7 objections and pre-printed forms</t>
+          <t>Protests by parties and groups</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bihar</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADR; Election Commission</t>
+          <t>INDIA bloc; Chief Electoral Officer, Delhi; Congress; Police</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-printed forms; Software (ECINET/ERONET)</t>
+          <t>Protest and march; Deletions</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -23264,54 +23329,49 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>LiveLaw</t>
+          <t>The Tribune</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>LiveLaw reported that the Association for Democratic Reforms told the Supreme Court that enumeration forms in Bihar were being uploaded by officials without voters' knowledge or consent. This is ADR's allegation in a court filing.</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>LiveLaw reported that ADR filed the rejoinder in reply to the Commission's counter-affidavit.</t>
+          <t>The Tribune reported that Delhi leaders of the INDIA bloc marched to the Election Commission office and gave the Delhi Chief Electoral Officer a memorandum demanding that the SIR be cancelled and excluded eligible voters be restored. It said police detained Delhi Congress president Devender Yadav at a separate protest at Jantar Mantar.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://www.livelaw.in/top-stories/bihar-sir-blos-mass-uploading-enumeration-forms-without-voters-knowledge-or-consent-adr-tells-supreme-court-298898</t>
+          <t>https://www.tribuneindia.com/news/delhi/india-bloc-leaders-march-to-ec-office-in-delhi-seek-rollback-of-sir/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Form 7 objections and pre-printed forms</t>
+          <t>Protests by parties and groups</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bankura; Khatra; Asansol</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Trinamool Congress; BJP; Police</t>
+          <t>INDIA bloc; Congress; Election Commission</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms; Police and FIRs</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -23321,49 +23381,54 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>National Herald</t>
+          <t>Daily Excelsior (PTI)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>National Herald reported that Trinamool workers stopped a vehicle in Khatra, Bankura said to carry thousands of pre-filled Form 7s, that police seized it and began an inquiry, and that both parties traded allegations over bulk Form 7s on the last day for filing.</t>
+          <t>An INDIA bloc delegation including Mallikarjun Kharge and Rahul Gandhi gave President Droupadi Murmu a memorandum after opposition MPs marched from Parliament House and were stopped by police at Vijay Chowk, PTI reported. Kharge said the President had asked for evidence, which the bloc would provide, and Rahul Gandhi said she had not denied what they told her and that the leaders would meet the Chief Justice on Monday. The News Mill reported that the memorandum asked for the Chief Election Commissioner's resignation, repeal of the 2023 law on the Commissioners, suspension of the SIR with the names the bloc says were removed illegally restored, a return to paper ballots, and annulment of Assembly elections of the past two years where it said evidence of vote theft had been presented. These are the INDIA bloc's demands and allegations.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>National Herald reported that the BJP alleged its workers were attacked and prevented from filing forms inside government offices.</t>
+          <t>No response from Rashtrapati Bhavan or the Commission to the memorandum was reported.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://www.nationalheraldindia.com/politics/form-7-flashpoint-bengal-sees-clashes-rival-claims-of-voter-roll-sabotage</t>
+          <t>https://www.dailyexcelsior.com/india-bloc-hands-over-memorandum-on-vote-chori-to-president-murmu-says-she-didnt-deny-charge/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Form 7 objections and pre-printed forms</t>
+          <t>Protests by parties and groups</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Congress; BJP</t>
+          <t>Cockroach Janta Party; CPI(M); Police</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms</t>
+          <t>Protest and march; Commission's independence</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -23373,54 +23438,54 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>The South First</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Scroll reported that Rajasthan Congress president Govind Singh Dotasra alleged that computer-printed Form 7s were distributed in every constituency and that booth agents' signatures were forged, and demanded a forensic inquiry. These are the Congress's allegations.</t>
+          <t>The South First reported on the morning of 10 October that police sealed central Delhi before the Cockroach Janta Party's protest at Jantar Mantar demanding the Chief Election Commissioner's resignation over the SIR. It said more than 1,000 people had been detained overnight and 45 Metro stations were shut, and that police detained CPI(M) leaders including Pinarayi Vijayan and John Brittas when they tried to march from Kerala House.</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Scroll reported that BJP minister Gautam Dak said a voter proposed for removal gets time to be heard and that the Congress wanted to create a dispute.</t>
+          <t>No statement from the Commission was reported. Police told the protesters that a gathering of more than four people was not allowed.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://scroll.in/latest/1090094/scroll_in</t>
+          <t>https://thesouthfirst.com/beyond-south/cockroach-janta-party-protest-new-delhi-sealed-even-before-the-first-slogan/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Form 7 objections and pre-printed forms</t>
+          <t>Booth officers' protests</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Karimganj North; Nagaon</t>
+          <t>Kannur</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Election Commission; Booth level officers</t>
+          <t>Booth level officers; Teachers' unions; Chief Electoral Officer, Kerala</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms; Notices and hearings</t>
+          <t>BLO workload; Deaths; Protest and march</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -23430,49 +23495,49 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>The News Minute</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Scroll reported that during Assam's Special Revision a booth officer in Karimganj North was handed objections against 133 voters on forms she described as half printed and half handwritten, and that hearings were suspended in three Nagaon constituencies after complaints of fake Form 7s.</t>
+          <t>The News Minute reported that hundreds of booth level officers across Kerala stayed away from SIR work on a strike call after the death of a BLO in Kannur, and that employee and teacher action councils marched to collectorates.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Scroll quoted a senior Commission official in Guwahati saying a voter can file any number of objections but that an ERO reviews them individually when one person files more than five.</t>
+          <t>The News Minute reported that Kerala's Chief Electoral Officer said he had not received any complaints regarding work pressure from BLOs.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://scroll.in/article/1090187/scroll_in</t>
+          <t>https://www.thenewsminute.com/kerala/officers-suicide-blos-across-kerala-boycott-sir-work-citing-deadline-stress</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Form 7 objections and pre-printed forms</t>
+          <t>Booth officers' protests</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BJP; Election Commission</t>
+          <t>Federation of Revenue Associations of Tamil Nadu</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Form 7</t>
+          <t>BLO workload; Schedule and deadlines; Protest and march</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -23482,49 +23547,49 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>Deccan Herald (Press Trust of India)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Scroll reported that at least seven people named as objectors on Form 7s in Assam, some of them BJP booth agents and members, said they had not filed the objections.</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Scroll quoted BJP MP Kamakhya Prasad Tasa as saying anyone can file objections and that it is for the Election Commission to take a final call.</t>
+          <t>Deccan Herald, carrying a PTI report, said the Federation of Revenue Associations of Tamil Nadu began a statewide boycott of SIR work over workload, staff shortages, deadline pressure and poor training.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://scroll.in/article/1090212/bjp-workers-in-assam-say-their-names-used-to-seek-mass-voter-deletion-without-their-knowledge</t>
+          <t>https://www.deccanherald.com/india/tamil-nadu/tamil-nadu-revenue-employees-association-begin-boycott-of-sir-work-3801680</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Form 7 objections and pre-printed forms</t>
+          <t>Booth officers' protests</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BJP; Government of Assam</t>
+          <t>BLO Adhikar Raksha Committee; Police; Chief Electoral Officer, West Bengal</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Form 7</t>
+          <t>BLO workload; Protest and march</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -23534,49 +23599,54 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>Deccan Herald (Press Trust of India)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>The Indian Express reported that Assam Chief Minister Himanta Biswa Sarma told reporters he had told BJP members to keep filing complaints against people he called 'Miyas' and to fill Form 7s wherever possible during the Special Revision.</t>
+          <t>Deccan Herald, carrying a PTI report, said booth level officers marching under the BLO Adhikar Raksha Committee clashed with police outside the West Bengal Chief Electoral Officer's office in Kolkata over SIR workload.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Deccan Herald reported that Chief Electoral Officer Manoj Agarwal described the BLOs as the "real heroes" of the exercise.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/bjp-complaints-against-miyas-practice-politics-of-polarisation-assam-cm-himanta-10498937/</t>
+          <t>https://www.deccanherald.com/india/west-bengal/blos-protest-outside-bengal-ceos-office-over-excessive-work-pressure-ec-calls-them-real-heroes-3808529</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Form 7 objections and pre-printed forms</t>
+          <t>Booth officers' protests</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Bhopal; Bhopal South-West</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>District Election Officer</t>
+          <t>Booth level officers; Teachers' unions</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Form 7</t>
+          <t>BLO workload; Protest and march</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23586,49 +23656,44 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ETV Bharat</t>
+          <t>The Wire</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>ETV Bharat reported that Bhopal's Collector ordered a probe after a man named as objector on Form 7s in Bhopal South-West denied filing them, and that officials found incorrect or fake objector details in several of the district's 9,037 Form 7s.</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>ETV Bharat quoted District Election Officer Kaushlendra Vikram Singh saying no one's name would be removed without verification.</t>
+          <t>The Wire reported that nearly 250 primary school teachers working as booth level officers stopped work and held a sit-in at a data uploading centre in Ahmedabad, alleging threats and pressure during the SIR.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/state/fake-objections-filed-to-delete-voter-names-in-bhopal-probe-ordered-enn26013005659</t>
+          <t>https://thewire.in/government/ahmedabad-250-blos-stage-protest-citing-threats-pressure-abuse-and-late-night-calls</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Form 7 objections and pre-printed forms</t>
+          <t>Booth officers' protests</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Congress; Election Commission; ADR</t>
+          <t>Uttar Pradeshiya Prathmik Shikshak Sangh; Teachers' unions</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Form 7</t>
+          <t>Deaths; BLO workload</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23638,22 +23703,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Frontline</t>
+          <t>Amar Ujala</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Frontline reported that Congress general secretary K. C. Venugopal wrote to the Commission on 29 January alleging misuse of Form 7 in several states, and that the Commission said there was no limit on forms per voter but that an ERO must verify when one person files more than five.</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Scroll reported on 23 January 2026 that a senior Commission official in Guwahati gave the same rule.</t>
+          <t>Amar Ujala reported that teachers' organisations in Uttar Pradesh, among them the Uttar Pradeshiya Prathmik Shikshak Sangh, objected to the deaths of teachers and staff on SIR duty and demanded jobs and compensation for their families.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://frontline.thehindu.com/politics/form-seven-voter-deletion-india-election-commission-bjp/article70582295.ece</t>
+          <t>https://www.amarujala.com/lucknow/up-teachers-organizations-angry-over-the-deaths-of-blos-opened-a-front-the-teacher-made-a-video-saying-2025-12-01</t>
         </is>
       </c>
     </row>
@@ -23665,22 +23725,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BJP; Government of Assam</t>
+          <t>Election Commission; Booth level officers</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Form 7; Deletions</t>
+          <t>Pre-printed forms</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -23690,17 +23750,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Scroll (PTI)</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Scroll reported, citing PTI, that after Assam's final roll the Chief Minister said several deletions had been made on complaints filed by BJP workers.</t>
+          <t>Deccan Chronicle reported the Commission saying that about 87 per cent of Bihar's 7.96 crore voters had been given semi-filled enumeration forms on the first booth officer visit.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://scroll.in/latest/1090665/scroll_in</t>
+          <t>https://deccanchronicle.com/nation/bihar-voter-roll-revision-semi-filled-forms-distributed-to-87-voters-1889439</t>
         </is>
       </c>
     </row>
@@ -23712,27 +23772,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gujarat</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Gir Somnath; Somnath</t>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>District Election Officer</t>
+          <t>ADR; Election Commission</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms</t>
+          <t>Pre-printed forms; Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -23742,22 +23802,22 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Newslaundry</t>
+          <t>LiveLaw</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Newslaundry reported that the 15,663 Form 7s in Somnath were filed by 269 people, each filing 50 or more, that copies it reviewed had the voter's details printed in English and the objector's details handwritten in Gujarati, and that six of the objectors filed affidavits saying they had not filed them.</t>
+          <t>LiveLaw reported that the Association for Democratic Reforms told the Supreme Court that enumeration forms in Bihar were being uploaded by officials without voters' knowledge or consent. This is ADR's allegation in a court filing.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Newslaundry reported that the District Election Officer, V. N. Upadhyay, said he had deployed six AEROs to verify the objections and assured that no name would be deleted arbitrarily.</t>
+          <t>LiveLaw reported that ADR filed the rejoinder in reply to the Commission's counter-affidavit.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://newslaundry.com/2026/02/11/inside-the-organised-attempt-to-delete-15000-voters-in-gujarats-somnath</t>
+          <t>https://www.livelaw.in/top-stories/bihar-sir-blos-mass-uploading-enumeration-forms-without-voters-knowledge-or-consent-adr-tells-supreme-court-298898</t>
         </is>
       </c>
     </row>
@@ -23769,27 +23829,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Alwar</t>
+          <t>Bankura; Khatra; Asansol</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BJP; District Election Officer</t>
+          <t>Trinamool Congress; BJP; Police</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Form 7; Police and FIRs</t>
+          <t>Form 7; Pre-printed forms; Police and FIRs</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -23799,22 +23859,22 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>The Quint</t>
+          <t>National Herald</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>The Quint reported that thousands of Form 7s in Alwar were filed in the names of BJP booth agents, several of whom said their signatures were forged, and that no FIR or inquiry had been announced a month later.</t>
+          <t>National Herald reported that Trinamool workers stopped a vehicle in Khatra, Bankura said to carry thousands of pre-filled Form 7s, that police seized it and began an inquiry, and that both parties traded allegations over bulk Form 7s on the last day for filing.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>The Quint reported that calls to the District Magistrate and Sub-Divisional Magistrate for comment went unanswered.</t>
+          <t>National Herald reported that the BJP alleged its workers were attacked and prevented from filing forms inside government offices.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://www.thequint.com/elections/muslim-voters-alwar-rolls-ec-probe-avoidance</t>
+          <t>https://www.nationalheraldindia.com/politics/form-7-flashpoint-bengal-sees-clashes-rival-claims-of-voter-roll-sabotage</t>
         </is>
       </c>
     </row>
@@ -23826,22 +23886,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Election Commission; Chief Electoral Officer, West Bengal; Electoral Registration Officer</t>
+          <t>Congress; BJP</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Form 7; Schedule and deadlines</t>
+          <t>Form 7; Pre-printed forms</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -23851,17 +23911,22 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>National Herald</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>National Herald reported that the Commission wrote to West Bengal's Chief Electoral Officer to send all Form 7 objections to EROs by 16 February and dispose of them by statutory procedure, and that it had taken cognisance of reports of Form 7 records being burnt.</t>
+          <t>Scroll reported that Rajasthan Congress president Govind Singh Dotasra alleged that computer-printed Form 7s were distributed in every constituency and that booth agents' signatures were forged, and demanded a forensic inquiry. These are the Congress's allegations.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Scroll reported that BJP minister Gautam Dak said a voter proposed for removal gets time to be heard and that the Congress wanted to create a dispute.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://www.nationalheraldindia.com/politics/form-7-controversy-deepens-strain-on-sir-phase-2</t>
+          <t>https://scroll.in/latest/1090094/scroll_in</t>
         </is>
       </c>
     </row>
@@ -23873,27 +23938,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Shamli</t>
+          <t>Karimganj North; Nagaon</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>District Election Officer; Booth level officers</t>
+          <t>Election Commission; Booth level officers</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms</t>
+          <t>Form 7; Pre-printed forms; Notices and hearings</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -23903,22 +23968,22 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Siasat (citing The Indian Express)</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Siasat reported, citing The Indian Express, that Form 7s against 544 voters of a Shamli village were found with a booth officer, said to have been already printed with the voters' EPIC numbers, and that the District Magistrate said the forms were fake and the probe found nothing.</t>
+          <t>Scroll reported that during Assam's Special Revision a booth officer in Karimganj North was handed objections against 133 voters on forms she described as half printed and half handwritten, and that hearings were suspended in three Nagaon constituencies after complaints of fake Form 7s.</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>DM Arvind Kumar Chauhan ordered a probe and later said that the case “didn’t have any substance.” “We got an investigation done and found nothing,” he added.</t>
+          <t>Scroll quoted a senior Commission official in Guwahati saying a voter can file any number of objections but that an ERO reviews them individually when one person files more than five.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/sir-544-muslim-voters-marked-for-deletion-in-up-village-leads-to-one-man-3438394/</t>
+          <t>https://scroll.in/article/1090187/scroll_in</t>
         </is>
       </c>
     </row>
@@ -23930,32 +23995,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gujarat</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Kodinar; Sidhpur</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Gujarat High Court</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Election Commission; Government of Gujarat</t>
+          <t>BJP; Election Commission</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Form 7; Police and FIRs</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -23965,22 +24020,22 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Deccan Herald</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Deccan Herald reported that the Gujarat High Court issued notice to the Commission and the state on two petitions seeking a Special Investigation Team inquiry into Form 7 objections filed during the SIR.</t>
+          <t>Scroll reported that at least seven people named as objectors on Form 7s in Assam, some of them BJP booth agents and members, said they had not filed the objections.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Deccan Herald reported that the matter was posted for further hearing on 7 July.</t>
+          <t>Scroll quoted BJP MP Kamakhya Prasad Tasa as saying anyone can file objections and that it is for the Election Commission to take a final call.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/gujarat/petitions-seek-investigation-into-thousands-of-fake-objection-pleas-during-sir-gujarat-high-court-issues-notice-3996966</t>
+          <t>https://scroll.in/article/1090212/bjp-workers-in-assam-say-their-names-used-to-seek-mass-voter-deletion-without-their-knowledge</t>
         </is>
       </c>
     </row>
@@ -23992,27 +24047,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>District Election Officer</t>
+          <t>BJP; Government of Assam</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-printed forms; Documents and declaration</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -24022,17 +24072,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported Hyderabad's District Election Officer R. V. Karnan explaining that booth officers would hand out enumeration forms already printed with each elector's details and photograph, which the elector completes and signs.</t>
+          <t>The Indian Express reported that Assam Chief Minister Himanta Biswa Sarma told reporters he had told BJP members to keep filing complaints against people he called 'Miyas' and to fill Form 7s wherever possible during the Special Revision.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/southern-states/telangana/enumeration-form-must-for-draft-electoral-roll-1965489</t>
+          <t>https://indianexpress.com/article/india/bjp-complaints-against-miyas-practice-politics-of-polarisation-assam-cm-himanta-10498937/</t>
         </is>
       </c>
     </row>
@@ -24044,27 +24094,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bhopal; Bhopal South-West</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BJP; AIMIM; Booth level officers; Chief Electoral Officer, Telangana</t>
+          <t>District Election Officer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-printed forms; Duplicates and errors</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -24074,17 +24124,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>ETV Bharat</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported that the Telangana BJP alleged to the Chief Electoral Officer that booth officers in Hyderabad were handing enumeration forms in bulk to AIMIM leaders at party camps and letting them upload filled forms. This is the BJP's allegation.</t>
+          <t>ETV Bharat reported that Bhopal's Collector ordered a probe after a man named as objector on Form 7s in Bhopal South-West denied filing them, and that officials found incorrect or fake objector details in several of the district's 9,037 Form 7s.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>ETV Bharat quoted District Election Officer Kaushlendra Vikram Singh saying no one's name would be removed without verification.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/southern-states/telangana/bjp-lodges-complaint-against-officials-allegedly-favouring-aimim-1969157</t>
+          <t>https://www.etvbharat.com/en/state/fake-objections-filed-to-delete-voter-names-in-bhopal-probe-ordered-enn26013005659</t>
         </is>
       </c>
     </row>
@@ -24096,27 +24151,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Rangareddy; Serilingampally</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BJP; Booth level officers; Chief Electoral Officer, Telangana</t>
+          <t>Congress; Election Commission; ADR</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Duplicates and errors</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -24126,17 +24176,22 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>Frontline</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported that the BJP alleged that some booth officers in Serilingampally uploaded the blank back of enumeration forms to the Commission's app without the voter's details, and asked the Chief Electoral Officer for a probe. This is the BJP's allegation.</t>
+          <t>Frontline reported that Congress general secretary K. C. Venugopal wrote to the Commission on 29 January alleging misuse of Form 7 in several states, and that the Commission said there was no limit on forms per voter but that an ERO must verify when one person files more than five.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Scroll reported on 23 January 2026 that a senior Commission official in Guwahati gave the same rule.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/southern-states/telangana/sir-bjp-urges-ceo-to-conduct-probe-into-allegations-1975019</t>
+          <t>https://frontline.thehindu.com/politics/form-seven-voter-deletion-india-election-commission-bjp/article70582295.ece</t>
         </is>
       </c>
     </row>
@@ -24148,32 +24203,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Hata; Kushinagar; Khalilabad</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Congress</t>
+          <t>BJP; Government of Assam</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Form 7</t>
+          <t>Form 7; Deletions</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -24183,17 +24228,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Scroll (PTI)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>The Hindu reported that the Supreme Court agreed to consider an application by Congress MP Tanuj Punia alleging that Form 7 objections in the Uttar Pradesh SIR were filed with false particulars, forged signatures and in the names of people who later denied filing them. The application cited one person filing objections against 32 electors in Hata, Kushinagar, and a UP Congress claim of 700 to 800 objections in four Khalilabad booths.</t>
+          <t>Scroll reported, citing PTI, that after Assam's final roll the Chief Minister said several deletions had been made on complaints filed by BJP workers.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/uttar-pradesh/form-7-misuse-supreme-court-to-consider-congress-mps-plea-alleging-targeted-deletions-in-up/article71314187.ece</t>
+          <t>https://scroll.in/latest/1090665/scroll_in</t>
         </is>
       </c>
     </row>
@@ -24205,22 +24250,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Gir Somnath; Somnath</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Congress; Chief Electoral Officer, Uttarakhand</t>
+          <t>District Election Officer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Form 7</t>
+          <t>Form 7; Pre-printed forms</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -24230,22 +24280,22 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>The Pioneer</t>
+          <t>Newslaundry</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>The Pioneer reported that an Uttarakhand Congress delegation told the Chief Electoral Officer that one person had filed objections against about 6,400 voters and about 1,200 people had filed more than ten each. These are the Congress's figures.</t>
+          <t>Newslaundry reported that the 15,663 Form 7s in Somnath were filed by 269 people, each filing 50 or more, that copies it reviewed had the voter's details printed in English and the objector's details handwritten in Gujarati, and that six of the objectors filed affidavits saying they had not filed them.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>The Pioneer reported that CEO V. V. R. C. Purushottam said the revision followed the rules and that observers had been sent to districts with many objections, and that Additional CEO Vijay Kumar Jogdande said an ERO must scrutinise cases where one person seeks to remove more than five names.</t>
+          <t>Newslaundry reported that the District Election Officer, V. N. Upadhyay, said he had deployed six AEROs to verify the objections and assured that no name would be deleted arbitrarily.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://dailypioneer.com/news/uttarakhand-congress-alleges-form-7-misuse-to-delete-voters-during-sir-approaches-ec</t>
+          <t>https://newslaundry.com/2026/02/11/inside-the-organised-attempt-to-delete-15000-voters-in-gujarats-somnath</t>
         </is>
       </c>
     </row>
@@ -24257,22 +24307,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Haridwar; Jhabrera</t>
+          <t>Alwar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BJP; Electoral Registration Officer; Election Commission</t>
+          <t>BJP; District Election Officer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -24287,22 +24337,22 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Newslaundry</t>
+          <t>The Quint</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Newslaundry reported that 35 people named as objectors on 1,657 Form 7s in Jhabrera, 31 of them BJP booth agents, said in affidavits that their names, EPIC numbers and signatures had been misused.</t>
+          <t>The Quint reported that thousands of Form 7s in Alwar were filed in the names of BJP booth agents, several of whom said their signatures were forged, and that no FIR or inquiry had been announced a month later.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Newslaundry quoted the Jhabrera ERO saying the objections were cancelled after those named sought to withdraw them and the voters would not be deleted, and that the Election Commission would not order any investigation and those whose names were misused should file an FIR.</t>
+          <t>The Quint reported that calls to the District Magistrate and Sub-Divisional Magistrate for comment went unanswered.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://www.newslaundry.com/2026/08/28/exclusive-bjp-agents-identities-misused-to-file-mass-objections-against-haridwars-muslim-voters</t>
+          <t>https://www.thequint.com/elections/muslim-voters-alwar-rolls-ec-probe-avoidance</t>
         </is>
       </c>
     </row>
@@ -24314,27 +24364,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Election Commission; Congress; BJP; AIMIM</t>
+          <t>Election Commission; Chief Electoral Officer, West Bengal; Electoral Registration Officer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Form 7; Transparency of lists</t>
+          <t>Form 7; Schedule and deadlines</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -24344,22 +24389,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>National Herald</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported, in a story datelined Hyderabad that does not say whether the figure covers the state or the district, that the Commission had received close to 50,000 Form 7 applications against entries in the draft roll, and that parties at a meeting chaired by Hyderabad's District Election Officer asked for the Form 10 lists by Assembly constituency.</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Deccan Chronicle reported that officials gave parties the total number of applications at a meeting at the GHMC office but did not share figures by Assembly constituency.</t>
+          <t>National Herald reported that the Commission wrote to West Bengal's Chief Electoral Officer to send all Form 7 objections to EROs by 16 February and dispose of them by statutory procedure, and that it had taken cognisance of reports of Form 7 records being burnt.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/southern-states/telangana/50000-forms-filed-seeking-deletion-of-votes-1984663</t>
+          <t>https://www.nationalheraldindia.com/politics/form-7-controversy-deepens-strain-on-sir-phase-2</t>
         </is>
       </c>
     </row>
@@ -24371,22 +24411,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Shamli</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BJP</t>
+          <t>District Election Officer; Booth level officers</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Form 7; Minorities</t>
+          <t>Form 7; Pre-printed forms</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -24396,17 +24441,22 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Newslaundry</t>
+          <t>Siasat (citing The Indian Express)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Newslaundry reported from its investigation in Uttarakhand that numerous applications were filed to remove Muslim voters from the rolls, many in the names of people it said were associated with the BJP. It reported that some people named as objectors later filed affidavits saying they had never filed the objections and that their names, EPIC numbers and signatures had been used fraudulently.</t>
+          <t>Siasat reported, citing The Indian Express, that Form 7s against 544 voters of a Shamli village were found with a booth officer, said to have been already printed with the voters' EPIC numbers, and that the District Magistrate said the forms were fake and the probe found nothing.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>DM Arvind Kumar Chauhan ordered a probe and later said that the case “didn’t have any substance.” “We got an investigation done and found nothing,” he added.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://www.newslaundry.com/2026/09/09/uttarakhand-sir-who-is-targeting-muslim-voters</t>
+          <t>https://www.siasat.com/sir-544-muslim-voters-marked-for-deletion-in-up-village-leads-to-one-man-3438394/</t>
         </is>
       </c>
     </row>
@@ -24418,27 +24468,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Karol Bagh; Patel Nagar; Sangam Vihar</t>
+          <t>Kodinar; Sidhpur</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Gujarat High Court</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Election Commission; Government of Gujarat</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Form 7; Software (ECINET/ERONET)</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -24448,22 +24503,22 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Deccan Herald</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>The Hindu reported that Form 10 lists published for 21 to 27 September showed four people in Delhi filing more than ten applications a day through the Commission's ECINET portal, which does not enforce the limit of ten a day for booth agents.</t>
+          <t>Deccan Herald reported that the Gujarat High Court issued notice to the Commission and the state on two petitions seeking a Special Investigation Team inquiry into Form 7 objections filed during the SIR.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>The Hindu reported that the office of Delhi's Chief Electoral Officer did not respond to a request for comment.</t>
+          <t>Deccan Herald reported that the matter was posted for further hearing on 7 July.</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/Delhi/party-appointed-blas-bypass-eci-cap-for-10-applications-a-day-through-its-own-portal-for-deletions/article71524945.ece</t>
+          <t>https://www.deccanherald.com/india/gujarat/petitions-seek-investigation-into-thousands-of-fake-objection-pleas-during-sir-gujarat-high-court-issues-notice-3996966</t>
         </is>
       </c>
     </row>
@@ -24475,27 +24530,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Babaleshwar</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Congress; Civil society groups; Chief Electoral Officer, Karnataka</t>
+          <t>District Election Officer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms; Minorities</t>
+          <t>Pre-printed forms; Documents and declaration</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -24505,22 +24560,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>The Hindu reported that as of September 28, 4,000 Form 7 applications seeking deletion of names had been filed in Karnataka, which it said mostly targeted Muslim voters. It reported that ten people filed Form 7s seeking deletion of 1,363 names in Babaleshwar in one day, often on forms with the voters' details already printed and only the objector's name handwritten. Civil society groups and the Karnataka Congress demanded that the Commission lodge criminal complaints.</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>V. Anbukumar, CEO, Karnataka, was not available for comment.</t>
+          <t>Deccan Chronicle reported Hyderabad's District Election Officer R. V. Karnan explaining that booth officers would hand out enumeration forms already printed with each elector's details and photograph, which the elector completes and signs.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/civil-society-groups-congress-demand-firs-over-bulk-form-7s-seeking-deletion-of-names/article71524777.ece</t>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/enumeration-form-must-for-draft-electoral-roll-1965489</t>
         </is>
       </c>
     </row>
@@ -24532,7 +24582,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -24547,12 +24597,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Telangana</t>
+          <t>BJP; AIMIM; Booth level officers; Chief Electoral Officer, Telangana</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Form 7</t>
+          <t>Pre-printed forms; Duplicates and errors</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -24562,17 +24612,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Telangana Today</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Telangana Today reported that the Chief Electoral Officer, C. Sudharshan Reddy, said 28,753 Form 7 applications had been filed in Telangana, about 5,000 of them in Hyderabad, and that forms received in bulk would be examined with special care.</t>
+          <t>Deccan Chronicle reported that the Telangana BJP alleged to the Chief Electoral Officer that booth officers in Hyderabad were handing enumeration forms in bulk to AIMIM leaders at party camps and letting them upload filled forms. This is the BJP's allegation.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://telanganatoday.com/nearly-29000-form-7-applications-filed-during-telangana-sir</t>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/bjp-lodges-complaint-against-officials-allegedly-favouring-aimim-1969157</t>
         </is>
       </c>
     </row>
@@ -24584,7 +24634,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -24594,17 +24644,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Hyderabad; Musheerabad</t>
+          <t>Rangareddy; Serilingampally</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Congress; BJP; Chief Electoral Officer, Telangana</t>
+          <t>BJP; Booth level officers; Chief Electoral Officer, Telangana</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms</t>
+          <t>Software (ECINET/ERONET); Duplicates and errors</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -24614,22 +24664,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Siasat</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Siasat reported that the Telangana Congress complained to the Chief Electoral Officer that a BJP booth agent in Musheerabad had filed Form 7 applications against a Congress booth agent and about 30 members of his family, on forms that were printed in advance. This is the Congress's allegation.</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Siasat reported that the Congress asked for an investigation to establish the facts, including a forensic examination of whether the forms came from a common source.</t>
+          <t>Deccan Chronicle reported that the BJP alleged that some booth officers in Serilingampally uploaded the blank back of enumeration forms to the Commission's app without the voter's details, and asked the Chief Electoral Officer for a probe. This is the BJP's allegation.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/telangana-sir-congress-alleges-vote-deletion-bid-in-musheerabad-3551155/</t>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/sir-bjp-urges-ceo-to-conduct-probe-into-allegations-1975019</t>
         </is>
       </c>
     </row>
@@ -24641,27 +24686,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hata; Kushinagar; Khalilabad</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Election Commission; Electoral Registration Officer</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Form 7; Police and FIRs</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -24671,17 +24721,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>The New Indian Express reported that the Commission wrote to election officials in Bengaluru that bulk Form 7 applications had come to its notice, with allegations that some were not authentic. It reported that the Commission directed Electoral Registration Officers to act against applicants who knowingly make false declarations, after an inquiry under Rule 20 of the Registration of Electors Rules, 1960.</t>
+          <t>The Hindu reported that the Supreme Court agreed to consider an application by Congress MP Tanuj Punia alleging that Form 7 objections in the Uttar Pradesh SIR were filed with false particulars, forged signatures and in the names of people who later denied filing them. The application cited one person filing objections against 32 electors in Hata, Kushinagar, and a UP Congress claim of 700 to 800 objections in four Khalilabad booths.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/karnataka/2026/Oct/01/karnataka-sir-eci-flags-bulk-form-7-claims-orders-action-against-false-declarations</t>
+          <t>https://www.thehindu.com/news/national/uttar-pradesh/form-7-misuse-supreme-court-to-consider-congress-mps-plea-alleging-targeted-deletions-in-up/article71314187.ece</t>
         </is>
       </c>
     </row>
@@ -24693,27 +24743,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Hyderabad; Bahadurpura; Aliyabad</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Congress; BJP; Chief Electoral Officer, Telangana</t>
+          <t>Congress; Chief Electoral Officer, Uttarakhand</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -24723,22 +24768,22 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>The South First</t>
+          <t>The Pioneer</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>The South First reported that it had seen a Form 7 from a polling station in Aliyabad, in Bahadurpura, with the voter's details printed and the objector's part left blank. The Congress alleged that such forms had been handed to BJP booth agents through the party's constituency in-charges.</t>
+          <t>The Pioneer reported that an Uttarakhand Congress delegation told the Chief Electoral Officer that one person had filed objections against about 6,400 voters and about 1,200 people had filed more than ten each. These are the Congress's figures.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>The South First reported that the Chief Electoral Officer, C. Sudharshan Reddy, said at a press briefing that officials would thoroughly verify all Form 7 applications before making any decision.</t>
+          <t>The Pioneer reported that CEO V. V. R. C. Purushottam said the revision followed the rules and that observers had been sent to districts with many objections, and that Additional CEO Vijay Kumar Jogdande said an ERO must scrutinise cases where one person seeks to remove more than five names.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://thesouthfirst.com/telangana/after-musheerabad-telangana-congress-says-it-found-more-pre-printed-form-7s-aimed-at-deleting-muslim-voters-in-bahadurpura/</t>
+          <t>https://dailypioneer.com/news/uttarakhand-congress-alleges-form-7-misuse-to-delete-voters-during-sir-approaches-ec</t>
         </is>
       </c>
     </row>
@@ -24750,27 +24795,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Chatra; West Singhbhum; Deoghar</t>
+          <t>Haridwar; Jhabrera</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Jharkhand</t>
+          <t>BJP; Electoral Registration Officer; Election Commission</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Form 7; Form 8</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -24780,22 +24825,22 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>The Wire</t>
+          <t>Newslaundry</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Of 13,443 Form 7 applications for deletion in Jharkhand, 4,790 came from the Chatra Assembly seat, about 36% of the state's total, in figures the Chief Electoral Officer released on 1 October, The Wire reported, citing the Hindustan Times. West Singhbhum had 1,906 and Deoghar 1,099.</t>
+          <t>Newslaundry reported that 35 people named as objectors on 1,657 Form 7s in Jhabrera, 31 of them BJP booth agents, said in affidavits that their names, EPIC numbers and signatures had been misused.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>The Wire reported that the Chief Electoral Officer said the Chatra figures were checked with the district administration and no bulk applications beyond the limit were found, and that address changes on Form 8 generate Form 7 entries automatically.</t>
+          <t>Newslaundry quoted the Jhabrera ERO saying the objections were cancelled after those named sought to withdraw them and the voters would not be deleted, and that the Election Commission would not order any investigation and those whose names were misused should file an FIR.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/rights/sir-single-jharkhand-assembly-constituency-accounts-for-over-a-third-of-voter-deletion-requests</t>
+          <t>https://www.newslaundry.com/2026/08/28/exclusive-bjp-agents-identities-misused-to-file-mass-objections-against-haridwars-muslim-voters</t>
         </is>
       </c>
     </row>
@@ -24807,22 +24852,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Karnataka</t>
+          <t>Election Commission; Congress; BJP; AIMIM</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Form 6; Form 7; Notices and hearings</t>
+          <t>Form 7; Transparency of lists</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -24832,22 +24882,22 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Vartha Bharati</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Vartha Bharati reported, quoting the Chief Electoral Officer's office, that Karnataka received 8,85,952 Form 6, 4,648 Form 6A, 84,900 Form 7 and 11,78,028 Form 8 applications between 16 June and 1 October, and that 35,60,833 hearings had been held, with 7,82,304 pending.</t>
+          <t>Deccan Chronicle reported, in a story datelined Hyderabad that does not say whether the figure covers the state or the district, that the Commission had received close to 50,000 Form 7 applications against entries in the draft roll, and that parties at a meeting chaired by Hyderabad's District Election Officer asked for the Form 10 lists by Assembly constituency.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>The figures are a running count while hearings continue. Karnataka's final roll is due on 27 October 2026.</t>
+          <t>Deccan Chronicle reported that officials gave parties the total number of applications at a meeting at the GHMC office but did not share figures by Assembly constituency.</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/karnataka/karnataka-4343-lakh-sir-notices-delivered-84900-form-7-applications-received-so-far-2279694</t>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/50000-forms-filed-seeking-deletion-of-votes-1984663</t>
         </is>
       </c>
     </row>
@@ -24859,27 +24909,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Karnataka</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Belagavi North; Bidar; Mysuru</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Police; Chief Electoral Officer, Karnataka</t>
+          <t>BJP</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms; Police and FIRs</t>
+          <t>Form 7; Minorities</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -24889,22 +24934,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>The News Minute (citing The Hindu)</t>
+          <t>Newslaundry</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>The News Minute reported that five FIRs were registered in Belagavi, Bidar and Mysuru over Form 7s alleged to carry false information or forged signatures, and that in Belagavi the voters' details had been filled in beforehand with the objector's name handwritten or blank.</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>The News Minute reported that Karnataka CEO V. Anbu Kumar said that although 84,900 Form 7s had been received, no one had been taken off the rolls.</t>
+          <t>Newslaundry reported from its investigation in Uttarakhand that numerous applications were filed to remove Muslim voters from the rolls, many in the names of people it said were associated with the BJP. It reported that some people named as objectors later filed affidavits saying they had never filed the objections and that their names, EPIC numbers and signatures had been used fraudulently.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/karnataka/five-firs-filed-across-karnataka-over-alleged-misuse-of-form-7-bjp-threatens-protest</t>
+          <t>https://www.newslaundry.com/2026/09/09/uttarakhand-sir-who-is-targeting-muslim-voters</t>
         </is>
       </c>
     </row>
@@ -24916,27 +24956,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Hyderabad; Goshamahal; Musheerabad</t>
+          <t>Karol Bagh; Patel Nagar; Sangam Vihar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Congress; BJP; District Election Officer; Electoral Registration Officer</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms; Police and FIRs</t>
+          <t>Form 7; Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -24946,22 +24986,22 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported, citing Congress sources, that a BJP booth agent brought 15 pre-printed Form 7s to the booth officer at booth 173 in Goshamahal and that the booth officer refused to accept them.</t>
+          <t>The Hindu reported that Form 10 lists published for 21 to 27 September showed four people in Delhi filing more than ten applications a day through the Commission's ECINET portal, which does not enforce the limit of ten a day for booth agents.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported that the District Election Officer had reportedly directed the Musheerabad ERO to file criminal cases against the booth agent there.</t>
+          <t>The Hindu reported that the office of Delhi's Chief Electoral Officer did not respond to a request for comment.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/southern-states/telangana/sir-15-pre-printed-form-7-now-appear-in-goshamahal-constituency-1993058</t>
+          <t>https://www.thehindu.com/news/cities/Delhi/party-appointed-blas-bypass-eci-cap-for-10-applications-a-day-through-its-own-portal-for-deletions/article71524945.ece</t>
         </is>
       </c>
     </row>
@@ -24973,22 +25013,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Hyderabad; Goshamahal; Bahadurpura</t>
+          <t>Babaleshwar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AIMIM; Congress</t>
+          <t>Congress; Civil society groups; Chief Electoral Officer, Karnataka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -25003,17 +25043,22 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>The News Minute</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>The News Minute reported that AIMIM president Asaduddin Owaisi alleged that Form 7s were being filed to remove Muslim voters and warned of protests, and that Congress leaders said the pre-printed forms found in Goshamahal and Bahadurpura were unsigned and were not accepted by booth officers.</t>
+          <t>The Hindu reported that as of September 28, 4,000 Form 7 applications seeking deletion of names had been filed in Karnataka, which it said mostly targeted Muslim voters. It reported that ten people filed Form 7s seeking deletion of 1,363 names in Babaleshwar in one day, often on forms with the voters' details already printed and only the objector's name handwritten. Civil society groups and the Karnataka Congress demanded that the Commission lodge criminal complaints.</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>V. Anbukumar, CEO, Karnataka, was not available for comment.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/telangana/owaisi-says-hyderabad-will-see-massive-protests-if-eci-doesnt-act-on-form-7-misuse</t>
+          <t>https://www.thehindu.com/news/national/karnataka/civil-society-groups-congress-demand-firs-over-bulk-form-7s-seeking-deletion-of-names/article71524777.ece</t>
         </is>
       </c>
     </row>
@@ -25025,22 +25070,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BJP; Police; Government of Karnataka; Chief Electoral Officer, Karnataka</t>
+          <t>Chief Electoral Officer, Telangana</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Form 7; Police and FIRs</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -25050,22 +25100,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>The News Minute</t>
+          <t>Telangana Today</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>The News Minute reported that Karnataka BJP leaders asked the state police chief to review the FIRs against party workers, saying filing several Form 7s is not by itself a crime and the rules set no limit on their number.</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>The News Minute reported that Deputy Chief Minister G. Parameshwara said ministers had gone to the CEO's office to submit a memorandum.</t>
+          <t>Telangana Today reported that the Chief Electoral Officer, C. Sudharshan Reddy, said 28,753 Form 7 applications had been filed in Telangana, about 5,000 of them in Hyderabad, and that forms received in bulk would be examined with special care.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/karnataka/karnataka-bjp-leaders-meet-dgp-seek-review-of-firs-over-form-7-filings</t>
+          <t>https://telanganatoday.com/nearly-29000-form-7-applications-filed-during-telangana-sir</t>
         </is>
       </c>
     </row>
@@ -25077,7 +25122,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -25087,12 +25132,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Hyderabad; Goshamahal; Musheerabad</t>
+          <t>Hyderabad; Musheerabad</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>District Election Officer; BJP; Chief Electoral Officer, Telangana</t>
+          <t>Congress; BJP; Chief Electoral Officer, Telangana</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -25107,22 +25152,22 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Siasat (PTI)</t>
+          <t>Siasat</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Siasat reported, citing PTI, that Hyderabad's District Election Officer R. V. Karnan said the Form 7s in Goshamahal and Musheerabad were not received in bulk and were rejected, the Goshamahal forms because they were unsigned and the Musheerabad ones because the electors were found living at the address.</t>
+          <t>Siasat reported that the Telangana Congress complained to the Chief Electoral Officer that a BJP booth agent in Musheerabad had filed Form 7 applications against a Congress booth agent and about 30 members of his family, on forms that were printed in advance. This is the Congress's allegation.</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Siasat reported that BJP state president N. Ramchander Rao said no BJP booth agents had submitted any such Form 7 applications, and that the Chief Electoral Officer had said bulk forms from a party had to be properly enquired into and verified.</t>
+          <t>Siasat reported that the Congress asked for an investigation to establish the facts, including a forensic examination of whether the forms came from a common source.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/contested-form-7s-rejected-no-bulk-filings-telangana-deo-3552749/</t>
+          <t>https://www.siasat.com/telangana-sir-congress-alleges-vote-deletion-bid-in-musheerabad-3551155/</t>
         </is>
       </c>
     </row>
@@ -25134,22 +25179,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Koppa</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Telangana; District Election Officer; Electoral Registration Officer</t>
+          <t>BJP</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Form 7; Police and FIRs</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -25159,22 +25209,22 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>The News Minute</t>
+          <t>Free Press Journal</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>The News Minute quoted a memo of 5 October in which the Chief Electoral Officer, C. Sudharshan Reddy, told District Election Officers that bulk Form 7 applications had been filed and that EROs should act under Section 31 of the Representation of the People Act against anyone who knowingly made a false declaration.</t>
+          <t>A BJP leader in Koppa, Chikkamagaluru, wrote on 1 October to withdraw Form 7 objections seeking the deletion of 243 voters filed on 21 and 22 September, saying the voters were found on re-verification to live within the polling stations' areas, Free Press Journal reported.</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Siasat reported that the CEO said this action would follow an inquiry. The memo itself was not found on the CEO Telangana website.</t>
+          <t>No response from the election authorities was reported.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/telangana/telangana-sir-congress-seeks-sit-probe-into-alleged-form-7-misuse</t>
+          <t>https://www.freepressjournal.in/india/karnataka-bjp-leader-withdraws-form-7-pleas-to-delete-243-voters-after-sir-row</t>
         </is>
       </c>
     </row>
@@ -25186,27 +25236,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Hyderabad; Musheerabad; Bahadurpura; Goshamahal</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Congress; Police; BJP</t>
+          <t>Election Commission; Electoral Registration Officer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms; Police and FIRs</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -25216,22 +25266,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>The South First</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>The South First reported that the Telangana Congress asked the Hyderabad Police Commissioner to register an FIR and set up a Special Investigation Team over pre-filled Form 7s in three constituencies, and to examine the BJP's role. These are the Congress's allegations.</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>The South First reported that the Congress said the Police Commissioner had assured it he would study the matter and take action.</t>
+          <t>The New Indian Express reported that the Commission wrote to election officials in Bengaluru that bulk Form 7 applications had come to its notice, with allegations that some were not authentic. It reported that the Commission directed Electoral Registration Officers to act against applicants who knowingly make false declarations, after an inquiry under Rule 20 of the Registration of Electors Rules, 1960.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://thesouthfirst.com/telangana/sir-telangana-ceo-orders-action-over-bulk-form-7-filings-congress-seeks-sit-probe/</t>
+          <t>https://www.newindianexpress.com/states/karnataka/2026/Oct/01/karnataka-sir-eci-flags-bulk-form-7-claims-orders-action-against-false-declarations</t>
         </is>
       </c>
     </row>
@@ -25243,22 +25288,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Hyderabad; Bahadurpura; Aliyabad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Karnataka; Electoral Registration Officer</t>
+          <t>Congress; BJP; Chief Electoral Officer, Telangana</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Form 7; Notices and hearings</t>
+          <t>Form 7; Pre-printed forms</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -25268,17 +25318,22 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>The News Minute</t>
+          <t>The South First</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Karnataka's Chief Electoral Officer said 91,278 Form 7 applications were received between 16 June and 4 October, that no name had yet been deleted because of one, and that each would go through a notice and hearing before an officer decided. He said EROs would inquire into bulk applications and that his office had registered no FIR, The News Minute reported.</t>
+          <t>The South First reported that it had seen a Form 7 from a polling station in Aliyabad, in Bahadurpura, with the voter's details printed and the objector's part left blank. The Congress alleged that such forms had been handed to BJP booth agents through the party's constituency in-charges.</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>The South First reported that the Chief Electoral Officer, C. Sudharshan Reddy, said at a press briefing that officials would thoroughly verify all Form 7 applications before making any decision.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://www.thenewsminute.com/karnataka/91278-form-7-applications-received-in-karnataka-officials-says-no-names-deleted-so-far</t>
+          <t>https://thesouthfirst.com/telangana/after-musheerabad-telangana-congress-says-it-found-more-pre-printed-form-7s-aimed-at-deleting-muslim-voters-in-bahadurpura/</t>
         </is>
       </c>
     </row>
@@ -25290,27 +25345,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Hyderabad; Goshamahal</t>
+          <t>Chatra; West Singhbhum; Deoghar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AIMIM; BJP; Congress</t>
+          <t>Chief Electoral Officer, Jharkhand</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms; Minorities</t>
+          <t>Form 7; Form 8</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -25320,22 +25375,22 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Deccan Chronicle (ANI)</t>
+          <t>The Wire</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported that Asaduddin Owaisi alleged that pre-printed Form 7s seeking the deletion of 122 electors, all Muslim, were submitted at booth 28 in Goshamahal in the name of a BJP supporter, and that the booth officer refused them. This is AIMIM's allegation.</t>
+          <t>Of 13,443 Form 7 applications for deletion in Jharkhand, 4,790 came from the Chatra Assembly seat, about 36% of the state's total, in figures the Chief Electoral Officer released on 1 October, The Wire reported, citing the Hindustan Times. West Singhbhum had 1,906 and Deoghar 1,099.</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Siasat reported on 5 October, citing PTI, that BJP state president N. Ramchander Rao said no BJP booth agents had submitted any such Form 7 applications.</t>
+          <t>The Wire reported that the Chief Electoral Officer said the Chatra figures were checked with the district administration and no bulk applications beyond the limit were found, and that address changes on Form 8 generate Form 7 entries automatically.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/southern-states/telangana/goshamahal-voter-deletion-row-owaisi-seeks-eci-action-1993544</t>
+          <t>https://m.thewire.in/article/rights/sir-single-jharkhand-assembly-constituency-accounts-for-over-a-third-of-voter-deletion-requests</t>
         </is>
       </c>
     </row>
@@ -25347,27 +25402,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Telangana</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Hyderabad; Musheerabad</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Chief Electoral Officer, Karnataka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Form 7; Pre-printed forms; Police and FIRs</t>
+          <t>Form 6; Form 7; Notices and hearings</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -25377,17 +25427,22 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Telangana Today</t>
+          <t>Vartha Bharati</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Telangana Today reported that Chikkadpally police were checking the forms, signatures and voter details in the Musheerabad case and whether similar forms were filed elsewhere, and that the forms had reportedly been rejected.</t>
+          <t>Vartha Bharati reported, quoting the Chief Electoral Officer's office, that Karnataka received 8,85,952 Form 6, 4,648 Form 6A, 84,900 Form 7 and 11,78,028 Form 8 applications between 16 June and 1 October, and that 35,60,833 hearings had been held, with 7,82,304 pending.</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>The figures are a running count while hearings continue. Karnataka's final roll is due on 27 October 2026.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://telanganatoday.com/police-probe-fake-form-7-applications-seeking-deletion-of-31-voters-in-musheerabad</t>
+          <t>https://english.varthabharati.in/karnataka/karnataka-4343-lakh-sir-notices-delivered-84900-form-7-applications-received-so-far-2279694</t>
         </is>
       </c>
     </row>
@@ -25399,32 +25454,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Haldwani</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Magistrate's court</t>
+          <t>Belagavi North; Bidar; Mysuru</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Police; Chief Electoral Officer, Karnataka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Form 7; Police and FIRs; Software (ECINET/ERONET)</t>
+          <t>Form 7; Pre-printed forms; Police and FIRs</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -25434,22 +25484,22 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Haldwani Express News</t>
+          <t>The News Minute (citing The Hindu)</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>A Judicial Magistrate First Class in Haldwani ordered the Banbhoolpura police on 6 October to register an FIR and investigate. A booth agent of a party had said that Form 7s seeking to delete 28 voters in part 134 were filed online in his name without his knowledge, and the court held that tracing who filed them needed a police investigation, Haldwani Express News reported.</t>
+          <t>The News Minute reported that five FIRs were registered in Belagavi, Bidar and Mysuru over Form 7s alleged to carry false information or forged signatures, and that in Belagavi the voters' details had been filled in beforehand with the objector's name handwritten or blank.</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Haldwani Express News reported that the police had told the court the complaint concerned SIR Form 7s and that the complainant could object before the assistant returning officer.</t>
+          <t>The News Minute reported that Karnataka CEO V. Anbu Kumar said that although 84,900 Form 7s had been received, no one had been taken off the rolls.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://haldwaniexpressnews.com/case-of-fake-form-7-to-remove-names-of-28-voters-court-orders-fir/</t>
+          <t>https://www.thenewsminute.com/karnataka/five-firs-filed-across-karnataka-over-alleged-misuse-of-form-7-bjp-threatens-protest</t>
         </is>
       </c>
     </row>
@@ -25461,7 +25511,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -25471,12 +25521,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Hyderabad; Musheerabad</t>
+          <t>Hyderabad; Goshamahal; Musheerabad</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Electoral Registration Officer; Police; BJP; Congress</t>
+          <t>Congress; BJP; District Election Officer; Electoral Registration Officer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -25496,289 +25546,314 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported that the Musheerabad ERO filed a police complaint, and Chikkadpally police registered a case, against a BJP booth agent who tried to submit 30 pre-printed Form 7s, the first such case in Telangana.</t>
+          <t>Deccan Chronicle reported, citing Congress sources, that a BJP booth agent brought 15 pre-printed Form 7s to the booth officer at booth 173 in Goshamahal and that the booth officer refused to accept them.</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported that the Congress welcomed the case and asked the police to find who printed and supplied the forms.</t>
+          <t>Deccan Chronicle reported that the District Election Officer had reportedly directed the Musheerabad ERO to file criminal cases against the booth agent there.</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/southern-states/telangana/first-fir-related-to-form-7-1993718</t>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/sir-15-pre-printed-form-7-now-appear-in-goshamahal-constituency-1993058</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Hyderabad; Goshamahal; Bahadurpura</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>AIMIM; Congress</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET)</t>
+          <t>Form 7; Pre-printed forms; Minorities</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>press</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Election Commission of India (PIB)</t>
+          <t>The News Minute</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>The Commission announced in May 2025 that it was building ECINET, one platform to bring together more than 40 of its apps and websites for voters, election officials and other users.</t>
+          <t>The News Minute reported that AIMIM president Asaduddin Owaisi alleged that Form 7s were being filed to remove Muslim voters and warned of protests, and that Congress leaders said the pre-printed forms found in Goshamahal and Bahadurpura were unsigned and were not accepted by booth officers.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126682</t>
+          <t>https://www.thenewsminute.com/telangana/owaisi-says-hyderabad-will-see-massive-protests-if-eci-doesnt-act-on-form-7-misuse</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>BJP; Police; Government of Karnataka; Chief Electoral Officer, Karnataka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Notices and hearings</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>press</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Supreme Court of India</t>
+          <t>The News Minute</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>The Supreme Court recorded, from the documents before it, what the logical discrepancy category in West Bengal covered and that about 1.36 crore voters fell in it.</t>
+          <t>The News Minute reported that Karnataka BJP leaders asked the state police chief to review the FIRs against party workers, saying filing several Form 7s is not by itself a crime and the rules set no limit on their number.</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>The News Minute reported that Deputy Chief Minister G. Parameshwara said ministers had gone to the CEO's office to submit a memorandum.</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_30_67603_Order_19-Jan-2026.pdf</t>
+          <t>https://www.thenewsminute.com/karnataka/karnataka-bjp-leaders-meet-dgp-seek-review-of-firs-over-form-7-filings</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Hyderabad; Goshamahal; Musheerabad</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>District Election Officer; BJP; Chief Electoral Officer, Telangana</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET)</t>
+          <t>Form 7; Pre-printed forms</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>press</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Election Commission of India (PIB)</t>
+          <t>Siasat (PTI)</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>The Commission launched ECINET formally on 22 January 2026 and said its trial version had already been used during the Bihar election and the SIR.</t>
+          <t>Siasat reported, citing PTI, that Hyderabad's District Election Officer R. V. Karnan said the Form 7s in Goshamahal and Musheerabad were not received in bulk and were rejected, the Goshamahal forms because they were unsigned and the Musheerabad ones because the electors were found living at the address.</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Siasat reported that BJP state president N. Ramchander Rao said no BJP booth agents had submitted any such Form 7 applications, and that the Chief Electoral Officer had said bulk forms from a party had to be properly enquired into and verified.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2217429</t>
+          <t>https://www.siasat.com/contested-form-7s-rejected-no-bulk-filings-telangana-deo-3552749/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Meghalaya</t>
+          <t>Chief Electoral Officer, Telangana; District Election Officer; Electoral Registration Officer</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Notices and hearings</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>press</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Meghalaya</t>
+          <t>The News Minute</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Meghalaya's Chief Electoral Officer listed six checks that ECINET used to flag mapping discrepancies in the third phase, among them a sibling age gap under nine months.</t>
+          <t>The News Minute quoted a memo of 5 October in which the Chief Electoral Officer, C. Sudharshan Reddy, told District Election Officers that bulk Form 7 applications had been filed and that EROs should act under Section 31 of the Representation of the People Act against anyone who knowingly made a false declaration.</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Siasat reported that the CEO said this action would follow an inquiry. The memo itself was not found on the CEO Telangana website.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://meghalaya.gov.in/sites/default/files/press_release/EL_63_2026_50.pdf</t>
+          <t>https://www.thenewsminute.com/telangana/telangana-sir-congress-seeks-sit-probe-into-alleged-form-7-misuse</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Hyderabad; Musheerabad; Bahadurpura; Goshamahal</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Congress; Police; BJP</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Commission's independence</t>
+          <t>Form 7; Pre-printed forms; Police and FIRs</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>press</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Election Commission of India (PIB)</t>
+          <t>The South First</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>After its full meeting on 26 September 2026 the Commission said field officers have access to ECINET by role, set up a committee with an independent expert to check ECINET against the law, and said new IT modules would first go to a committee of officers.</t>
+          <t>The South First reported that the Telangana Congress asked the Hyderabad Police Commissioner to register an FIR and set up a Special Investigation Team over pre-filled Form 7s in three constituencies, and to examine the BJP's role. These are the Congress's allegations.</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>The South First reported that the Congress said the Police Commissioner had assured it he would study the matter and take action.</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2315309&amp;reg=3&amp;lang=1</t>
+          <t>https://thesouthfirst.com/telangana/sir-telangana-ceo-orders-action-over-bulk-form-7-filings-congress-seeks-sit-probe/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Bhopal</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Booth level officers</t>
+          <t>Chief Electoral Officer, Karnataka; Electoral Registration Officer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); BLO workload</t>
+          <t>Form 7; Notices and hearings</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -25788,44 +25863,49 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Free Press Journal</t>
+          <t>The News Minute</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Booth officers in Bhopal told the Free Press Journal they were asked to upload 100 forms a day and could not, because the booth officers' app server was down or very slow.</t>
+          <t>Karnataka's Chief Electoral Officer said 91,278 Form 7 applications were received between 16 June and 4 October, that no name had yet been deleted because of one, and that each would go through a notice and hearing before an officer decided. He said EROs would inquire into bulk applications and that his office had registered no FIR, The News Minute reported.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/bhopal/mp-special-intensive-revision-100-forms-a-day-blos-complain-of-impossible-targets-voters-cant-find-old-records</t>
+          <t>https://www.thenewsminute.com/karnataka/91278-form-7-applications-received-in-karnataka-officials-says-no-names-deleted-so-far</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>West Bengal; Madhya Pradesh</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Jayanagar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Congress; BJP; Police</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Notices and hearings; Software (ECINET/ERONET); Transparency of lists</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -25835,49 +25915,54 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>The Daily Jagran (ANI)</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported, from internal Commission records it acquired, that the Commission's software initially flagged 1.31 crore voters in West Bengal and 2.35 crore in Madhya Pradesh for logical discrepancies, and that officials had no written instructions on how to resolve them. It reported that no criteria for deciding which flagged voters to summon had been made public.</t>
+          <t>Jayanagar police in Bengaluru registered an FIR against two BJP booth level agents and others on a complaint by Karnataka Mahila Congress president Sowmya Reddy, The Daily Jagran reported, carrying ANI. The complaint alleged Form 7 applications with forged signatures seeking to delete 5,698 voters by falsely claiming they had shifted.</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>The Collective said the Commission did not answer its question on how flagged voters were chosen, and that questions sent to the Commission and three state offices on testing and procedure went unanswered.</t>
+          <t>No response from the BJP, the Chief Electoral Officer or the Commission was reported.</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/trc/ecis-software-branded-3-66-crore-voters-as-suspects</t>
+          <t>https://www.thedailyjagran.com/india/news/karnataka-sir-row-fir-against-bjp-blas-for-fake-voter-deletion-in-jayanagar-10331739</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Hyderabad; Goshamahal</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, West Bengal</t>
+          <t>AIMIM; BJP; Congress</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Notices and hearings</t>
+          <t>Form 7; Pre-printed forms; Minorities</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -25887,49 +25972,54 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>Deccan Chronicle (ANI)</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that on 29 December 2025 the West Bengal Chief Electoral Officer's office told state officials in writing that the logical discrepancy software was faulty because the 2002 roll had not been digitised accurately.</t>
+          <t>Deccan Chronicle reported that Asaduddin Owaisi alleged that pre-printed Form 7s seeking the deletion of 122 electors, all Muslim, were submitted at booth 28 in Goshamahal in the name of a BJP supporter, and that the booth officer refused them. This is AIMIM's allegation.</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>The Collective said the Commission and the West Bengal Chief Electoral Officer did not reply to its questions on the WhatsApp instructions.</t>
+          <t>Siasat reported on 5 October, citing PTI, that BJP state president N. Ramchander Rao said no BJP booth agents had submitted any such Form 7 applications.</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/trc/ecis-top-wb-officer-sent-orders-to-state-officials-on-whatsapp</t>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/goshamahal-voter-deletion-row-owaisi-seeks-eci-action-1993544</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Hyderabad; Musheerabad</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, West Bengal</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Notices and hearings; Duplicates and errors</t>
+          <t>Form 7; Pre-printed forms; Police and FIRs</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -25939,44 +26029,54 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Siasat (IANS, citing officials of the Chief Electoral Officer, West Bengal)</t>
+          <t>Telangana Today</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Officials of West Bengal's Chief Electoral Officer told IANS that the logical discrepancy check caught people who had falsely linked themselves to unrelated voters, and gave examples they said were found at hearings.</t>
+          <t>Telangana Today reported that Chikkadpally police were checking the forms, signatures and voter details in the Musheerabad case and whether similar forms were filed elsewhere, and that the forms had reportedly been rejected.</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/west-bengal-sir-eci-explains-why-logical-discrepancy-cases-are-high-3328210/</t>
+          <t>https://telanganatoday.com/police-probe-fake-form-7-applications-seeking-deletion-of-31-voters-in-musheerabad</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Haldwani</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Magistrate's court</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Election Commission; Booth level officers</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); BLO workload</t>
+          <t>Form 7; Police and FIRs; Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -25986,49 +26086,49 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>Haldwani Express News</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>The New Indian Express reported that the Android version of the booth officers' app was updated 31 times between 13 November 2025 and 20 January 2026, with no user manual for the updates, and that officials relied on the app to learn what the revision allowed.</t>
+          <t>A Judicial Magistrate First Class in Haldwani ordered the Banbhoolpura police on 6 October to register an FIR and investigate. A booth agent of a party had said that Form 7s seeking to delete 28 voters in part 134 were filed online in his name without his knowledge, and the court held that tracing who filed them needed a police investigation, Haldwani Express News reported.</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Haldwani Express News reported that the police had told the court the complaint concerned SIR Form 7s and that the complainant could object before the assistant returning officer.</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Jan/24/blo-app-underwent-30-changes-in-two-months-in-tamil-nadu</t>
+          <t>https://haldwaniexpressnews.com/case-of-fake-form-7-to-remove-names-of-28-voters-court-orders-fir/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Chennai</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Booth level officers</t>
+          <t>BJP; JD(S); Governor of Karnataka; Government of Karnataka; Police</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); BLO workload</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -26038,44 +26138,49 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>The New Indian Express</t>
+          <t>ThePrint (PTI)</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>The same report quoted a Chennai booth officer who said the app often froze on her phone, so that data was lost or finished work had to be done again.</t>
+          <t>A BJP and JD(S) delegation including Union Minister H D Kumaraswamy and R Ashoka asked Governor Thaawarchand Gehlot to direct the state government to stop registering criminal cases against people who filed Form 7 objections, ThePrint reported, carrying PTI. They alleged police were being misused to intimidate BJP workers and that the Chief Electoral Office had given in to the state government.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>No response from the state government, the Chief Electoral Officer or Congress was reported.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Jan/24/blo-app-underwent-30-changes-in-two-months-in-tamil-nadu</t>
+          <t>https://theprint.in/india/nda-leaders-seek-ktaka-guv-intervention-over-govt-interference-in-sir/3063113/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Election Commission; Electoral Registration Officer</t>
+          <t>Congress; BJP; JD(S); Booth level officers</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Notices and hearings; Software (ECINET/ERONET)</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -26085,49 +26190,54 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>The News Minute</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that hearing notices in West Bengal were generated in bulk by the Commission's software for logical discrepancies, and that two EROs it spoke to, with a few deputies, were signing 4,000 to 5,000 printed notices each day. It reported that the software transliterated names from Bengali into English before matching, so that spellings such as Xalxo and Khalkho triggered a discrepancy. The Collective said this showed the Commission had misled the Supreme Court, where it said there was no automated generation of notices.</t>
+          <t>Chief Minister D K Shivakumar alleged on 6 October that BJP and JD(S) workers had filed Form 7 applications in bulk and then collected back and destroyed more than a lakh of them, threatening booth officers, The News Minute reported. This is his allegation.</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>The Collective said the Commission had not responded by publication. It set its finding against the Commission's submission to the Court that "There is no automated generation of notices" and that officers were "signing them off after application of mind".</t>
+          <t>BJP MLC C T Ravi asked the Commission to register a case against people making baseless allegations and sought legal action against Shivakumar.</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/trc/eci-misled-the-sc-on-sir-in-west-bengal</t>
+          <t>https://www.thenewsminute.com/karnataka/congress-and-bjp-jds-trade-charges-over-bulk-form-7-filings-during-sir-in-karnataka</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Hyderabad; Musheerabad</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Electoral Registration Officer; Police; BJP; Congress</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Notices and hearings; Software (ECINET/ERONET)</t>
+          <t>Form 7; Pre-printed forms; Police and FIRs</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -26137,49 +26247,54 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that in West Bengal the logical discrepancy check flagged five kinds of mismatch, from spelling differences between the Bengali 2002 roll and the English draft to age gaps with parents and grandparents.</t>
+          <t>Deccan Chronicle reported that the Musheerabad ERO filed a police complaint, and Chikkadpally police registered a case, against a BJP booth agent who tried to submit 30 pre-printed Form 7s, the first such case in Telangana.</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>The Collective said it sent detailed questions to the Commission and had no answer by publication.</t>
+          <t>Deccan Chronicle reported that the Congress welcomed the case and asked the police to find who printed and supplied the forms.</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/first-fir-related-to-form-7-1993718</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Jayanagar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Electoral Registration Officer; District Election Officer</t>
+          <t>BJP; JD(S); Police; Congress</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Notices and hearings</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -26189,49 +26304,54 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>Punjab Kesari (IANS)</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that a registration officer showed its reporter that the button to clear voters with a name mismatch had disappeared from ERONET since that morning, so such cases now needed the district officer's approval.</t>
+          <t>A BJP and JD(S) delegation led by Jayanagar MLA C K Ramamurthy went to Jayanagar police station in Bengaluru and demanded that the FIR against BJP workers over Form 7 applications be withdrawn, IANS reported. They warned of an intensified agitation if it was not, and alleged that applications meant to be confidential had been handed to Congress workers.</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>The Collective said it sent detailed questions to the Commission and had no answer by publication.</t>
+          <t>No police response was reported.</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
+          <t>https://english.punjabkesari.com/india/sir-row-bjp-jds-delegation-visits-jayanagar-police-station-in-bengaluru-demands-withdrawal-of-fir-against-workers</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Kodagu</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>BJP; Police</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Form 6; Documents and declaration; Software (ECINET/ERONET)</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -26241,49 +26361,44 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>Punjab Kesari (IANS)</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>The Indian Express reported that the online Form 6 on the Commission's ECINET portal carried a new declaration asking whether the applicant or their parents or grandparents were in the electoral roll of the last SIR, although the statutory form had not been amended. It reported that the section was not marked mandatory but applicants could not proceed to submission without completing it, and that the downloadable Form 6 on the same portal did not include it.</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>The EC did not respond to a request for comment and Legislative Department Secretary Rajiv Mani could not be reached despite repeated attempts.</t>
+          <t>Police at Shanivarasanthe in Kodagu district registered a case against five BJP booth level workers on a complaint that they sought the deletion of 64 voters in Byadagutta village through Form 7 applications, IANS reported.</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/election-commission-changes-form-6-for-new-voters-inserts-section-asking-them-about-parents-in-sir-10782435/</t>
+          <t>https://english.punjabkesari.com/india/sir-row-bjp-jds-delegation-visits-jayanagar-police-station-in-bengaluru-demands-withdrawal-of-fir-against-workers</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Karnataka</t>
+          <t>Electoral Registration Officer</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET)</t>
+          <t>Form 6; Form 7</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -26293,34 +26408,34 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Wire (citing The Hindu)</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>The Hindu reported that 13 days into the Karnataka SIR only 0.41% of enumeration forms had been submitted online, and that voters complained of captcha failures, server errors and an ECINet search that failed to find records appearing in the published rolls. It reported that online submission required a current mobile number linked to the voter's EPIC.</t>
+          <t>The Wire reported, citing The Hindu's analysis of Delhi's constituency data, that 569 Form 6 applications and 3,209 Form 7 applications were disposed of between 31 August and 4 October, about six Form 7s for every Form 6. It said 2,352 of the Form 7s were disposed of in the last two weeks, and that 2.12 lakh Form 6 and 51,747 Form 7 applications had been submitted from 16 June, before the claims period began on 31 August.</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Karnataka Chief Electoral Officer V. Anbu Kumar said the process was still under way. However, the CEO did not comment on the technical glitches reported by voters.</t>
+          <t>No response from the Chief Electoral Officer was reported.</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/bangalore/sir-not-even-05-submit-enumeration-forms-online-amid-website-glitches/article71214116.ece</t>
+          <t>https://m.thewire.in/article/government/for-every-form-6-disposal-six-form-7s-cleared-in-delhi-report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -26330,12 +26445,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Chief Electoral Officer, Telangana; BJP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET)</t>
+          <t>Form 7; Deletions</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -26345,44 +26460,59 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Deccan Chronicle</t>
+          <t>ETV Bharat (PTI)</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Deccan Chronicle reported that people filling in enumeration forms on ECINET in Telangana kept being sent back to the home page, and an official put it down to the load from voters in more than a dozen states at once.</t>
+          <t>Data released by Telangana's Chief Electoral Officer on 8 October showed 24,323 Form 7 applications received from 15 June to 7 October and 12,204 names removed, PTI reported. The figure is lower than the 28,753 Form 7s the CEO said on 1 October had been filed, and the reports do not explain the difference.</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>State BJP president N Ramchander Rao said the Commission decides deletions only after field inquiries.</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/southern-states/telangana/sir-ecinet-portal-faces-peak-hour-glitches-1973124</t>
+          <t>https://www.etvbharat.com/en/state/over-24000-form-7-applications-received-during-sir-in-telangana-enn26100809020</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Belagavi</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Karnataka High Court</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>BJP; Congress; Police</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Form 6; Commission's independence; Documents and declaration</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -26392,44 +26522,49 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>LiveLaw</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>The Indian Express reported, from internal records it investigated, that on May 16 Election Commissioner Vivek Joshi recorded that Form 6 is prescribed by statute and cannot be altered without amending the Registration of Electors Rules, 1960, and that Commissioner Sukhbir Singh Sandhu concurred on May 19. It reported that the declaration was added to the online form anyway, and that on August 13 Sandhu wrote that the changes were unauthorised and illegal and must be removed immediately.</t>
+          <t>The Karnataka High Court at Dharwad told the police to take no coercive steps until 13 October against a BJP functionary and two supporters booked over Form 7s against voters in Belagavi, LiveLaw reported. A Congress block agent's complaint, as the police record it, alleges they handed about 198 fabricated Form 7s to the booth officer.</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>The Government Pleader sought time to file objections and the latest investigation report.</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/express-exclusive/election-commission-illegal-changes-form-6-gyanesh-kumar-10889714/</t>
+          <t>https://www.livelaw.in/high-court/karnataka-high-court/karnataka-high-court-shields-bjp-leader-ravi-patil-coercive-steps-sir-553786</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Election Commission; Chief Electoral Officer, Delhi; Electoral Registration Officer</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Commission's independence; Software (ECINET/ERONET)</t>
+          <t>Form 7</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -26439,49 +26574,54 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>Social News XYZ (IANS)</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>The Indian Express reported that Election Commissioners Sukhbir Singh Sandhu and Vivek Joshi warned on file, from November 2025 to August 2026, that control of the electoral roll software was being centralised in the Commission's IT division. It reported that on August 14 Sandhu wrote that many Chief Electoral Officers, District Election Officers and Electoral Registration Officers had told him they lacked proper and complete access to ERONet, and that on July 29 both Commissioners wrote separately to the Cabinet Secretary about a change in work allocation.</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>The Election Commission and the two ECs, Sandhu and Joshi, did not respond to calls and questionnaires emailed by The Indian Express seeking comment.</t>
+          <t>Delhi Chief Electoral Officer Ashok Kumar announced on 9 October that the Commission had decided to limit an individual voter to ten Form 7 objections for the whole claims and objections period and five a month during continuous updation, citing bulk objections on unsubstantiated grounds, IANS reported. The statement said registration officers would act against false objections under Section 31 of the Representation of the People Act, 1950.</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/express-exclusive/election-commission-special-intensive-revision-sir-electoral-roll-centralisation-eci-ecinet-10889738/</t>
+          <t>https://www.socialnews.xyz/2026/10/09/delhi-ceo-restricts-number-of-form-7-an-individual-can-file-to-raise-objections/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Changes to the software</t>
+          <t>Form 7 objections and pre-printed forms</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Malleshwaram</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Karnataka High Court</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>BJP; Police; Government of Karnataka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Notices and hearings; Women</t>
+          <t>Form 7; Police and FIRs</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -26491,17 +26631,22 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Bar and Bench</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>The Hindu reported that up to 11 categories of logical discrepancy were being applied in the third phase of the SIR, up from four when the concept was introduced in West Bengal. They include a sibling age gap of nine months or less, which flagged a Delhi resident's twin children, and a marital mapping mismatch where a woman is linked to her father in the old roll and her husband in the new. It reported that the term has never been clearly defined in any official communication.</t>
+          <t>The Karnataka High Court stayed proceedings in two FIRs against two BJP booth agents accused over bulk Form 7s against voters in Bengaluru's Malleshwaram constituency, Bar and Bench reported. The judge said the FIRs looked premature because the registration officer had not yet decided the Form 7s.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>The State said the allegations of impersonation and forgery needed investigation and that the agents filed more applications than allowed. The complainant's counsel said the bulk filing was a conspiracy aimed at OBC and SC/ST voters.</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/the-many-categories-of-sirs-logical-discrepancy-list-keep-voters-on-toes/article71504625.ece</t>
+          <t>https://www.barandbench.com/news/litigation/sir-karnataka-high-court-grants-relief-to-bjp-booth-agents-booked-for-attempting-to-delete-voters</t>
         </is>
       </c>
     </row>
@@ -26513,47 +26658,42 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Electoral Registration Officer; Chief Electoral Officer, Goa; Election Commission</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Notices and hearings; Deletions</t>
+          <t>Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>Election Commission of India (PIB)</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>The Indian Express reported that Goa's Electoral Registration Officers heard electors flagged for logical discrepancies and found 97 of them eligible, but could not reverse the earlier decisions on ECINET because the permission was controlled from Delhi. It reported that the Goa Chief Electoral Officer's office wrote eight times in seven days asking for a rollback option, and that all 97 were missing from the final roll published on February 21 and were still missing on September 20.</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Goa's Chief Electoral Officer, Sanjay Goel, told the paper the decision not to include them was the Commission's. The Indian Express later reported that the Commission said, after its meeting of 26 September, that 81 of the 97 had filled Form 6 and that the Chief Electoral Officer had been told to help include them.</t>
+          <t>The Commission announced in May 2025 that it was building ECINET, one platform to bring together more than 40 of its apps and websites for voters, election officials and other users.</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/express-exclusive/election-commission-goa-sir-voter-deletion-ecinet-10891422/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126682</t>
         </is>
       </c>
     </row>
@@ -26565,12 +26705,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -26580,27 +26725,27 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET)</t>
+          <t>Notices and hearings</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>The Pioneer</t>
+          <t>Supreme Court of India</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Commission officials said ECINET is decentralised, that each field officer acts through their own login, and that nobody at headquarters can perform those officers' statutory functions. ERONET is now part of ECINET.</t>
+          <t>The Supreme Court recorded, from the documents before it, what the logical discrepancy category in West Bengal covered and that about 1.36 crore voters fell in it.</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://dailypioneer.com/news/ecinet-is-decentralised-only-designated-officials-have-access-says-eci</t>
+          <t>https://api.sci.gov.in/supremecourt/2025/64235/64235_2025_1_30_67603_Order_19-Jan-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -26612,52 +26757,42 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Vikaspuri</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Electoral Registration Officer; Chief Electoral Officer, Delhi</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Deletions; Notices and hearings</t>
+          <t>Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Election Commission of India (PIB)</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>The Hindu reported that more than 350 Delhi electors had been marked ineligible within a month of hearings, about 200 of them in Vikaspuri, and officials said the marking could not be rolled back by the registration officer or the state's Chief Electoral Officer.</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>The Delhi Chief Electoral Officer wrote to officers on 25 September 2026 setting a 10-point checklist before marking anyone ineligible and telling them not to delete names on flimsy or frivolous grounds.</t>
+          <t>The Commission launched ECINET formally on 22 January 2026 and said its trial version had already been used during the Bihar election and the SIR.</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/Delhi/delhi-sir-over-350names-already-marked-ineligible-ceo-warns-against-deletion-on-flimsy-grounds/article71513195.ece</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2217429</t>
         </is>
       </c>
     </row>
@@ -26669,17 +26804,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Maharashtra; Election Commission</t>
+          <t>Chief Electoral Officer, Meghalaya</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -26689,27 +26824,22 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Outlook India (citing NDTV)</t>
+          <t>Chief Electoral Officer, Meghalaya</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Outlook, citing NDTV, reported that Maharashtra's Chief Electoral Officer S Chockalingam asked for four changes to the ECINET software and more discretion for registration officers in logical discrepancy cases.</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>The Commission said on 26 September that several portal upgrades had already been made on inputs from state Chief Electoral Officers and that further flexibility needed by field officers would be made operational.</t>
+          <t>Meghalaya's Chief Electoral Officer listed six checks that ECINET used to flag mapping discrepancies in the third phase, among them a sibling age gap under nine months.</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://www.outlookindia.com/national/maharashtra-poll-chief-seeks-more-ero-powers-as-ecinet-faces-scrutiny-over-sir</t>
+          <t>https://meghalaya.gov.in/sites/default/files/press_release/EL_63_2026_50.pdf</t>
         </is>
       </c>
     </row>
@@ -26721,7 +26851,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -26736,32 +26866,27 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Form 6; Documents and declaration; Software (ECINET/ERONET)</t>
+          <t>Software (ECINET/ERONET); Commission's independence</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>Election Commission of India (PIB)</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>The Indian Express reported that on the night of 29 to 30 September 2026 the Commission removed the SIR declaration from the online Form 6 on ECINET for states where the final SIR rolls have been published. It reported that the declaration remained for states where the SIR is still ongoing.</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>The article cites the Commission's September 26 announcement that ‘for non-SIR period, the Forms applicable as per Rules (the Registration of Electors Rules 1960) will be used’.</t>
+          <t>After its full meeting on 26 September 2026 the Commission said field officers have access to ECINET by role, set up a committee with an independent expert to check ECINET against the law, and said new IT modules would first go to a committee of officers.</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/election-commission-removes-sir-declaration-form-6-ecinet-portal-investigation-gyanesh-kumar-10899952/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2315309&amp;reg=3&amp;lang=1</t>
         </is>
       </c>
     </row>
@@ -26773,22 +26898,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Bhopal</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Congress; Election Commission</t>
+          <t>Booth level officers</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Commission's independence</t>
+          <t>Software (ECINET/ERONET); BLO workload</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -26798,22 +26928,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>ThePrint (PTI)</t>
+          <t>Free Press Journal</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Congress general secretary Jairam Ramesh alleged that by restricting registration officers' access to the ECINet roll system and overruling them in Goa, West Bengal and other states, the Commission broke the Representation of the People Act, 1950.</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>PTI recalled that the Commission, under fire over objections from two of its Commissioners, had said differing views are a normal part of deliberation and that all its orders carry full legal sanction and follow established statutory procedures.</t>
+          <t>Booth officers in Bhopal told the Free Press Journal they were asked to upload 100 forms a day and could not, because the booth officers' app server was down or very slow.</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cong-accuses-ec-of-lying-about-ecinet-calls-for-accountability/3059961/</t>
+          <t>https://www.freepressjournal.in/bhopal/mp-special-intensive-revision-100-forms-a-day-blos-complain-of-impossible-targets-voters-cant-find-old-records</t>
         </is>
       </c>
     </row>
@@ -26825,12 +26950,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>West Bengal; Madhya Pradesh</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -26840,7 +26965,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Form 6; Deletions; Documents and declaration</t>
+          <t>Notices and hearings; Software (ECINET/ERONET); Transparency of lists</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -26850,22 +26975,22 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>The Reporters' Collective</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>The Indian Express reported a letter of 29 September from the Commission’s Secretary ordering a special drive to enrol "left out and young/first time eligible electors" in the 20 states and union territories where the revision is complete, using the statutory Form 6, with the added declaration kept for the revision phase only. It reported that at a video conference with all Chief Electoral Officers, the states were told to compare the roll from before the revision with the one after, list those removed, visit them at home and help those left out fill in Form 6, with help from the parties’ booth agents.</t>
+          <t>The Reporters' Collective reported, from internal Commission records it acquired, that the Commission's software initially flagged 1.31 crore voters in West Bengal and 2.35 crore in Madhya Pradesh for logical discrepancies, and that officials had no written instructions on how to resolve them. It reported that no criteria for deciding which flagged voters to summon had been made public.</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>The letter of 29 September itself was not found. The Commission's letter of 1 October, which continues it, is in the timeline above. The Commission’s press note of 26 September, in the timeline above, had already ordered the drive, and Uttarakhand’s Chief Electoral Officer set out its steps in a press note of 3 October.</t>
+          <t>The Collective said the Commission did not answer its question on how flagged voters were chosen, and that questions sent to the Commission and three state offices on testing and procedure went unanswered.</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/election-commission-of-india-sir-left-out-voters-special-drive-10903082/</t>
+          <t>https://www.reporters-collective.in/trc/ecis-software-branded-3-66-crore-voters-as-suspects</t>
         </is>
       </c>
     </row>
@@ -26877,17 +27002,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Election Commission; Electoral Registration Officer; Chief Electoral Officer, Delhi</t>
+          <t>Chief Electoral Officer, West Bengal</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -26902,22 +27027,22 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Reporters' Collective</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>The Hindu reported that the options reached Delhi officers on 30 September and only the ten states and union territories where the third phase was still under way, and that a case marked ineligible still could not be reversed.</t>
+          <t>The Reporters' Collective reported that on 29 December 2025 the West Bengal Chief Electoral Officer's office told state officials in writing that the logical discrepancy software was faulty because the 2002 roll had not been digitised accurately.</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>The Delhi CEO’s office and the EC did not respond to queries on why the options were introduced at this stage.</t>
+          <t>The Collective said the Commission and the West Bengal Chief Electoral Officer did not reply to its questions on the WhatsApp instructions.</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/ec-explains-new-eronet-options-for-sir-notice-disposal-to-eros-through-demo-video-no-written-instructions-yet/article71543373.ece</t>
+          <t>https://www.reporters-collective.in/trc/ecis-top-wb-officer-sent-orders-to-state-officials-on-whatsapp</t>
         </is>
       </c>
     </row>
@@ -26929,22 +27054,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Congress; Election Commission</t>
+          <t>Chief Electoral Officer, West Bengal</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Form 6; Documents and declaration; Commission's independence</t>
+          <t>Notices and hearings; Duplicates and errors</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -26954,17 +27079,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Business Today</t>
+          <t>Siasat (IANS, citing officials of the Chief Electoral Officer, West Bengal)</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Rahul Gandhi of the Congress, the Leader of the Opposition, said the Chief Election Commissioner had changed Form 6 illegally and unilaterally. The Commission replied on X that the statement was misleading, that its Bihar order of 24 June 2025 had the Commission's unanimous approval and was upheld by the Supreme Court on 27 May 2026, and that its press note of 26 September said the declaration attached to Form 6 had been upheld, Business Today reported.</t>
+          <t>Officials of West Bengal's Chief Electoral Officer told IANS that the logical discrepancy check caught people who had falsely linked themselves to unrelated voters, and gave examples they said were found at hearings.</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/misleading-eci-fact-checks-rahul-gandhis-form-6-claim-cites-sc-ruling-on-bihar-sir-order-559674-2026-10-05</t>
+          <t>https://www.siasat.com/west-bengal-sir-eci-explains-why-logical-discrepancy-cases-are-high-3328210/</t>
         </is>
       </c>
     </row>
@@ -26976,27 +27101,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Appellate tribunal (West Bengal)</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Election Commission; Booth level officers</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Adjudication and appeals; Software (ECINET/ERONET)</t>
+          <t>Software (ECINET/ERONET); BLO workload</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -27006,22 +27126,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>The Indian Express reported that at a meeting on 11 August 2026 more than a dozen West Bengal appeal tribunal judges recorded that the Commission's portal did not let them serve notices, hold virtual hearings, restore a deleted voter or give appellants a copy of the order.</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>The paper said it emailed the Commission and the Registrar General of the Calcutta High Court on 1 October and received no response.</t>
+          <t>The New Indian Express reported that the Android version of the booth officers' app was updated 31 times between 13 November 2025 and 20 January 2026, with no user manual for the updates, and that officials relied on the app to learn what the revision allowed.</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/bengal-sir-tribunals-election-commission-portal-issues-deleted-voters-10908185/</t>
+          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Jan/24/blo-app-underwent-30-changes-in-two-months-in-tamil-nadu</t>
         </is>
       </c>
     </row>
@@ -27033,22 +27148,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CERT-In; Election Commission</t>
+          <t>Booth level officers</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET)</t>
+          <t>Software (ECINET/ERONET); BLO workload</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -27058,22 +27178,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Hindustan Times</t>
+          <t>The New Indian Express</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Hindustan Times reported that a security researcher emailed CERT-In on 8 July 2026, copied to the Commission's complaints address, about flaws in the voter-services website and the ECINET app. The worst, in the researcher's account, let anyone obtain election officials' names and mobile numbers without logging in.</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>HT said neither CERT-In nor the Commission answered its questions of 5 October. On 6 October CERT-In told the researcher that one flaw, the hardcoded encryption key he rated least serious, had been fixed and that work on the rest was under progress. HT said none of the flaws related directly to registration officers' access to the roll, and that the email alleged no theft or misuse of data.</t>
+          <t>The same report quoted a Chennai booth officer who said the app often froze on her phone, so that data was lost or finished work had to be done again.</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/ecinet-flaws-were-flagged-to-poll-body-eci-cyber-security-agency-cert-in-in-july-says-researcher-101791401749277.html</t>
+          <t>https://www.newindianexpress.com/states/tamil-nadu/2026/Jan/24/blo-app-underwent-30-changes-in-two-months-in-tamil-nadu</t>
         </is>
       </c>
     </row>
@@ -27085,22 +27200,22 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Congress; BJP; Election Commission</t>
+          <t>Election Commission; Electoral Registration Officer</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Commission's independence</t>
+          <t>Notices and hearings; Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -27110,34 +27225,34 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>The Reporters' Collective</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Congress alleged after the Hindustan Times report that ECINET was designed to centralise deletions and additions from the BJP's headquarters. This is a party's allegation. Hindustan Times had said none of the flaws it reported related directly to registration officers' access to the roll.</t>
+          <t>The Reporters' Collective reported that hearing notices in West Bengal were generated in bulk by the Commission's software for logical discrepancies, and that two EROs it spoke to, with a few deputies, were signing 4,000 to 5,000 printed notices each day. It reported that the software transliterated names from Bengali into English before matching, so that spellings such as Xalxo and Khalkho triggered a discrepancy. The Collective said this showed the Commission had misled the Supreme Court, where it said there was no automated generation of notices.</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Scroll did not report a response from the Commission to this allegation.</t>
+          <t>The Collective said the Commission had not responded by publication. It set its finding against the Commission's submission to the Court that "There is no automated generation of notices" and that officers were "signing them off after application of mind".</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://scroll.in/latest/1096252/ec-online-portal-designed-to-centralise-voter-deletions-from-bjp-headquarters-congress-alleges</t>
+          <t>https://www.reporters-collective.in/trc/eci-misled-the-sc-on-sir-in-west-bengal</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Instructions given without a written order</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -27147,12 +27262,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, West Bengal; Trinamool Congress; District Election Officer</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Schedule and deadlines; Deletions</t>
+          <t>Notices and hearings; Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -27167,24 +27282,24 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that West Bengal's Chief Electoral Officer sent instructions on a WhatsApp group of district magistrates that brought forward the enumeration deadline and asked officers to mark voters absent before the written deadline. The Trinamool Congress had first made the allegation before the Supreme Court.</t>
+          <t>The Reporters' Collective reported that in West Bengal the logical discrepancy check flagged five kinds of mismatch, from spelling differences between the Bengali 2002 roll and the English draft to age gaps with parents and grandparents.</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>The Collective said the Commission and the West Bengal Chief Electoral Officer did not reply to its questions on the WhatsApp instructions.</t>
+          <t>The Collective said it sent detailed questions to the Commission and had no answer by publication.</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/trc/ecis-top-wb-officer-sent-orders-to-state-officials-on-whatsapp</t>
+          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Instructions given without a written order</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -27199,12 +27314,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>District Election Officer; Chief Electoral Officer, West Bengal</t>
+          <t>Electoral Registration Officer; District Election Officer</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Notices and hearings; Documents and declaration; Software (ECINET/ERONET)</t>
+          <t>Software (ECINET/ERONET); Notices and hearings</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -27219,12 +27334,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that district magistrates of at least three West Bengal districts wrote to the state election office asking for a written procedure for logical discrepancy cases, and that the portal accepted only the 12 listed documents.</t>
+          <t>The Reporters' Collective reported that a registration officer showed its reporter that the button to clear voters with a name mismatch had disappeared from ERONET since that morning, so such cases now needed the district officer's approval.</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>The Collective reported that the officers received no response and carried on with their own methods.</t>
+          <t>The Collective said it sent detailed questions to the Commission and had no answer by publication.</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -27236,27 +27351,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Instructions given without a written order</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Electoral Registration Officer</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Documents and declaration; Software (ECINET/ERONET)</t>
+          <t>Form 6; Documents and declaration; Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -27266,44 +27381,49 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>A registration officer told The Reporters' Collective that officers were told orally to ask unmapped electors for a second document besides Aadhaar, and that the software for a time would not accept Aadhaar alone. The Collective said it could not check this claim.</t>
+          <t>The Indian Express reported that the online Form 6 on the Commission's ECINET portal carried a new declaration asking whether the applicant or their parents or grandparents were in the electoral roll of the last SIR, although the statutory form had not been amended. It reported that the section was not marked mandatory but applicants could not proceed to submission without completing it, and that the downloadable Form 6 on the same portal did not include it.</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>The EC did not respond to a request for comment and Legislative Department Secretary Rajiv Mani could not be reached despite repeated attempts.</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
+          <t>https://indianexpress.com/article/india/election-commission-changes-form-6-for-new-voters-inserts-section-asking-them-about-parents-in-sir-10782435/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Instructions given without a written order</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Election Commission; Electoral Registration Officer</t>
+          <t>Chief Electoral Officer, Karnataka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Documents and declaration; Minorities</t>
+          <t>Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -27313,44 +27433,49 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>The New Indian Express (PTI)</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>PTI reported that the Commission's written instructions of 14 May 2026 for the third phase told registration officers to refer suspected foreign nationals to the authority under the Citizenship Act.</t>
+          <t>The Hindu reported that 13 days into the Karnataka SIR only 0.41% of enumeration forms had been submitted online, and that voters complained of captcha failures, server errors and an ECINet search that failed to find records appearing in the published rolls. It reported that online submission required a current mobile number linked to the voter's EPIC.</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Karnataka Chief Electoral Officer V. Anbu Kumar said the process was still under way. However, the CEO did not comment on the technical glitches reported by voters.</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/india/2026/Jun/07/sir-ec-state-poll-machinery-to-share-details-of-suspected-foreigners-with-authorities-2</t>
+          <t>https://www.thehindu.com/news/cities/bangalore/sir-not-even-05-submit-enumeration-forms-online-amid-website-glitches/article71214116.ece</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Instructions given without a written order</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Electoral Registration Officer; Chief Electoral Officer, Delhi; Election Commission</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Minorities</t>
+          <t>Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -27360,34 +27485,29 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>Deccan Chronicle</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>A Delhi registration officer told The Hindu that officers were first told to identify suspected foreigners during enumeration and later told in the middle of it to stop, and that many oral instructions had been taken back.</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>The Delhi CEO's office and the EC did not respond to The Hindu's queries on why the new ERONET options were introduced at that stage.</t>
+          <t>Deccan Chronicle reported that people filling in enumeration forms on ECINET in Telangana kept being sent back to the home page, and an official put it down to the load from voters in more than a dozen states at once.</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/ec-explains-new-eronet-options-for-sir-notice-disposal-to-eros-through-demo-video-no-written-instructions-yet/article71543373.ece</t>
+          <t>https://www.deccanchronicle.com/southern-states/telangana/sir-ecinet-portal-faces-peak-hour-glitches-1973124</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Instructions given without a written order</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -27397,12 +27517,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Election Commission; Electoral Registration Officer</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Software (ECINET/ERONET); Notices and hearings</t>
+          <t>Form 6; Commission's independence; Documents and declaration</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -27412,54 +27532,44 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>The Hindu</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>The Hindu reported that new ERONET options letting registration officers clear notice cases without a hearing or documents were explained only through an eight-minute video from the Commission's IT department, with no written instruction.</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>The Delhi CEO’s office and the EC did not respond to queries on why the options were introduced at this stage.</t>
+          <t>The Indian Express reported, from internal records it investigated, that on May 16 Election Commissioner Vivek Joshi recorded that Form 6 is prescribed by statute and cannot be altered without amending the Registration of Electors Rules, 1960, and that Commissioner Sukhbir Singh Sandhu concurred on May 19. It reported that the declaration was added to the online form anyway, and that on August 13 Sandhu wrote that the changes were unauthorised and illegal and must be removed immediately.</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/ec-explains-new-eronet-options-for-sir-notice-disposal-to-eros-through-demo-video-no-written-instructions-yet/article71543373.ece</t>
+          <t>https://indianexpress.com/article/express-exclusive/election-commission-illegal-changes-form-6-gyanesh-kumar-10889714/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Wrong entries reported on the rolls</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bihar</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Patna</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Election Commission; Booth level officers</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Duplicates and errors; Living electors marked dead</t>
+          <t>Commission's independence; Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -27469,59 +27579,49 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>BBC News</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>The BBC reported that voters in villages near Patna told it the Bihar draft roll carried wrong photographs, duplicate entries and the name of a person who died more than five years earlier. It reported that in Danara village many residents were not sure officials had visited their homes.</t>
+          <t>The Indian Express reported that Election Commissioners Sukhbir Singh Sandhu and Vivek Joshi warned on file, from November 2025 to August 2026, that control of the electoral roll software was being centralised in the Commission's IT division. It reported that on August 14 Sandhu wrote that many Chief Electoral Officers, District Election Officers and Electoral Registration Officers had told him they lacked proper and complete access to ERONet, and that on July 29 both Commissioners wrote separately to the Cabinet Secretary about a change in work allocation.</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>In response to the BBC's questions, the Election Commission shared its 24 June order on conducting the SIR and a 27 July press note outlining efforts to ensure no eligible voter was "left behind". "Further, [the commission] does not take any responsibility of any other misinformation or unsubstantiated allegations being floated around by some vested interests," it added. The BBC also noted the commission has said BLOs worked "very responsibly".</t>
+          <t>The Election Commission and the two ECs, Sandhu and Joshi, did not respond to calls and questionnaires emailed by The Indian Express seeking comment.</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c3wnx7689l5o</t>
+          <t>https://indianexpress.com/article/express-exclusive/election-commission-special-intensive-revision-sir-electoral-roll-centralisation-eci-ecinet-10889738/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Wrong entries reported on the rolls</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bihar</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Ara; Bhojpur</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Election Commission; Booth level officers</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Living electors marked dead</t>
+          <t>Notices and hearings; Women</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -27531,54 +27631,44 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>The Wire</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>The Wire reported that a voter from Ara, Bhojpur, who had been declared dead in the Bihar draft roll, appeared alive in the Supreme Court on 12 August 2025, produced by petitioner Yogendra Yadav. The voter told The Wire he had filled the enumeration form and that the BLO came to his house only after he complained.</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Senior advocate Rakesh Dwivedi, for the Commission, called the production of the voter "drama". The bench of Justices Surya Kant and Joymalya Bagchi said there may have been an "inadvertent error", which could be rectified.</t>
+          <t>The Hindu reported that up to 11 categories of logical discrepancy were being applied in the third phase of the SIR, up from four when the concept was introduced in West Bengal. They include a sibling age gap of nine months or less, which flagged a Delhi resident's twin children, and a marital mapping mismatch where a woman is linked to her father in the old roll and her husband in the new. It reported that the term has never been clearly defined in any official communication.</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/government/declared-dead-in-draft-electoral-roll-bihar-voter-appears-in-supreme-court</t>
+          <t>https://www.thehindu.com/news/national/the-many-categories-of-sirs-logical-discrepancy-list-keep-voters-on-toes/article71504625.ece</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Wrong entries reported on the rolls</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bihar</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Purnia</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Electoral Registration Officer; Booth level officers; Election Commission; Chief Electoral Officer, Bihar</t>
+          <t>Electoral Registration Officer; Chief Electoral Officer, Goa; Election Commission</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Deletions; Migrants</t>
+          <t>Software (ECINET/ERONET); Notices and hearings; Deletions</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -27588,49 +27678,49 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Scroll reported that its analysis found 200 booths across 58 constituencies in 26 Bihar districts where between 324 and 641 names were deleted from the draft roll, 77,454 in all. It reported that most deleted voters its team met in 10 of those booths had been marked absent or shifted though they had lived at their addresses for years, and that interviews with 17 BLOs showed no consistent procedure for deciding deletions.</t>
+          <t>The Indian Express reported that Goa's Electoral Registration Officers heard electors flagged for logical discrepancies and found 97 of them eligible, but could not reverse the earlier decisions on ECINET because the permission was controlled from Delhi. It reported that the Goa Chief Electoral Officer's office wrote eight times in seven days asking for a rollback option, and that all 97 were missing from the final roll published on February 21 and were still missing on September 20.</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Parth Gupta, electoral registration officer for Purnia, acknowledged that one deleted voter should not have been asked for her parents' documents, and said, “Please provide her details and I will look into it.” Scroll also reported that Election Commission spokespersons and Bihar Chief Electoral Officer Vinod Singh Gunjiyal did not respond to requests for comment.</t>
+          <t>Goa's Chief Electoral Officer, Sanjay Goel, told the paper the decision not to include them was the Commission's. The Indian Express later reported that the Commission said, after its meeting of 26 September, that 81 of the 97 had filled Form 6 and that the Chief Electoral Officer had been told to help include them.</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://scroll.in/article/1086533/how-booth-level-officers-in-bihar-are-deleting-voters-arbitrarily</t>
+          <t>https://indianexpress.com/article/express-exclusive/election-commission-goa-sir-voter-deletion-ecinet-10891422/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Wrong entries reported on the rolls</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Election Commission; Electoral Registration Officer; Chief Electoral Officer, Bihar</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Duplicates and errors; Software (ECINET/ERONET)</t>
+          <t>Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27640,34 +27730,29 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>The Pioneer</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that a top Commission official and four Bihar EROs confirmed to it that the Commission did not run its de-duplication software during the Bihar SIR and did not give state officials access to it. It quoted the official saying the focus was on document collection. It reported that its own earlier analysis of the final roll found 14.35 lakh suspect duplicate entries.</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>The Collective said the Commission and Bihar's Chief Electoral Officer did not answer its emailed questions. In person, the Chief Electoral Officer told its reporter "We cannot share this information with you" and said the Supreme Court was hearing the matter.</t>
+          <t>Commission officials said ECINET is decentralised, that each field officer acts through their own login, and that nobody at headquarters can perform those officers' statutory functions. ERONET is now part of ECINET.</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/trc/eci-skipped-its-fraud-busting-software-lakhs-of-duplicates</t>
+          <t>https://dailypioneer.com/news/ecinet-is-decentralised-only-designated-officials-have-access-says-eci</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Wrong entries reported on the rolls</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -27677,17 +27762,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Okhla</t>
+          <t>Vikaspuri</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Delhi</t>
+          <t>Electoral Registration Officer; Chief Electoral Officer, Delhi</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Deletions; Notices and hearings</t>
+          <t>Software (ECINET/ERONET); Deletions; Notices and hearings</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27697,49 +27782,49 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Newslaundry</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Newslaundry reported that several voters in Delhi's Okhla constituency whose names were removed before the SIR began said they got no notice or hearing and learnt of the deletion only when they tried to take part in the SIR. It reported that 34,644 names were deleted in Okhla during the 2026 mapping phase, against 9,170 in all of 2025.</t>
+          <t>The Hindu reported that more than 350 Delhi electors had been marked ineligible within a month of hearings, about 200 of them in Vikaspuri, and officials said the marking could not be rolled back by the registration officer or the state's Chief Electoral Officer.</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Delhi Chief Electoral Officer Ashok Kumar said that no voter had been deleted without an inquiry and an opportunity for a hearing.</t>
+          <t>The Delhi Chief Electoral Officer wrote to officers on 25 September 2026 setting a 10-point checklist before marking anyone ineligible and telling them not to delete names on flimsy or frivolous grounds.</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://www.newslaundry.com/2026/09/24/i-didnt-know-my-name-was-deleted-voters-in-okhla-on-the-pre-sir-clean-up</t>
+          <t>https://www.thehindu.com/news/cities/Delhi/delhi-sir-over-350names-already-marked-ineligible-ceo-warns-against-deletion-on-flimsy-grounds/article71513195.ece</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Wrong entries reported on the rolls</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Chief Electoral Officer, Goa</t>
+          <t>Chief Electoral Officer, Maharashtra; Election Commission</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Form 6; Software (ECINET/ERONET); Deletions</t>
+          <t>Software (ECINET/ERONET); Notices and hearings</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27749,49 +27834,49 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>The Pioneer</t>
+          <t>Outlook India (citing NDTV)</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Goa's Chief Electoral Officer said on X that 88 of the 97 voters missing from the final roll of February 2026 had filed Form 6 and been accepted, The Pioneer reported. The cases came to light after The Indian Express reported that the Commission's software did not let verified electors be added.</t>
+          <t>Outlook, citing NDTV, reported that Maharashtra's Chief Electoral Officer S Chockalingam asked for four changes to the ECINET software and more discretion for registration officers in logical discrepancy cases.</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>The Commission said on 26 September that several portal upgrades had already been made on inputs from state Chief Electoral Officers and that further flexibility needed by field officers would be made operational.</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://dailypioneer.com/news/goa-ceo-88-of-97-left-out-voters-file-form-6-after-sir</t>
+          <t>https://www.outlookindia.com/national/maharashtra-poll-chief-seeks-more-ero-powers-as-ecinet-faces-scrutiny-over-sir</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Deaths reported during the revision</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kerala; Rajasthan; Tamil Nadu</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Kannur; Jaipur</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Booth level officers; Police; Federation of Revenue Associations of Tamil Nadu</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Deaths; BLO workload</t>
+          <t>Form 6; Documents and declaration; Software (ECINET/ERONET)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27806,49 +27891,44 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>The Indian Express reported the deaths of two BLOs. The family of a BLO in Kannur, Kerala, alleged he was under pressure to finish by December 4, and police said a note found on a BLO in Jaipur said he faced extreme pressure from his supervisor and was told he would be suspended if he did not meet his SIR target. It also reported that revenue employees in Tamil Nadu announced a statewide boycott of SIR work over workload.</t>
+          <t>The Indian Express reported that on the night of 29 to 30 September 2026 the Commission removed the SIR declaration from the online Form 6 on ECINET for states where the final SIR rolls have been published. It reported that the declaration remained for states where the SIR is still ongoing.</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Kannur District Collector Arun K Vijayan's report indicated that the BLO was not under any work pressure. The Indian Express said its multiple calls and messages to Rajasthan CEO Naveen got no response.</t>
+          <t>The article cites the Commission's September 26 announcement that ‘for non-SIR period, the Forms applicable as per Rules (the Registration of Electors Rules 1960) will be used’.</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/india/two-suicides-blo-protests-threaten-to-disrupt-sir-in-tamil-nadu-kerala-rajasthan-10371492/</t>
+          <t>https://indianexpress.com/article/india/election-commission-removes-sir-declaration-form-6-ecinet-portal-investigation-gyanesh-kumar-10899952/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Deaths reported during the revision</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Gujarat</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Tapi; Vadodara</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Booth level officers; District Election Officer</t>
+          <t>Congress; Election Commission</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Deaths; BLO workload; Women</t>
+          <t>Software (ECINET/ERONET); Commission's independence</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27858,34 +27938,34 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>ThePrint (PTI)</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>The Indian Express reported that two women assistant BLOs died of heart attacks in Tapi and Vadodara districts, bringing BLO deaths in Gujarat that week to four. The husband of one said she was a heart patient who had asked to be excused from BLO duty, which the Vadodara Collector disputed.</t>
+          <t>Congress general secretary Jairam Ramesh alleged that by restricting registration officers' access to the ECINet roll system and overruling them in Goa, West Bengal and other states, the Commission broke the Representation of the People Act, 1950.</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Vadodara District Collector Anil Dhameliya said, “We checked with the institute as well as with the local officials. She had not made any official request to be excused (from BLO duty)… We have learnt now that she was suffering from a heart ailment and had episodes of fainting in her institute as well.” He also said, “We have been cautious about ensuring that there is no excessive workload on the BLOs and therefore, we have appointed additional staff to assist in the process.” An unnamed government official said, “With a large workforce of over two lakh involved in the SIR work, these deaths can be termed as natural. Linking these to SIR is not justified and logical.”</t>
+          <t>PTI recalled that the Commission, under fire over objections from two of its Commissioners, had said differing views are a normal part of deliberation and that all its orders carry full legal sanction and follow established statutory procedures.</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/ahmedabad/blo-deaths-gujarat-sir-work-pressure-10380699/</t>
+          <t>https://theprint.in/india/cong-accuses-ec-of-lying-about-ecinet-calls-for-accountability/3059961/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Deaths reported during the revision</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -27895,12 +27975,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Booth level officers; Election Commission</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Deaths; BLO workload; Software (ECINET/ERONET)</t>
+          <t>Form 6; Deletions; Documents and declaration</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27910,54 +27990,49 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>BBC News</t>
+          <t>The Indian Express</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>The BBC reported that 10 BLOs it spoke to in Uttar Pradesh and West Bengal said they worked 14 to 15 hours a day with little rest, and that families linked the deaths of more than a dozen poll workers, by alleged suicide or heart attack, to election work stress. The BBC said it had not independently verified the causes of death. It reported BLOs saying the SIR app crashed often and that many had not been paid.</t>
+          <t>The Indian Express reported a letter of 29 September from the Commission’s Secretary ordering a special drive to enrol "left out and young/first time eligible electors" in the 20 states and union territories where the revision is complete, using the statutory Form 6, with the added declaration kept for the revision phase only. It reported that at a video conference with all Chief Electoral Officers, the states were told to compare the roll from before the revision with the one after, list those removed, visit them at home and help those left out fill in Form 6, with help from the parties’ booth agents.</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>The BBC said the Commission did not answer its questions. It cited media reports of a court affidavit in which the Commission called claims linking booth officers' deaths to the revision "false, exaggerated and politically motivated".</t>
+          <t>The letter of 29 September itself was not found. The Commission's letter of 1 October, which continues it, is in the timeline above. The Commission’s press note of 26 September, in the timeline above, had already ordered the drive, and Uttarakhand’s Chief Electoral Officer set out its steps in a press note of 3 October.</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/cy7v05exgdvo</t>
+          <t>https://indianexpress.com/article/india/election-commission-of-india-sir-left-out-voters-special-drive-10903082/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Deaths reported during the revision</t>
+          <t>Changes to the software</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>West Bengal</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Birbhum; Rampurhat; Howrah</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Election Commission; Electoral Registration Officer; Chief Electoral Officer, Delhi</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Deaths; Notices and hearings</t>
+          <t>Software (ECINET/ERONET); Notices and hearings</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27967,67 +28042,1293 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>The Indian Express</t>
+          <t>The Hindu</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>The Indian Express reported that a 75-year-old man died of cardiac arrest, according to hospital sources, after falling ill in a queue for an SIR hearing at the Rampurhat-1 block office in Birbhum. His wife and family alleged the SIR process had caused him excessive stress and held the Election Commission responsible. It also reported that an elderly man died of cardiac arrest at an SIR hearing in Howrah the previous day.</t>
+          <t>The Hindu reported that the options reached Delhi officers on 30 September and only the ten states and union territories where the third phase was still under way, and that a case marked ineligible still could not be reversed.</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>The Delhi CEO’s office and the EC did not respond to queries on why the options were introduced at this stage.</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/kolkata/elderly-man-dies-cardiac-arrest-sir-hearing-kin-allege-stress-10466884/</t>
+          <t>https://www.thehindu.com/news/national/ec-explains-new-eronet-options-for-sir-notice-disposal-to-eros-through-demo-video-no-written-instructions-yet/article71543373.ece</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Congress; Election Commission</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Form 6; Documents and declaration; Commission's independence</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Business Today</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi of the Congress, the Leader of the Opposition, said the Chief Election Commissioner had changed Form 6 illegally and unilaterally. The Commission replied on X that the statement was misleading, that its Bihar order of 24 June 2025 had the Commission's unanimous approval and was upheld by the Supreme Court on 27 May 2026, and that its press note of 26 September said the declaration attached to Form 6 had been upheld, Business Today reported.</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>https://www.businesstoday.in/india/story/misleading-eci-fact-checks-rahul-gandhis-form-6-claim-cites-sc-ruling-on-bihar-sir-order-559674-2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Appellate tribunal (West Bengal)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Election Commission</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Adjudication and appeals; Software (ECINET/ERONET)</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that at a meeting on 11 August 2026 more than a dozen West Bengal appeal tribunal judges recorded that the Commission's portal did not let them serve notices, hold virtual hearings, restore a deleted voter or give appellants a copy of the order.</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>The paper said it emailed the Commission and the Registrar General of the Calcutta High Court on 1 October and received no response.</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/bengal-sir-tribunals-election-commission-portal-issues-deleted-voters-10908185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>CERT-In; Election Commission</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Software (ECINET/ERONET)</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Hindustan Times</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Hindustan Times reported that a security researcher emailed CERT-In on 8 July 2026, copied to the Commission's complaints address, about flaws in the voter-services website and the ECINET app. The worst, in the researcher's account, let anyone obtain election officials' names and mobile numbers without logging in.</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>HT said neither CERT-In nor the Commission answered its questions of 5 October. On 6 October CERT-In told the researcher that one flaw, the hardcoded encryption key he rated least serious, had been fixed and that work on the rest was under progress. HT said none of the flaws related directly to registration officers' access to the roll, and that the email alleged no theft or misuse of data.</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/ecinet-flaws-were-flagged-to-poll-body-eci-cyber-security-agency-cert-in-in-july-says-researcher-101791401749277.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Congress; BJP; Election Commission</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Software (ECINET/ERONET); Commission's independence</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Congress alleged after the Hindustan Times report that ECINET was designed to centralise deletions and additions from the BJP's headquarters. This is a party's allegation. Hindustan Times had said none of the flaws it reported related directly to registration officers' access to the roll.</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Scroll did not report a response from the Commission to this allegation.</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>https://scroll.in/latest/1096252/ec-online-portal-designed-to-centralise-voter-deletions-from-bjp-headquarters-congress-alleges</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Changes to the software</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>CERT-In; Election Commission</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Software (ECINET/ERONET)</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>The Wire</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>The security researcher who reported the ECINET flaws told The Wire that CERT-In and the Commission did not reply to him until a Hindustan Times reporter contacted them. CERT-In then said one issue had been resolved, which he said was the most minor. He said the flaws affected at least eight parts of the Commission's systems, including the Suvidha portal and ECORE.</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>No statement from the Commission was reported.</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>https://m.thewire.in/article/government/was-ghosted-why-nisarga-adhikary-wrote-to-election-commission-and-cert-in-in-july</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Chief Electoral Officer, West Bengal; Trinamool Congress; District Election Officer</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Schedule and deadlines; Deletions</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that West Bengal's Chief Electoral Officer sent instructions on a WhatsApp group of district magistrates that brought forward the enumeration deadline and asked officers to mark voters absent before the written deadline. The Trinamool Congress had first made the allegation before the Supreme Court.</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>The Collective said the Commission and the West Bengal Chief Electoral Officer did not reply to its questions on the WhatsApp instructions.</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/ecis-top-wb-officer-sent-orders-to-state-officials-on-whatsapp</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>District Election Officer; Chief Electoral Officer, West Bengal</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Notices and hearings; Documents and declaration; Software (ECINET/ERONET)</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that district magistrates of at least three West Bengal districts wrote to the state election office asking for a written procedure for logical discrepancy cases, and that the portal accepted only the 12 listed documents.</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>The Collective reported that the officers received no response and carried on with their own methods.</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Electoral Registration Officer</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Documents and declaration; Software (ECINET/ERONET)</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>A registration officer told The Reporters' Collective that officers were told orally to ask unmapped electors for a second document besides Aadhaar, and that the software for a time would not accept Aadhaar alone. The Collective said it could not check this claim.</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/voter-registration-in-wb-as-it-deemed-fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Election Commission; Electoral Registration Officer</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Documents and declaration; Minorities</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>The New Indian Express (PTI)</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>PTI reported that the Commission's written instructions of 14 May 2026 for the third phase told registration officers to refer suspected foreign nationals to the authority under the Citizenship Act.</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/india/2026/Jun/07/sir-ec-state-poll-machinery-to-share-details-of-suspected-foreigners-with-authorities-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Electoral Registration Officer; Chief Electoral Officer, Delhi; Election Commission</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Minorities</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>A Delhi registration officer told The Hindu that officers were first told to identify suspected foreigners during enumeration and later told in the middle of it to stop, and that many oral instructions had been taken back.</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>The Delhi CEO's office and the EC did not respond to The Hindu's queries on why the new ERONET options were introduced at that stage.</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/ec-explains-new-eronet-options-for-sir-notice-disposal-to-eros-through-demo-video-no-written-instructions-yet/article71543373.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Instructions given without a written order</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Election Commission; Electoral Registration Officer</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Software (ECINET/ERONET); Notices and hearings</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>The Hindu</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>The Hindu reported that new ERONET options letting registration officers clear notice cases without a hearing or documents were explained only through an eight-minute video from the Commission's IT department, with no written instruction.</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>The Delhi CEO’s office and the EC did not respond to queries on why the options were introduced at this stage.</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/ec-explains-new-eronet-options-for-sir-notice-disposal-to-eros-through-demo-video-no-written-instructions-yet/article71543373.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Election Commission; Booth level officers</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Duplicates and errors; Living electors marked dead</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>BBC News</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>The BBC reported that voters in villages near Patna told it the Bihar draft roll carried wrong photographs, duplicate entries and the name of a person who died more than five years earlier. It reported that in Danara village many residents were not sure officials had visited their homes.</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>In response to the BBC's questions, the Election Commission shared its 24 June order on conducting the SIR and a 27 July press note outlining efforts to ensure no eligible voter was "left behind". "Further, [the commission] does not take any responsibility of any other misinformation or unsubstantiated allegations being floated around by some vested interests," it added. The BBC also noted the commission has said BLOs worked "very responsibly".</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/news/articles/c3wnx7689l5o</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Ara; Bhojpur</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Election Commission; Booth level officers</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Living electors marked dead</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>The Wire</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>The Wire reported that a voter from Ara, Bhojpur, who had been declared dead in the Bihar draft roll, appeared alive in the Supreme Court on 12 August 2025, produced by petitioner Yogendra Yadav. The voter told The Wire he had filled the enumeration form and that the BLO came to his house only after he complained.</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Senior advocate Rakesh Dwivedi, for the Commission, called the production of the voter "drama". The bench of Justices Surya Kant and Joymalya Bagchi said there may have been an "inadvertent error", which could be rectified.</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>https://m.thewire.in/article/government/declared-dead-in-draft-electoral-roll-bihar-voter-appears-in-supreme-court</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Purnia</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Electoral Registration Officer; Booth level officers; Election Commission; Chief Electoral Officer, Bihar</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Deletions; Migrants</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Scroll reported that its analysis found 200 booths across 58 constituencies in 26 Bihar districts where between 324 and 641 names were deleted from the draft roll, 77,454 in all. It reported that most deleted voters its team met in 10 of those booths had been marked absent or shifted though they had lived at their addresses for years, and that interviews with 17 BLOs showed no consistent procedure for deciding deletions.</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Parth Gupta, electoral registration officer for Purnia, acknowledged that one deleted voter should not have been asked for her parents' documents, and said, “Please provide her details and I will look into it.” Scroll also reported that Election Commission spokespersons and Bihar Chief Electoral Officer Vinod Singh Gunjiyal did not respond to requests for comment.</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>https://scroll.in/article/1086533/how-booth-level-officers-in-bihar-are-deleting-voters-arbitrarily</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Election Commission; Electoral Registration Officer; Chief Electoral Officer, Bihar</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Duplicates and errors; Software (ECINET/ERONET)</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>The Reporters' Collective reported that a top Commission official and four Bihar EROs confirmed to it that the Commission did not run its de-duplication software during the Bihar SIR and did not give state officials access to it. It quoted the official saying the focus was on document collection. It reported that its own earlier analysis of the final roll found 14.35 lakh suspect duplicate entries.</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>The Collective said the Commission and Bihar's Chief Electoral Officer did not answer its emailed questions. In person, the Chief Electoral Officer told its reporter "We cannot share this information with you" and said the Supreme Court was hearing the matter.</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>https://www.reporters-collective.in/trc/eci-skipped-its-fraud-busting-software-lakhs-of-duplicates</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Okhla</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Chief Electoral Officer, Delhi</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Deletions; Notices and hearings</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Newslaundry</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Newslaundry reported that several voters in Delhi's Okhla constituency whose names were removed before the SIR began said they got no notice or hearing and learnt of the deletion only when they tried to take part in the SIR. It reported that 34,644 names were deleted in Okhla during the 2026 mapping phase, against 9,170 in all of 2025.</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Delhi Chief Electoral Officer Ashok Kumar said that no voter had been deleted without an inquiry and an opportunity for a hearing.</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>https://www.newslaundry.com/2026/09/24/i-didnt-know-my-name-was-deleted-voters-in-okhla-on-the-pre-sir-clean-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Chief Electoral Officer, Goa</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Form 6; Software (ECINET/ERONET); Deletions</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>The Pioneer</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Goa's Chief Electoral Officer said on X that 88 of the 97 voters missing from the final roll of February 2026 had filed Form 6 and been accepted, The Pioneer reported. The cases came to light after The Indian Express reported that the Commission's software did not let verified electors be added.</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>https://dailypioneer.com/news/goa-ceo-88-of-97-left-out-voters-file-form-6-after-sir</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Vijayapura</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>District Election Officer</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Living electors marked dead; Deletions</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>The Week</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>The Week reported that Vijayapura City MLA Basanagouda R Patil Yatnal wrote to officials on 31 August seeking the deletion of 1,054 voters, eight of whom were shown as dead on death certificates, and that three living women among them came forward on 7 October. District Electoral Officer Anandh K said no Form 7 had been filed and the certificates were found to belong to namesakes, so the inquiry was opened under the Registration of Births and Deaths Act.</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Deputy Commissioner and District Electoral Officer Anandh K said officials were still seeking legal opinion on how to proceed. No response from the MLA was reported.</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/news/india/2026/10/07/dead-on-voter-list-but-alive-3-vijayapura-women-demand-action-over-sir-controversy.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Wrong entries reported on the rolls</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Chief Electoral Officer, Andhra Pradesh; Booth level officers</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Deletions; Form 6</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>The Hans India</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>The Hans India reported that Andhra Pradesh's Chief Electoral Officer announced a door-to-door re-check of 46,62,583 names before the final roll of 16 October. They are the 44,89,512 left off the draft and the 1,73,071 found ineligible after notices, and booth officers are to help anyone left off in error file Form 6.</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>The paper quoted the Chief Electoral Officer, Vivek Yadav, as saying the drive will recheck the flagged cases, and that a name found deleted by mistake is to be restored through Form 6 after verification.</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>https://www.thehansindia.com/news/cities/amaravati/final-verification-for-4663l-flagged-voters-launched-1130023</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
           <t>Deaths reported during the revision</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Kerala; Rajasthan; Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Kannur; Jaipur</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Booth level officers; Police; Federation of Revenue Associations of Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Deaths; BLO workload</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>The Indian Express reported the deaths of two BLOs. The family of a BLO in Kannur, Kerala, alleged he was under pressure to finish by December 4, and police said a note found on a BLO in Jaipur said he faced extreme pressure from his supervisor and was told he would be suspended if he did not meet his SIR target. It also reported that revenue employees in Tamil Nadu announced a statewide boycott of SIR work over workload.</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Kannur District Collector Arun K Vijayan's report indicated that the BLO was not under any work pressure. The Indian Express said its multiple calls and messages to Rajasthan CEO Naveen got no response.</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/india/two-suicides-blo-protests-threaten-to-disrupt-sir-in-tamil-nadu-kerala-rajasthan-10371492/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Deaths reported during the revision</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Tapi; Vadodara</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Booth level officers; District Election Officer</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Deaths; BLO workload; Women</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that two women assistant BLOs died of heart attacks in Tapi and Vadodara districts, bringing BLO deaths in Gujarat that week to four. The husband of one said she was a heart patient who had asked to be excused from BLO duty, which the Vadodara Collector disputed.</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Vadodara District Collector Anil Dhameliya said, “We checked with the institute as well as with the local officials. She had not made any official request to be excused (from BLO duty)… We have learnt now that she was suffering from a heart ailment and had episodes of fainting in her institute as well.” He also said, “We have been cautious about ensuring that there is no excessive workload on the BLOs and therefore, we have appointed additional staff to assist in the process.” An unnamed government official said, “With a large workforce of over two lakh involved in the SIR work, these deaths can be termed as natural. Linking these to SIR is not justified and logical.”</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/ahmedabad/blo-deaths-gujarat-sir-work-pressure-10380699/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Deaths reported during the revision</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Booth level officers; Election Commission</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Deaths; BLO workload; Software (ECINET/ERONET)</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>BBC News</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>The BBC reported that 10 BLOs it spoke to in Uttar Pradesh and West Bengal said they worked 14 to 15 hours a day with little rest, and that families linked the deaths of more than a dozen poll workers, by alleged suicide or heart attack, to election work stress. The BBC said it had not independently verified the causes of death. It reported BLOs saying the SIR app crashed often and that many had not been paid.</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>The BBC said the Commission did not answer its questions. It cited media reports of a court affidavit in which the Commission called claims linking booth officers' deaths to the revision "false, exaggerated and politically motivated".</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/news/articles/cy7v05exgdvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Deaths reported during the revision</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Birbhum; Rampurhat; Howrah</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Election Commission</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Deaths; Notices and hearings</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>The Indian Express</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>The Indian Express reported that a 75-year-old man died of cardiac arrest, according to hospital sources, after falling ill in a queue for an SIR hearing at the Rampurhat-1 block office in Birbhum. His wife and family alleged the SIR process had caused him excessive stress and held the Election Commission responsible. It also reported that an elderly man died of cardiac arrest at an SIR hearing in Howrah the previous day.</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/kolkata/elderly-man-dies-cardiac-arrest-sir-hearing-kin-allege-stress-10466884/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Deaths reported during the revision</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
         <is>
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>Purulia</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>Police; Election Commission</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G188" t="inlineStr">
         <is>
           <t>Deaths; Notices and hearings; Police and FIRs</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="H188" t="inlineStr">
         <is>
           <t>press</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I188" t="inlineStr">
         <is>
           <t>The New Indian Express (citing PTI)</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
+      <c r="J188" t="inlineStr">
         <is>
           <t>The New Indian Express, citing PTI, reported that police in Purulia registered an FIR on a complaint by the son of an 82-year-old man who died allegedly by suicide on 29 December hours before he was due at an SIR hearing. An officer was quoted as saying the case included charges of abetment of suicide and criminal conspiracy against Election Commission officials, with no official named. The family alleged he acted out of anxiety over the SIR.</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t>https://www.newindianexpress.com/india/2026/Jan/21/fir-against-eci-in-west-bengal-over-alleged-suicide-of-elderly-man-due-to-sir-anxiety</t>
         </is>
@@ -28044,7 +29345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28260,7 +29561,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>All India</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -28270,27 +29571,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>a transparency activist, co-convenor of the National Campaign for People's Right to Information</t>
+          <t>Commonwealth Human Rights Initiative</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The order or notification for the 2003 intensive revision of Bihar's rolls and the guidelines for that revision, including the forms and documents required.</t>
+          <t>How many cases the Commission had referred to the competent authority under the Citizenship Act, 1955 after deletions in the SIR, as the Supreme Court directed in May 2026, for Bihar and for each state and union territory where the revision was complete, with a split by gender.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>not supplied</t>
+          <t>no record held</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Deccan Herald and The Times of India reported that the CPIO sent only the link to the 2025 SIR guidelines of 24 June 2025 and gave nothing on the 2003 revision.</t>
+          <t>The Commission's information officer replied after 50 days that it held none of the information. He said the counts might be with the Chief Electoral Officers of the states but did not transfer the application to them.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -28300,24 +29609,24 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Deccan Herald</t>
+          <t>The Wire</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/election-commission-refuses-to-provide-2003-bihar-sir-order-on-rti-query-3701142</t>
+          <t>https://m.thewire.in/article/rights/rti-reveals-in-sir-purging-of-ineligibles-from-the-voter-lists-might-be-a-bogey</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All India</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -28327,12 +29636,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>a transparency activist, co-convenor of the National Campaign for People's Right to Information</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>All files, notings, correspondence, minutes, presentations and drafts on the SIR ordered on 24 June 2025, and a list of the files recording it.</t>
+          <t>The order or notification for the 2003 intensive revision of Bihar's rolls and the guidelines for that revision, including the forms and documents required.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -28342,7 +29656,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that the Commission replied with a link to a page of 'comprehensive instructions' dated 14 July 2025 that the outlet could not open, and did not name any file on the decision.</t>
+          <t>Deccan Herald and The Times of India reported that the CPIO sent only the link to the 2025 SIR guidelines of 24 June 2025 and gave nothing on the 2003 revision.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -28352,24 +29666,24 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>Deccan Herald</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/blog/a-dead-weblink-eci-refuses-to-share-its-records-under-rti-law</t>
+          <t>https://www.deccanherald.com/india/election-commission-refuses-to-provide-2003-bihar-sir-order-on-rti-query-3701142</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>All India</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -28379,40 +29693,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>a Trinamool Congress leader</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>95</v>
+          <t>The Reporters' Collective</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Technical documents on the 'logical discrepancy' module in ERONET used for the West Bengal SIR, its logic and parameters, procurement and testing records, file notings, instructions to EROs, and the number of electors flagged under each sub-category.</t>
+          <t>All files, notings, correspondence, minutes, presentations and drafts on the SIR ordered on 24 June 2025, and a list of the files recording it.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>refused</t>
+          <t>not supplied</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Deccan Herald (PTI) reported that the Commission held the software questions exempt under Section 8(1)(d), said no module or separate procurement had been made for the West Bengal SIR, and directed the question on flagged electors to the EROs.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>8(1)(d)</t>
+          <t>The Reporters' Collective reported that the Commission replied with a link to a page of 'comprehensive instructions' dated 14 July 2025 that the outlet could not open, and did not name any file on the decision.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -28422,54 +29718,67 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Deccan Herald (PTI)</t>
+          <t>The Reporters' Collective</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/west-bengal/tmcs-saket-gokhale-says-ec-withholding-details-of-sir-software-cites-rti-response-4157888</t>
+          <t>https://www.reporters-collective.in/blog/a-dead-weblink-eci-refuses-to-share-its-records-under-rti-law</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>All India</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministry of Law and Justice, transferred to the Election Commission of India</t>
+          <t>Election Commission of India</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>a Trinamool Congress leader</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>95</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Whether the Commission sought the Law Ministry's legal opinion on the SIR and, if so, the full paper trail of files, correspondence, memos, notes and presentations.</t>
+          <t>Technical documents on the 'logical discrepancy' module in ERONET used for the West Bengal SIR, its logic and parameters, procurement and testing records, file notings, instructions to EROs, and the number of electors flagged under each sub-category.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>transferred</t>
+          <t>refused</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that the Ministry said it keeps no record of such advice and transferred the request to the Commission, which replied on 20 August 2025 that it had no information.</t>
+          <t>Deccan Herald (PTI) reported that the Commission held the software questions exempt under Section 8(1)(d), said no module or separate procurement had been made for the West Bengal SIR, and directed the question on flagged electors to the EROs.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8(1)(d)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -28479,39 +29788,44 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>The Reporters' Collective</t>
+          <t>Deccan Herald (PTI)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/blog/a-dead-weblink-eci-refuses-to-share-its-records-under-rti-law</t>
+          <t>https://www.deccanherald.com/india/west-bengal/tmcs-saket-gokhale-says-ec-withholding-details-of-sir-software-cites-rti-response-4157888</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>All India</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CEO Bihar, transferred to the 38 DEOs</t>
+          <t>Ministry of Law and Justice, transferred to the Election Commission of India</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>a transparency activist</t>
+          <t>The Reporters' Collective</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>How many times EROs sent speed post notices to absent or shifted electors during the SIR, how many replies they received and how many notices came back undelivered.</t>
+          <t>Whether the Commission sought the Law Ministry's legal opinion on the SIR and, if so, the full paper trail of files, correspondence, memos, notes and presentations.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -28521,7 +29835,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The Reporters' Collective reported that the CEO sent the application to all 38 district election offices and that after eleven months only the Dulhin Bazar subdivision of Patna and the Hajipur district office had replied, the first saying it sent no speed post notices and the second saying electors were marked from the BLOs' door to door survey.</t>
+          <t>The Reporters' Collective reported that the Ministry said it keeps no record of such advice and transferred the request to the Commission, which replied on 20 August 2025 that it had no information.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -28536,57 +29850,44 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.reporters-collective.in/blog/follow-regulations-during-sir-not-in-bihar</t>
+          <t>https://www.reporters-collective.in/blog/a-dead-weblink-eci-refuses-to-share-its-records-under-rti-law</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>All India</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Election Commission of India</t>
+          <t>CEO Bihar, transferred to the 38 DEOs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>an independent writer</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>110</v>
+          <t>a transparency activist</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>File notings on the decision to begin the second phase of the SIR and the minutes of all meetings held on it.</t>
+          <t>How many times EROs sent speed post notices to absent or shifted electors during the SIR, how many replies they received and how many notices came back undelivered.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>partly supplied</t>
+          <t>transferred</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The Wire reported that after a first appeal the Commission supplied two pages of file notings showing the proposal initiated by an Under Secretary on 27 October 2025 and approved the same day, and supplied no minutes of meetings.</t>
+          <t>The Reporters' Collective reported that the CEO sent the application to all 38 district election offices and that after eleven months only the Dulhin Bazar subdivision of Patna and the Hajipur district office had replied, the first saying it sent no speed post notices and the second saying electors were marked from the BLOs' door to door survey.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -28596,54 +29897,54 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>The Wire</t>
+          <t>The Reporters' Collective</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://thewire.in/government/if-voter-rolls-were-properly-maintained-would-sir-be-needed-rti-records-tell-the-story</t>
+          <t>https://www.reporters-collective.in/blog/follow-regulations-during-sir-not-in-bihar</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>All India</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CEO West Bengal</t>
+          <t>Ministry of Home Affairs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>a Congress Member of Parliament from West Bengal</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
+          <t>Commonwealth Human Rights Initiative</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Figures on appeals before the SIR appellate tribunals in West Bengal, received, decided, allowed and rejected, district by district.</t>
+          <t>The name and designation of the competent authority under the Citizenship Act, 1955 for cases referred after deletions in the SIR in Bihar and the other states and union territories, and how many cases the Commission had referred to it.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>supplied</t>
+          <t>transferred</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The Wire reported a 28 page reply, Memo No. 8551/Home (Elec), showing that as of 7 August 2026 the tribunals had received 38,10,620 appeals and decided 82,782, of which 75,443 ended in inclusion and 7,339 in exclusion, with a footnote that the total mixes appeals against inclusion and against exclusion.</t>
+          <t>The Ministry transferred the application to the Law Ministry's Legislative Department the same day, which sent it to the Commission two days later. The Commission replied after 40 days, passing the questions on the competent authority back to the Ministry of Home Affairs and the questions on the counts to the Chief Electoral Officer, Bihar. No answer naming the authority had been reported.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -28658,19 +29959,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://thewire.in/rights/rti-reveals-bengal-tribunal-decided-on-just-2-17-sir-appeals-over-37-lakh-still-in-limbo</t>
+          <t>https://m.thewire.in/article/rights/rti-reveals-in-sir-purging-of-ineligibles-from-the-voter-lists-might-be-a-bogey</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>All India</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -28680,22 +29981,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>a petitioner in the Calcutta High Court</t>
-        </is>
+          <t>an independent writer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>110</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The circular or notification under which the SIR was carried out in West Bengal and any record the Commission holds on foreign nationals on the roll.</t>
+          <t>File notings on the decision to begin the second phase of the SIR and the minutes of all meetings held on it.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>appeal</t>
+          <t>partly supplied</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ETV Bharat reported that the CPIO gave no information, that the first appellate authority directed disclosure within seven days and warned on 9 February 2026, and that on 18 March 2026 the Calcutta High Court directed the CPIO to supply the information within seven days.</t>
+          <t>The Wire reported that after a first appeal the Commission supplied two pages of file notings showing the proposal initiated by an Under Secretary on 27 October 2025 and approved the same day, and supplied no minutes of meetings.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -28705,67 +30019,176 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ETV Bharat Bangla</t>
+          <t>The Wire</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/bn/state/calcutta-high-court-directs-election-commission-of-india-to-answer-rti-over-sir-circular-in-west-bengal-west-bengal-news-wbs26031805380</t>
+          <t>https://thewire.in/government/if-voter-rolls-were-properly-maintained-would-sir-be-needed-rti-records-tell-the-story</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CEO West Bengal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>a Congress Member of Parliament from West Bengal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Figures on appeals before the SIR appellate tribunals in West Bengal, received, decided, allowed and rejected, district by district.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>supplied</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>The Wire reported a 28 page reply, Memo No. 8551/Home (Elec), showing that as of 7 August 2026 the tribunals had received 38,10,620 appeals and decided 82,782, of which 75,443 ended in inclusion and 7,339 in exclusion, with a footnote that the total mixes appeals against inclusion and against exclusion.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>The Wire</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>https://thewire.in/rights/rti-reveals-bengal-tribunal-decided-on-just-2-17-sir-appeals-over-37-lakh-still-in-limbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Election Commission of India</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>a petitioner in the Calcutta High Court</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>The circular or notification under which the SIR was carried out in West Bengal and any record the Commission holds on foreign nationals on the roll.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>appeal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ETV Bharat reported that the CPIO gave no information, that the first appellate authority directed disclosure within seven days and warned on 9 February 2026, and that on 18 March 2026 the Calcutta High Court directed the CPIO to supply the information within seven days.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ETV Bharat Bangla</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/bn/state/calcutta-high-court-directs-election-commission-of-india-to-answer-rti-over-sir-circular-in-west-bengal-west-bengal-news-wbs26031805380</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>All India</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Election Commission of India, CEO Delhi, CEO West Bengal</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Internet Freedom Foundation</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>The criteria for flagging 'logical discrepancies' and their version history, contracts for ERONET 2.0, ECINET and roll digitisation, Election Commissioners' recorded objections and minutes, data retention and sharing, and State-wise counts of electors excluded, noticed, deleted and restored on appeal.</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Internet Freedom Foundation said it had filed the applications and would publish the responses and appeal any refusal.</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>press</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Internet Freedom Foundation</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://internetfreedom.in/iff-filed-rti-applications-seeking-what-the-election-commission-has-not-disclosed-about-the-sir/</t>
         </is>
@@ -79559,7 +80982,7 @@
         <v>26487213</v>
       </c>
       <c r="D3" t="n">
-        <v>9288180</v>
+        <v>9288187</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -79581,7 +81004,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -79590,9 +81013,12 @@
       <c r="K3" t="n">
         <v>6050000</v>
       </c>
+      <c r="L3" t="n">
+        <v>12969</v>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/telangana-sir-48-88-lakh-voters-cleared-for-final-rolls-3550135/</t>
+          <t>https://www.siasat.com/telangana-sir-over-74-lakh-voters-found-eligible-after-hearing-3554650/</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -79875,7 +81301,7 @@
         <v>428949</v>
       </c>
       <c r="L8" t="n">
-        <v>1194</v>
+        <v>1510</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
